--- a/BWI/bestwine_output/bestwine_Greece.xlsx
+++ b/BWI/bestwine_output/bestwine_Greece.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA353"/>
+  <dimension ref="A1:AA354"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -38477,6 +38477,95 @@
         </is>
       </c>
     </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>Tsipouri Alexia Kai Sia E.e. Greek-e-foodmarket.com</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>Tsipouri Alexia Kai Sia E.e. Greek-e-foodmarket.com</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>103849</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>Nea Ionia</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>Vorios Tomeas Athinon</t>
+        </is>
+      </c>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>24 Patriarchou Grigoriou E</t>
+        </is>
+      </c>
+      <c r="H354" s="2" t="inlineStr">
+        <is>
+          <t>142 31</t>
+        </is>
+      </c>
+      <c r="I354" s="2" t="inlineStr">
+        <is>
+          <t>https://www.greek-e-foodmarket.com</t>
+        </is>
+      </c>
+      <c r="J354" s="2" t="inlineStr"/>
+      <c r="K354" s="2" t="inlineStr"/>
+      <c r="L354" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M354" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N354" s="2" t="inlineStr">
+        <is>
+          <t>theodorou@greek-e-foodmarket.com</t>
+        </is>
+      </c>
+      <c r="O354" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0277 7993</t>
+        </is>
+      </c>
+      <c r="P354" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q354" s="2" t="inlineStr">
+        <is>
+          <t>800522492</t>
+        </is>
+      </c>
+      <c r="R354" s="2" t="inlineStr"/>
+      <c r="S354" s="2" t="inlineStr"/>
+      <c r="T354" s="2" t="inlineStr"/>
+      <c r="U354" s="2" t="inlineStr"/>
+      <c r="V354" s="2" t="inlineStr"/>
+      <c r="W354" s="2" t="inlineStr"/>
+      <c r="X354" s="2" t="inlineStr"/>
+      <c r="Y354" s="2" t="inlineStr"/>
+      <c r="Z354" s="2" t="inlineStr"/>
+      <c r="AA354" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Greece.xlsx
+++ b/BWI/bestwine_output/bestwine_Greece.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA354"/>
+  <dimension ref="A1:AA357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -38566,6 +38566,305 @@
       <c r="Z354" s="2" t="inlineStr"/>
       <c r="AA354" s="2" t="inlineStr"/>
     </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>Pgm Spirits Single Member P.c.</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>Pgm Spirits Single Member P.c.</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>158443</t>
+        </is>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>Aspropyrgos</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>Dyo Pefka</t>
+        </is>
+      </c>
+      <c r="H355" s="2" t="inlineStr">
+        <is>
+          <t>193 00</t>
+        </is>
+      </c>
+      <c r="I355" s="2" t="inlineStr">
+        <is>
+          <t>https://pgm-group.eu, https://pgm-trade.eu</t>
+        </is>
+      </c>
+      <c r="J355" s="2" t="inlineStr"/>
+      <c r="K355" s="2" t="inlineStr"/>
+      <c r="L355" s="2" t="inlineStr"/>
+      <c r="M355" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N355" s="2" t="inlineStr">
+        <is>
+          <t>info@pgm-group.eu</t>
+        </is>
+      </c>
+      <c r="O355" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0609 0129</t>
+        </is>
+      </c>
+      <c r="P355" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q355" s="2" t="inlineStr"/>
+      <c r="R355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pgm-spirits/</t>
+        </is>
+      </c>
+      <c r="S355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pgmgreece</t>
+        </is>
+      </c>
+      <c r="T355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pgmtrade/</t>
+        </is>
+      </c>
+      <c r="U355" s="2" t="inlineStr"/>
+      <c r="V355" s="2" t="inlineStr"/>
+      <c r="W355" s="2" t="inlineStr">
+        <is>
+          <t>Pavlos Moschidis</t>
+        </is>
+      </c>
+      <c r="X355" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y355" s="2" t="inlineStr"/>
+      <c r="Z355" s="2" t="inlineStr"/>
+      <c r="AA355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pavlos-moschidis-a97b3622/</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>Pgm Spirits Single Member P.c.</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>Pgm Spirits Single Member P.c.</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>158443</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>Aspropyrgos</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>Dyo Pefka</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="inlineStr">
+        <is>
+          <t>193 00</t>
+        </is>
+      </c>
+      <c r="I356" s="2" t="inlineStr">
+        <is>
+          <t>https://pgm-group.eu, https://pgm-trade.eu</t>
+        </is>
+      </c>
+      <c r="J356" s="2" t="inlineStr"/>
+      <c r="K356" s="2" t="inlineStr"/>
+      <c r="L356" s="2" t="inlineStr"/>
+      <c r="M356" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N356" s="2" t="inlineStr">
+        <is>
+          <t>info@pgm-group.eu</t>
+        </is>
+      </c>
+      <c r="O356" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0609 0129</t>
+        </is>
+      </c>
+      <c r="P356" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q356" s="2" t="inlineStr"/>
+      <c r="R356" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pgm-spirits/</t>
+        </is>
+      </c>
+      <c r="S356" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pgmgreece</t>
+        </is>
+      </c>
+      <c r="T356" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pgmtrade/</t>
+        </is>
+      </c>
+      <c r="U356" s="2" t="inlineStr"/>
+      <c r="V356" s="2" t="inlineStr"/>
+      <c r="W356" s="2" t="inlineStr">
+        <is>
+          <t>Stamatis Diamantopoulos</t>
+        </is>
+      </c>
+      <c r="X356" s="2" t="inlineStr">
+        <is>
+          <t>National Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y356" s="2" t="inlineStr"/>
+      <c r="Z356" s="2" t="inlineStr"/>
+      <c r="AA356" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stamatis-diamantopoulos-0292a6140/</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>Tsipouri Alexia Kai Sia E.e. Greek-e-foodmarket.com</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>Tsipouri Alexia Kai Sia E.e. Greek-e-foodmarket.com</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>103849</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Nea Ionia</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>24 Patriarchou Grigoriou E</t>
+        </is>
+      </c>
+      <c r="H357" s="2" t="inlineStr">
+        <is>
+          <t>142 31</t>
+        </is>
+      </c>
+      <c r="I357" s="2" t="inlineStr">
+        <is>
+          <t>https://www.greek-e-foodmarket.com</t>
+        </is>
+      </c>
+      <c r="J357" s="2" t="inlineStr"/>
+      <c r="K357" s="2" t="inlineStr"/>
+      <c r="L357" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M357" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N357" s="2" t="inlineStr">
+        <is>
+          <t>theodorou@greek-e-foodmarket.com</t>
+        </is>
+      </c>
+      <c r="O357" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0277 7993</t>
+        </is>
+      </c>
+      <c r="P357" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q357" s="2" t="inlineStr">
+        <is>
+          <t>800522492</t>
+        </is>
+      </c>
+      <c r="R357" s="2" t="inlineStr"/>
+      <c r="S357" s="2" t="inlineStr"/>
+      <c r="T357" s="2" t="inlineStr"/>
+      <c r="U357" s="2" t="inlineStr"/>
+      <c r="V357" s="2" t="inlineStr"/>
+      <c r="W357" s="2" t="inlineStr"/>
+      <c r="X357" s="2" t="inlineStr"/>
+      <c r="Y357" s="2" t="inlineStr"/>
+      <c r="Z357" s="2" t="inlineStr"/>
+      <c r="AA357" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Greece.xlsx
+++ b/BWI/bestwine_output/bestwine_Greece.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA357"/>
+  <dimension ref="A1:AA362"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -38865,6 +38865,531 @@
       <c r="Z357" s="2" t="inlineStr"/>
       <c r="AA357" s="2" t="inlineStr"/>
     </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>Concepts S.a.</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>Concepts S.a.</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>19610</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>Piraeus</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>16 Mesologgiou</t>
+        </is>
+      </c>
+      <c r="H358" s="2" t="inlineStr">
+        <is>
+          <t>185 45</t>
+        </is>
+      </c>
+      <c r="I358" s="2" t="inlineStr">
+        <is>
+          <t>https://concepts.gr</t>
+        </is>
+      </c>
+      <c r="J358" s="2" t="inlineStr"/>
+      <c r="K358" s="2" t="inlineStr"/>
+      <c r="L358" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="M358" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N358" s="2" t="inlineStr">
+        <is>
+          <t>info@concepts.gr</t>
+        </is>
+      </c>
+      <c r="O358" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0410 0011</t>
+        </is>
+      </c>
+      <c r="P358" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q358" s="2" t="inlineStr">
+        <is>
+          <t>099899595</t>
+        </is>
+      </c>
+      <c r="R358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/concepts-ltd</t>
+        </is>
+      </c>
+      <c r="S358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ConceptsGR/</t>
+        </is>
+      </c>
+      <c r="T358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/concepts_greece/</t>
+        </is>
+      </c>
+      <c r="U358" s="2" t="inlineStr"/>
+      <c r="V358" s="2" t="inlineStr"/>
+      <c r="W358" s="2" t="inlineStr">
+        <is>
+          <t>Demetre Steinhauer</t>
+        </is>
+      </c>
+      <c r="X358" s="2" t="inlineStr">
+        <is>
+          <t>Managing Partner</t>
+        </is>
+      </c>
+      <c r="Y358" s="2" t="inlineStr"/>
+      <c r="Z358" s="2" t="inlineStr"/>
+      <c r="AA358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/demetre-steinhauer-a4a31b20/</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>Concepts S.a.</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>Concepts S.a.</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>19610</t>
+        </is>
+      </c>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr">
+        <is>
+          <t>Piraeus</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t>16 Mesologgiou</t>
+        </is>
+      </c>
+      <c r="H359" s="2" t="inlineStr">
+        <is>
+          <t>185 45</t>
+        </is>
+      </c>
+      <c r="I359" s="2" t="inlineStr">
+        <is>
+          <t>https://concepts.gr</t>
+        </is>
+      </c>
+      <c r="J359" s="2" t="inlineStr"/>
+      <c r="K359" s="2" t="inlineStr"/>
+      <c r="L359" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="M359" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N359" s="2" t="inlineStr">
+        <is>
+          <t>info@concepts.gr</t>
+        </is>
+      </c>
+      <c r="O359" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0410 0011</t>
+        </is>
+      </c>
+      <c r="P359" s="2" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="Q359" s="2" t="inlineStr">
+        <is>
+          <t>099899595</t>
+        </is>
+      </c>
+      <c r="R359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/concepts-ltd</t>
+        </is>
+      </c>
+      <c r="S359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/ConceptsGR/</t>
+        </is>
+      </c>
+      <c r="T359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/concepts_greece/</t>
+        </is>
+      </c>
+      <c r="U359" s="2" t="inlineStr"/>
+      <c r="V359" s="2" t="inlineStr"/>
+      <c r="W359" s="2" t="inlineStr">
+        <is>
+          <t>Simos Tagaras</t>
+        </is>
+      </c>
+      <c r="X359" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y359" s="2" t="inlineStr"/>
+      <c r="Z359" s="2" t="inlineStr"/>
+      <c r="AA359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/simostag/</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="2" t="inlineStr">
+        <is>
+          <t>Pgm Spirits Single Member P.c.</t>
+        </is>
+      </c>
+      <c r="B360" s="2" t="inlineStr">
+        <is>
+          <t>Pgm Spirits Single Member P.c.</t>
+        </is>
+      </c>
+      <c r="C360" s="2" t="inlineStr">
+        <is>
+          <t>158443</t>
+        </is>
+      </c>
+      <c r="D360" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E360" s="2" t="inlineStr">
+        <is>
+          <t>Aspropyrgos</t>
+        </is>
+      </c>
+      <c r="F360" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G360" s="2" t="inlineStr">
+        <is>
+          <t>Dyo Pefka</t>
+        </is>
+      </c>
+      <c r="H360" s="2" t="inlineStr">
+        <is>
+          <t>193 00</t>
+        </is>
+      </c>
+      <c r="I360" s="2" t="inlineStr">
+        <is>
+          <t>https://pgm-group.eu, https://pgm-trade.eu</t>
+        </is>
+      </c>
+      <c r="J360" s="2" t="inlineStr"/>
+      <c r="K360" s="2" t="inlineStr"/>
+      <c r="L360" s="2" t="inlineStr"/>
+      <c r="M360" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N360" s="2" t="inlineStr">
+        <is>
+          <t>info@pgm-group.eu</t>
+        </is>
+      </c>
+      <c r="O360" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0609 0129</t>
+        </is>
+      </c>
+      <c r="P360" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q360" s="2" t="inlineStr"/>
+      <c r="R360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pgm-spirits/</t>
+        </is>
+      </c>
+      <c r="S360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pgmgreece</t>
+        </is>
+      </c>
+      <c r="T360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pgmtrade/</t>
+        </is>
+      </c>
+      <c r="U360" s="2" t="inlineStr"/>
+      <c r="V360" s="2" t="inlineStr"/>
+      <c r="W360" s="2" t="inlineStr">
+        <is>
+          <t>Pavlos Moschidis</t>
+        </is>
+      </c>
+      <c r="X360" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y360" s="2" t="inlineStr"/>
+      <c r="Z360" s="2" t="inlineStr"/>
+      <c r="AA360" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pavlos-moschidis-a97b3622/</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="2" t="inlineStr">
+        <is>
+          <t>Pgm Spirits Single Member P.c.</t>
+        </is>
+      </c>
+      <c r="B361" s="2" t="inlineStr">
+        <is>
+          <t>Pgm Spirits Single Member P.c.</t>
+        </is>
+      </c>
+      <c r="C361" s="2" t="inlineStr">
+        <is>
+          <t>158443</t>
+        </is>
+      </c>
+      <c r="D361" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E361" s="2" t="inlineStr">
+        <is>
+          <t>Aspropyrgos</t>
+        </is>
+      </c>
+      <c r="F361" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G361" s="2" t="inlineStr">
+        <is>
+          <t>Dyo Pefka</t>
+        </is>
+      </c>
+      <c r="H361" s="2" t="inlineStr">
+        <is>
+          <t>193 00</t>
+        </is>
+      </c>
+      <c r="I361" s="2" t="inlineStr">
+        <is>
+          <t>https://pgm-group.eu, https://pgm-trade.eu</t>
+        </is>
+      </c>
+      <c r="J361" s="2" t="inlineStr"/>
+      <c r="K361" s="2" t="inlineStr"/>
+      <c r="L361" s="2" t="inlineStr"/>
+      <c r="M361" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N361" s="2" t="inlineStr">
+        <is>
+          <t>info@pgm-group.eu</t>
+        </is>
+      </c>
+      <c r="O361" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0609 0129</t>
+        </is>
+      </c>
+      <c r="P361" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="Q361" s="2" t="inlineStr"/>
+      <c r="R361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/pgm-spirits/</t>
+        </is>
+      </c>
+      <c r="S361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pgmgreece</t>
+        </is>
+      </c>
+      <c r="T361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/pgmtrade/</t>
+        </is>
+      </c>
+      <c r="U361" s="2" t="inlineStr"/>
+      <c r="V361" s="2" t="inlineStr"/>
+      <c r="W361" s="2" t="inlineStr">
+        <is>
+          <t>Stamatis Diamantopoulos</t>
+        </is>
+      </c>
+      <c r="X361" s="2" t="inlineStr">
+        <is>
+          <t>National Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y361" s="2" t="inlineStr"/>
+      <c r="Z361" s="2" t="inlineStr"/>
+      <c r="AA361" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stamatis-diamantopoulos-0292a6140/</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="2" t="inlineStr">
+        <is>
+          <t>Tsipouri Alexia Kai Sia E.e. Greek-e-foodmarket.com</t>
+        </is>
+      </c>
+      <c r="B362" s="2" t="inlineStr">
+        <is>
+          <t>Tsipouri Alexia Kai Sia E.e. Greek-e-foodmarket.com</t>
+        </is>
+      </c>
+      <c r="C362" s="2" t="inlineStr">
+        <is>
+          <t>103849</t>
+        </is>
+      </c>
+      <c r="D362" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E362" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Nea Ionia</t>
+        </is>
+      </c>
+      <c r="F362" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G362" s="2" t="inlineStr">
+        <is>
+          <t>24 Patriarchou Grigoriou E</t>
+        </is>
+      </c>
+      <c r="H362" s="2" t="inlineStr">
+        <is>
+          <t>142 31</t>
+        </is>
+      </c>
+      <c r="I362" s="2" t="inlineStr">
+        <is>
+          <t>https://www.greek-e-foodmarket.com</t>
+        </is>
+      </c>
+      <c r="J362" s="2" t="inlineStr"/>
+      <c r="K362" s="2" t="inlineStr"/>
+      <c r="L362" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M362" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N362" s="2" t="inlineStr">
+        <is>
+          <t>theodorou@greek-e-foodmarket.com</t>
+        </is>
+      </c>
+      <c r="O362" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0277 7993</t>
+        </is>
+      </c>
+      <c r="P362" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q362" s="2" t="inlineStr">
+        <is>
+          <t>800522492</t>
+        </is>
+      </c>
+      <c r="R362" s="2" t="inlineStr"/>
+      <c r="S362" s="2" t="inlineStr"/>
+      <c r="T362" s="2" t="inlineStr"/>
+      <c r="U362" s="2" t="inlineStr"/>
+      <c r="V362" s="2" t="inlineStr"/>
+      <c r="W362" s="2" t="inlineStr"/>
+      <c r="X362" s="2" t="inlineStr"/>
+      <c r="Y362" s="2" t="inlineStr"/>
+      <c r="Z362" s="2" t="inlineStr"/>
+      <c r="AA362" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Greece.xlsx
+++ b/BWI/bestwine_output/bestwine_Greece.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA362"/>
+  <dimension ref="A1:AA365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -39390,6 +39390,333 @@
       <c r="Z362" s="2" t="inlineStr"/>
       <c r="AA362" s="2" t="inlineStr"/>
     </row>
+    <row r="363">
+      <c r="A363" s="2" t="inlineStr">
+        <is>
+          <t>Marinakis G. Emporiki S.a. Caterplus</t>
+        </is>
+      </c>
+      <c r="B363" s="2" t="inlineStr">
+        <is>
+          <t>Marinakis G. Emporiki S.a. Caterplus</t>
+        </is>
+      </c>
+      <c r="C363" s="2" t="inlineStr">
+        <is>
+          <t>88373</t>
+        </is>
+      </c>
+      <c r="D363" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E363" s="2" t="inlineStr">
+        <is>
+          <t>Koskinou</t>
+        </is>
+      </c>
+      <c r="F363" s="2" t="inlineStr">
+        <is>
+          <t>South Aegean</t>
+        </is>
+      </c>
+      <c r="G363" s="2" t="inlineStr">
+        <is>
+          <t>Vrysia - Koskinou</t>
+        </is>
+      </c>
+      <c r="H363" s="2" t="inlineStr">
+        <is>
+          <t>851 00</t>
+        </is>
+      </c>
+      <c r="I363" s="2" t="inlineStr">
+        <is>
+          <t>https://caterplus.gr, https://eshop.caterplus.gr</t>
+        </is>
+      </c>
+      <c r="J363" s="2" t="inlineStr"/>
+      <c r="K363" s="2" t="inlineStr"/>
+      <c r="L363" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M363" s="2" t="inlineStr"/>
+      <c r="N363" s="2" t="inlineStr">
+        <is>
+          <t>info@caterplus.gr</t>
+        </is>
+      </c>
+      <c r="O363" s="2" t="inlineStr">
+        <is>
+          <t>+30 2241 085197</t>
+        </is>
+      </c>
+      <c r="P363" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q363" s="2" t="inlineStr">
+        <is>
+          <t>099889909</t>
+        </is>
+      </c>
+      <c r="R363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/m-caterplus/</t>
+        </is>
+      </c>
+      <c r="S363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/caterplusgr/</t>
+        </is>
+      </c>
+      <c r="T363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/caterplusgr</t>
+        </is>
+      </c>
+      <c r="U363" s="2" t="inlineStr"/>
+      <c r="V363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@caterplusgr</t>
+        </is>
+      </c>
+      <c r="W363" s="2" t="inlineStr">
+        <is>
+          <t>Aggelos Marinakis</t>
+        </is>
+      </c>
+      <c r="X363" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y363" s="2" t="inlineStr"/>
+      <c r="Z363" s="2" t="inlineStr"/>
+      <c r="AA363" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aggelos-marinakis-9873571b0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="inlineStr">
+        <is>
+          <t>Marinakis G. Emporiki S.a. Caterplus</t>
+        </is>
+      </c>
+      <c r="B364" s="2" t="inlineStr">
+        <is>
+          <t>Marinakis G. Emporiki S.a. Caterplus</t>
+        </is>
+      </c>
+      <c r="C364" s="2" t="inlineStr">
+        <is>
+          <t>88373</t>
+        </is>
+      </c>
+      <c r="D364" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E364" s="2" t="inlineStr">
+        <is>
+          <t>Koskinou</t>
+        </is>
+      </c>
+      <c r="F364" s="2" t="inlineStr">
+        <is>
+          <t>South Aegean</t>
+        </is>
+      </c>
+      <c r="G364" s="2" t="inlineStr">
+        <is>
+          <t>Vrysia - Koskinou</t>
+        </is>
+      </c>
+      <c r="H364" s="2" t="inlineStr">
+        <is>
+          <t>851 00</t>
+        </is>
+      </c>
+      <c r="I364" s="2" t="inlineStr">
+        <is>
+          <t>https://caterplus.gr, https://eshop.caterplus.gr</t>
+        </is>
+      </c>
+      <c r="J364" s="2" t="inlineStr"/>
+      <c r="K364" s="2" t="inlineStr"/>
+      <c r="L364" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M364" s="2" t="inlineStr"/>
+      <c r="N364" s="2" t="inlineStr">
+        <is>
+          <t>info@caterplus.gr</t>
+        </is>
+      </c>
+      <c r="O364" s="2" t="inlineStr">
+        <is>
+          <t>+30 2241 085197</t>
+        </is>
+      </c>
+      <c r="P364" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q364" s="2" t="inlineStr">
+        <is>
+          <t>099889909</t>
+        </is>
+      </c>
+      <c r="R364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/m-caterplus/</t>
+        </is>
+      </c>
+      <c r="S364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/caterplusgr/</t>
+        </is>
+      </c>
+      <c r="T364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/caterplusgr</t>
+        </is>
+      </c>
+      <c r="U364" s="2" t="inlineStr"/>
+      <c r="V364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@caterplusgr</t>
+        </is>
+      </c>
+      <c r="W364" s="2" t="inlineStr">
+        <is>
+          <t>Ilias Marinakis</t>
+        </is>
+      </c>
+      <c r="X364" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y364" s="2" t="inlineStr"/>
+      <c r="Z364" s="2" t="inlineStr"/>
+      <c r="AA364" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ilias-marinakis-60a2396a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>Live &amp; Wander P.c.</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>Live &amp; Wander P.c.</t>
+        </is>
+      </c>
+      <c r="C365" s="2" t="inlineStr">
+        <is>
+          <t>57152</t>
+        </is>
+      </c>
+      <c r="D365" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E365" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Agia Paraskevi</t>
+        </is>
+      </c>
+      <c r="F365" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G365" s="2" t="inlineStr">
+        <is>
+          <t>21 Perikleous</t>
+        </is>
+      </c>
+      <c r="H365" s="2" t="inlineStr">
+        <is>
+          <t>151 22</t>
+        </is>
+      </c>
+      <c r="I365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.liveandwander.gr</t>
+        </is>
+      </c>
+      <c r="J365" s="2" t="inlineStr"/>
+      <c r="K365" s="2" t="inlineStr"/>
+      <c r="L365" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M365" s="2" t="inlineStr"/>
+      <c r="N365" s="2" t="inlineStr">
+        <is>
+          <t>info@liveandwander.gr</t>
+        </is>
+      </c>
+      <c r="O365" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 1117 8743</t>
+        </is>
+      </c>
+      <c r="P365" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q365" s="2" t="inlineStr">
+        <is>
+          <t>801274103</t>
+        </is>
+      </c>
+      <c r="R365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/live-and-wander/</t>
+        </is>
+      </c>
+      <c r="S365" s="2" t="inlineStr"/>
+      <c r="T365" s="2" t="inlineStr"/>
+      <c r="U365" s="2" t="inlineStr"/>
+      <c r="V365" s="2" t="inlineStr"/>
+      <c r="W365" s="2" t="inlineStr">
+        <is>
+          <t>Athanasia Panagiotopoulou</t>
+        </is>
+      </c>
+      <c r="X365" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y365" s="2" t="inlineStr"/>
+      <c r="Z365" s="2" t="inlineStr"/>
+      <c r="AA365" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/athanasia-panagiotopoulou</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Greece.xlsx
+++ b/BWI/bestwine_output/bestwine_Greece.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA365"/>
+  <dimension ref="A1:AA369"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -39717,6 +39717,430 @@
         </is>
       </c>
     </row>
+    <row r="366">
+      <c r="A366" s="2" t="inlineStr">
+        <is>
+          <t>Kitsaneli Antel &amp; Co E.e.</t>
+        </is>
+      </c>
+      <c r="B366" s="2" t="inlineStr">
+        <is>
+          <t>Kitsaneli Antel &amp; Co E.e.</t>
+        </is>
+      </c>
+      <c r="C366" s="2" t="inlineStr">
+        <is>
+          <t>7401</t>
+        </is>
+      </c>
+      <c r="D366" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E366" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Aigaleo</t>
+        </is>
+      </c>
+      <c r="F366" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G366" s="2" t="inlineStr">
+        <is>
+          <t>9 Didimotichou</t>
+        </is>
+      </c>
+      <c r="H366" s="2" t="inlineStr">
+        <is>
+          <t>122 42</t>
+        </is>
+      </c>
+      <c r="I366" s="2" t="inlineStr">
+        <is>
+          <t>https://planv.gr</t>
+        </is>
+      </c>
+      <c r="J366" s="2" t="inlineStr"/>
+      <c r="K366" s="2" t="inlineStr"/>
+      <c r="L366" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M366" s="2" t="inlineStr"/>
+      <c r="N366" s="2" t="inlineStr">
+        <is>
+          <t>info@planv.gr</t>
+        </is>
+      </c>
+      <c r="O366" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0578 7050</t>
+        </is>
+      </c>
+      <c r="P366" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q366" s="2" t="inlineStr">
+        <is>
+          <t>998277488</t>
+        </is>
+      </c>
+      <c r="R366" s="2" t="inlineStr"/>
+      <c r="S366" s="2" t="inlineStr"/>
+      <c r="T366" s="2" t="inlineStr"/>
+      <c r="U366" s="2" t="inlineStr"/>
+      <c r="V366" s="2" t="inlineStr"/>
+      <c r="W366" s="2" t="inlineStr">
+        <is>
+          <t>Vassilis Kitsanelis</t>
+        </is>
+      </c>
+      <c r="X366" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y366" s="2" t="inlineStr"/>
+      <c r="Z366" s="2" t="inlineStr"/>
+      <c r="AA366" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/vassilis-kitsanelis-35941597/</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="inlineStr">
+        <is>
+          <t>Marinakis G. Emporiki S.a. Caterplus</t>
+        </is>
+      </c>
+      <c r="B367" s="2" t="inlineStr">
+        <is>
+          <t>Marinakis G. Emporiki S.a. Caterplus</t>
+        </is>
+      </c>
+      <c r="C367" s="2" t="inlineStr">
+        <is>
+          <t>88373</t>
+        </is>
+      </c>
+      <c r="D367" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E367" s="2" t="inlineStr">
+        <is>
+          <t>Koskinou</t>
+        </is>
+      </c>
+      <c r="F367" s="2" t="inlineStr">
+        <is>
+          <t>South Aegean</t>
+        </is>
+      </c>
+      <c r="G367" s="2" t="inlineStr">
+        <is>
+          <t>Vrysia - Koskinou</t>
+        </is>
+      </c>
+      <c r="H367" s="2" t="inlineStr">
+        <is>
+          <t>851 00</t>
+        </is>
+      </c>
+      <c r="I367" s="2" t="inlineStr">
+        <is>
+          <t>https://caterplus.gr, https://eshop.caterplus.gr</t>
+        </is>
+      </c>
+      <c r="J367" s="2" t="inlineStr"/>
+      <c r="K367" s="2" t="inlineStr"/>
+      <c r="L367" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M367" s="2" t="inlineStr"/>
+      <c r="N367" s="2" t="inlineStr">
+        <is>
+          <t>info@caterplus.gr</t>
+        </is>
+      </c>
+      <c r="O367" s="2" t="inlineStr">
+        <is>
+          <t>+30 2241 085197</t>
+        </is>
+      </c>
+      <c r="P367" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q367" s="2" t="inlineStr">
+        <is>
+          <t>099889909</t>
+        </is>
+      </c>
+      <c r="R367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/m-caterplus/</t>
+        </is>
+      </c>
+      <c r="S367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/caterplusgr/</t>
+        </is>
+      </c>
+      <c r="T367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/caterplusgr</t>
+        </is>
+      </c>
+      <c r="U367" s="2" t="inlineStr"/>
+      <c r="V367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@caterplusgr</t>
+        </is>
+      </c>
+      <c r="W367" s="2" t="inlineStr">
+        <is>
+          <t>Aggelos Marinakis</t>
+        </is>
+      </c>
+      <c r="X367" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y367" s="2" t="inlineStr"/>
+      <c r="Z367" s="2" t="inlineStr"/>
+      <c r="AA367" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aggelos-marinakis-9873571b0/</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="inlineStr">
+        <is>
+          <t>Marinakis G. Emporiki S.a. Caterplus</t>
+        </is>
+      </c>
+      <c r="B368" s="2" t="inlineStr">
+        <is>
+          <t>Marinakis G. Emporiki S.a. Caterplus</t>
+        </is>
+      </c>
+      <c r="C368" s="2" t="inlineStr">
+        <is>
+          <t>88373</t>
+        </is>
+      </c>
+      <c r="D368" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E368" s="2" t="inlineStr">
+        <is>
+          <t>Koskinou</t>
+        </is>
+      </c>
+      <c r="F368" s="2" t="inlineStr">
+        <is>
+          <t>South Aegean</t>
+        </is>
+      </c>
+      <c r="G368" s="2" t="inlineStr">
+        <is>
+          <t>Vrysia - Koskinou</t>
+        </is>
+      </c>
+      <c r="H368" s="2" t="inlineStr">
+        <is>
+          <t>851 00</t>
+        </is>
+      </c>
+      <c r="I368" s="2" t="inlineStr">
+        <is>
+          <t>https://caterplus.gr, https://eshop.caterplus.gr</t>
+        </is>
+      </c>
+      <c r="J368" s="2" t="inlineStr"/>
+      <c r="K368" s="2" t="inlineStr"/>
+      <c r="L368" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M368" s="2" t="inlineStr"/>
+      <c r="N368" s="2" t="inlineStr">
+        <is>
+          <t>info@caterplus.gr</t>
+        </is>
+      </c>
+      <c r="O368" s="2" t="inlineStr">
+        <is>
+          <t>+30 2241 085197</t>
+        </is>
+      </c>
+      <c r="P368" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q368" s="2" t="inlineStr">
+        <is>
+          <t>099889909</t>
+        </is>
+      </c>
+      <c r="R368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/m-caterplus/</t>
+        </is>
+      </c>
+      <c r="S368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/caterplusgr/</t>
+        </is>
+      </c>
+      <c r="T368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/caterplusgr</t>
+        </is>
+      </c>
+      <c r="U368" s="2" t="inlineStr"/>
+      <c r="V368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@caterplusgr</t>
+        </is>
+      </c>
+      <c r="W368" s="2" t="inlineStr">
+        <is>
+          <t>Ilias Marinakis</t>
+        </is>
+      </c>
+      <c r="X368" s="2" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y368" s="2" t="inlineStr"/>
+      <c r="Z368" s="2" t="inlineStr"/>
+      <c r="AA368" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ilias-marinakis-60a2396a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="inlineStr">
+        <is>
+          <t>Live &amp; Wander P.c.</t>
+        </is>
+      </c>
+      <c r="B369" s="2" t="inlineStr">
+        <is>
+          <t>Live &amp; Wander P.c.</t>
+        </is>
+      </c>
+      <c r="C369" s="2" t="inlineStr">
+        <is>
+          <t>57152</t>
+        </is>
+      </c>
+      <c r="D369" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E369" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Agia Paraskevi</t>
+        </is>
+      </c>
+      <c r="F369" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G369" s="2" t="inlineStr">
+        <is>
+          <t>21 Perikleous</t>
+        </is>
+      </c>
+      <c r="H369" s="2" t="inlineStr">
+        <is>
+          <t>151 22</t>
+        </is>
+      </c>
+      <c r="I369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.liveandwander.gr</t>
+        </is>
+      </c>
+      <c r="J369" s="2" t="inlineStr"/>
+      <c r="K369" s="2" t="inlineStr"/>
+      <c r="L369" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M369" s="2" t="inlineStr"/>
+      <c r="N369" s="2" t="inlineStr">
+        <is>
+          <t>info@liveandwander.gr</t>
+        </is>
+      </c>
+      <c r="O369" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 1117 8743</t>
+        </is>
+      </c>
+      <c r="P369" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q369" s="2" t="inlineStr">
+        <is>
+          <t>801274103</t>
+        </is>
+      </c>
+      <c r="R369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/live-and-wander/</t>
+        </is>
+      </c>
+      <c r="S369" s="2" t="inlineStr"/>
+      <c r="T369" s="2" t="inlineStr"/>
+      <c r="U369" s="2" t="inlineStr"/>
+      <c r="V369" s="2" t="inlineStr"/>
+      <c r="W369" s="2" t="inlineStr">
+        <is>
+          <t>Athanasia Panagiotopoulou</t>
+        </is>
+      </c>
+      <c r="X369" s="2" t="inlineStr">
+        <is>
+          <t>Founder &amp; Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="Y369" s="2" t="inlineStr"/>
+      <c r="Z369" s="2" t="inlineStr"/>
+      <c r="AA369" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/athanasia-panagiotopoulou</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Greece.xlsx
+++ b/BWI/bestwine_output/bestwine_Greece.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA369"/>
+  <dimension ref="A1:AA372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -40141,6 +40141,281 @@
         </is>
       </c>
     </row>
+    <row r="370">
+      <c r="A370" s="2" t="inlineStr">
+        <is>
+          <t>Bevanda Ltd</t>
+        </is>
+      </c>
+      <c r="B370" s="2" t="inlineStr">
+        <is>
+          <t>Bevanda Ltd</t>
+        </is>
+      </c>
+      <c r="C370" s="2" t="inlineStr">
+        <is>
+          <t>25111</t>
+        </is>
+      </c>
+      <c r="D370" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E370" s="2" t="inlineStr">
+        <is>
+          <t>Aspropyrgos</t>
+        </is>
+      </c>
+      <c r="F370" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G370" s="2" t="inlineStr">
+        <is>
+          <t>Location Kyrillos - Aspropyrgos T.k.</t>
+        </is>
+      </c>
+      <c r="H370" s="2" t="inlineStr">
+        <is>
+          <t>193 00</t>
+        </is>
+      </c>
+      <c r="I370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bevanda.gr</t>
+        </is>
+      </c>
+      <c r="J370" s="2" t="inlineStr"/>
+      <c r="K370" s="2" t="inlineStr"/>
+      <c r="L370" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M370" s="2" t="inlineStr"/>
+      <c r="N370" s="2" t="inlineStr">
+        <is>
+          <t>bevanda@bevanda.gr</t>
+        </is>
+      </c>
+      <c r="O370" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0559 7610</t>
+        </is>
+      </c>
+      <c r="P370" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q370" s="2" t="inlineStr">
+        <is>
+          <t>997763470</t>
+        </is>
+      </c>
+      <c r="R370" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bevanda-ltd-greece</t>
+        </is>
+      </c>
+      <c r="S370" s="2" t="inlineStr"/>
+      <c r="T370" s="2" t="inlineStr"/>
+      <c r="U370" s="2" t="inlineStr"/>
+      <c r="V370" s="2" t="inlineStr"/>
+      <c r="W370" s="2" t="inlineStr"/>
+      <c r="X370" s="2" t="inlineStr"/>
+      <c r="Y370" s="2" t="inlineStr"/>
+      <c r="Z370" s="2" t="inlineStr"/>
+      <c r="AA370" s="2" t="inlineStr"/>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="inlineStr">
+        <is>
+          <t>Chaitidis A. - Nyfoudis N. Llc</t>
+        </is>
+      </c>
+      <c r="B371" s="2" t="inlineStr">
+        <is>
+          <t>Chaitidis A. - Nyfoudis N. Llc</t>
+        </is>
+      </c>
+      <c r="C371" s="2" t="inlineStr">
+        <is>
+          <t>33677</t>
+        </is>
+      </c>
+      <c r="D371" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E371" s="2" t="inlineStr">
+        <is>
+          <t>Pylaia Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F371" s="2" t="inlineStr">
+        <is>
+          <t>Central Macedonia</t>
+        </is>
+      </c>
+      <c r="G371" s="2" t="inlineStr">
+        <is>
+          <t>John Kennedy 7</t>
+        </is>
+      </c>
+      <c r="H371" s="2" t="inlineStr">
+        <is>
+          <t>555 35</t>
+        </is>
+      </c>
+      <c r="I371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.winehouse.gr</t>
+        </is>
+      </c>
+      <c r="J371" s="2" t="inlineStr"/>
+      <c r="K371" s="2" t="inlineStr"/>
+      <c r="L371" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M371" s="2" t="inlineStr"/>
+      <c r="N371" s="2" t="inlineStr">
+        <is>
+          <t>wine@winehouse.gr</t>
+        </is>
+      </c>
+      <c r="O371" s="2" t="inlineStr">
+        <is>
+          <t>+30 231 045 4187</t>
+        </is>
+      </c>
+      <c r="P371" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q371" s="2" t="inlineStr">
+        <is>
+          <t>800649061</t>
+        </is>
+      </c>
+      <c r="R371" s="2" t="inlineStr"/>
+      <c r="S371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/anestiswinehouse/</t>
+        </is>
+      </c>
+      <c r="T371" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thewinehousegreece</t>
+        </is>
+      </c>
+      <c r="U371" s="2" t="inlineStr"/>
+      <c r="V371" s="2" t="inlineStr"/>
+      <c r="W371" s="2" t="inlineStr"/>
+      <c r="X371" s="2" t="inlineStr"/>
+      <c r="Y371" s="2" t="inlineStr"/>
+      <c r="Z371" s="2" t="inlineStr"/>
+      <c r="AA371" s="2" t="inlineStr"/>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="inlineStr">
+        <is>
+          <t>Spyros Spingos S.A.</t>
+        </is>
+      </c>
+      <c r="B372" s="2" t="inlineStr">
+        <is>
+          <t>Spyros Spingos S.A.</t>
+        </is>
+      </c>
+      <c r="C372" s="2" t="inlineStr">
+        <is>
+          <t>80873</t>
+        </is>
+      </c>
+      <c r="D372" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E372" s="2" t="inlineStr">
+        <is>
+          <t>Corfu</t>
+        </is>
+      </c>
+      <c r="F372" s="2" t="inlineStr">
+        <is>
+          <t>Ioanian Islands</t>
+        </is>
+      </c>
+      <c r="G372" s="2" t="inlineStr">
+        <is>
+          <t>Mamaloi Alepou,  3rd km. Ethnikis Pelekas</t>
+        </is>
+      </c>
+      <c r="H372" s="2" t="inlineStr">
+        <is>
+          <t>491 00</t>
+        </is>
+      </c>
+      <c r="I372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.qualityfruit.gr</t>
+        </is>
+      </c>
+      <c r="J372" s="2" t="inlineStr"/>
+      <c r="K372" s="2" t="inlineStr"/>
+      <c r="L372" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M372" s="2" t="inlineStr"/>
+      <c r="N372" s="2" t="inlineStr">
+        <is>
+          <t>info@qualityfruit.gr</t>
+        </is>
+      </c>
+      <c r="O372" s="2" t="inlineStr">
+        <is>
+          <t>+30 2661 034552</t>
+        </is>
+      </c>
+      <c r="P372" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q372" s="2" t="inlineStr">
+        <is>
+          <t>998897303</t>
+        </is>
+      </c>
+      <c r="R372" s="2" t="inlineStr"/>
+      <c r="S372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/qualityfruit.gr</t>
+        </is>
+      </c>
+      <c r="T372" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/spiggosspiros/</t>
+        </is>
+      </c>
+      <c r="U372" s="2" t="inlineStr"/>
+      <c r="V372" s="2" t="inlineStr"/>
+      <c r="W372" s="2" t="inlineStr"/>
+      <c r="X372" s="2" t="inlineStr"/>
+      <c r="Y372" s="2" t="inlineStr"/>
+      <c r="Z372" s="2" t="inlineStr"/>
+      <c r="AA372" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Greece.xlsx
+++ b/BWI/bestwine_output/bestwine_Greece.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA372"/>
+  <dimension ref="A1:AA381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -40416,6 +40416,883 @@
       <c r="Z372" s="2" t="inlineStr"/>
       <c r="AA372" s="2" t="inlineStr"/>
     </row>
+    <row r="373">
+      <c r="A373" s="2" t="inlineStr">
+        <is>
+          <t>Zoris, G., &amp; Co. E.e.</t>
+        </is>
+      </c>
+      <c r="B373" s="2" t="inlineStr">
+        <is>
+          <t>Zoris, G., &amp; Co. E.e.</t>
+        </is>
+      </c>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>7430</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Zografos</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G373" s="2" t="inlineStr">
+        <is>
+          <t>83 Georgiou Papandreou</t>
+        </is>
+      </c>
+      <c r="H373" s="2" t="inlineStr">
+        <is>
+          <t>157 73</t>
+        </is>
+      </c>
+      <c r="I373" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cava-zografou.gr</t>
+        </is>
+      </c>
+      <c r="J373" s="2" t="inlineStr"/>
+      <c r="K373" s="2" t="inlineStr"/>
+      <c r="L373" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M373" s="2" t="inlineStr"/>
+      <c r="N373" s="2" t="inlineStr">
+        <is>
+          <t>zorishighspirits@gmail.com</t>
+        </is>
+      </c>
+      <c r="O373" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0771 6951</t>
+        </is>
+      </c>
+      <c r="P373" s="2" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="Q373" s="2" t="inlineStr">
+        <is>
+          <t>091095574</t>
+        </is>
+      </c>
+      <c r="R373" s="2" t="inlineStr"/>
+      <c r="S373" s="2" t="inlineStr"/>
+      <c r="T373" s="2" t="inlineStr"/>
+      <c r="U373" s="2" t="inlineStr"/>
+      <c r="V373" s="2" t="inlineStr"/>
+      <c r="W373" s="2" t="inlineStr"/>
+      <c r="X373" s="2" t="inlineStr"/>
+      <c r="Y373" s="2" t="inlineStr"/>
+      <c r="Z373" s="2" t="inlineStr"/>
+      <c r="AA373" s="2" t="inlineStr"/>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="inlineStr">
+        <is>
+          <t>Oktakosia S.a.</t>
+        </is>
+      </c>
+      <c r="B374" s="2" t="inlineStr">
+        <is>
+          <t>Oktakosia S.a.</t>
+        </is>
+      </c>
+      <c r="C374" s="2" t="inlineStr">
+        <is>
+          <t>7429</t>
+        </is>
+      </c>
+      <c r="D374" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E374" s="2" t="inlineStr">
+        <is>
+          <t>Δημοτική Ενότητα Ιωαννιτών</t>
+        </is>
+      </c>
+      <c r="F374" s="2" t="inlineStr">
+        <is>
+          <t>Epirus</t>
+        </is>
+      </c>
+      <c r="G374" s="2" t="inlineStr">
+        <is>
+          <t>1 Leoforos Georgiou Gennimata</t>
+        </is>
+      </c>
+      <c r="H374" s="2" t="inlineStr">
+        <is>
+          <t>452 21</t>
+        </is>
+      </c>
+      <c r="I374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cava800.gr</t>
+        </is>
+      </c>
+      <c r="J374" s="2" t="inlineStr"/>
+      <c r="K374" s="2" t="inlineStr"/>
+      <c r="L374" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="M374" s="2" t="inlineStr"/>
+      <c r="N374" s="2" t="inlineStr">
+        <is>
+          <t>info@cava800.gr</t>
+        </is>
+      </c>
+      <c r="O374" s="2" t="inlineStr">
+        <is>
+          <t>+30 2651 064800</t>
+        </is>
+      </c>
+      <c r="P374" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q374" s="2" t="inlineStr">
+        <is>
+          <t>082749459</t>
+        </is>
+      </c>
+      <c r="R374" s="2" t="inlineStr"/>
+      <c r="S374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cava800ioannina</t>
+        </is>
+      </c>
+      <c r="T374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cava800/</t>
+        </is>
+      </c>
+      <c r="U374" s="2" t="inlineStr"/>
+      <c r="V374" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCeBfdfNGEoQpq6J--8k36fw</t>
+        </is>
+      </c>
+      <c r="W374" s="2" t="inlineStr"/>
+      <c r="X374" s="2" t="inlineStr"/>
+      <c r="Y374" s="2" t="inlineStr"/>
+      <c r="Z374" s="2" t="inlineStr"/>
+      <c r="AA374" s="2" t="inlineStr"/>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="inlineStr">
+        <is>
+          <t>Kougioumtzoglou, I., &amp; Co E.e.</t>
+        </is>
+      </c>
+      <c r="B375" s="2" t="inlineStr">
+        <is>
+          <t>Kougioumtzoglou, I., &amp; Co E.e.</t>
+        </is>
+      </c>
+      <c r="C375" s="2" t="inlineStr">
+        <is>
+          <t>44241</t>
+        </is>
+      </c>
+      <c r="D375" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E375" s="2" t="inlineStr">
+        <is>
+          <t>Paros Municipality</t>
+        </is>
+      </c>
+      <c r="F375" s="2" t="inlineStr">
+        <is>
+          <t>South Aegean</t>
+        </is>
+      </c>
+      <c r="G375" s="2" t="inlineStr">
+        <is>
+          <t>147 Eparchiaki Odos Parikias-Naousas</t>
+        </is>
+      </c>
+      <c r="H375" s="2" t="inlineStr">
+        <is>
+          <t>844 00</t>
+        </is>
+      </c>
+      <c r="I375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cavaiosif.gr</t>
+        </is>
+      </c>
+      <c r="J375" s="2" t="inlineStr"/>
+      <c r="K375" s="2" t="inlineStr"/>
+      <c r="L375" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M375" s="2" t="inlineStr"/>
+      <c r="N375" s="2" t="inlineStr">
+        <is>
+          <t>cavaiosif@gmail.com</t>
+        </is>
+      </c>
+      <c r="O375" s="2" t="inlineStr">
+        <is>
+          <t>+30 2284 053513</t>
+        </is>
+      </c>
+      <c r="P375" s="2" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="Q375" s="2" t="inlineStr">
+        <is>
+          <t>801687390</t>
+        </is>
+      </c>
+      <c r="R375" s="2" t="inlineStr"/>
+      <c r="S375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Cava-Iosif-181836769109698/</t>
+        </is>
+      </c>
+      <c r="T375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cavaiosif/</t>
+        </is>
+      </c>
+      <c r="U375" s="2" t="inlineStr"/>
+      <c r="V375" s="2" t="inlineStr"/>
+      <c r="W375" s="2" t="inlineStr">
+        <is>
+          <t>Iosif Kougioumtoglou</t>
+        </is>
+      </c>
+      <c r="X375" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y375" s="2" t="inlineStr"/>
+      <c r="Z375" s="2" t="inlineStr"/>
+      <c r="AA375" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/iosif-kougioumtoglou-9152a6126/?originalSubdomain=gr</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>Thanopoulos, D., S.a.</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>Thanopoulos, D., S.a.</t>
+        </is>
+      </c>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>23604</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Kifisia</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G376" s="2" t="inlineStr">
+        <is>
+          <t>164 Charilaou Trikoupi</t>
+        </is>
+      </c>
+      <c r="H376" s="2" t="inlineStr">
+        <is>
+          <t>146 71</t>
+        </is>
+      </c>
+      <c r="I376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thanopoulos.gr</t>
+        </is>
+      </c>
+      <c r="J376" s="2" t="inlineStr"/>
+      <c r="K376" s="2" t="inlineStr"/>
+      <c r="L376" s="2" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="M376" s="2" t="inlineStr"/>
+      <c r="N376" s="2" t="inlineStr">
+        <is>
+          <t>info@thanopoulos.gr</t>
+        </is>
+      </c>
+      <c r="O376" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0625 4504</t>
+        </is>
+      </c>
+      <c r="P376" s="2" t="inlineStr">
+        <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="Q376" s="2" t="inlineStr">
+        <is>
+          <t>094053607</t>
+        </is>
+      </c>
+      <c r="R376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/d-thanopoulos-s-a-</t>
+        </is>
+      </c>
+      <c r="S376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/thanopoulos.supermarket/</t>
+        </is>
+      </c>
+      <c r="T376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thanopoulos.gr</t>
+        </is>
+      </c>
+      <c r="U376" s="2" t="inlineStr"/>
+      <c r="V376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCD8JQM24JCbbBz3EVzcCWOQ</t>
+        </is>
+      </c>
+      <c r="W376" s="2" t="inlineStr">
+        <is>
+          <t>Pericles Thanopoulos</t>
+        </is>
+      </c>
+      <c r="X376" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y376" s="2" t="inlineStr"/>
+      <c r="Z376" s="2" t="inlineStr"/>
+      <c r="AA376" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/pericles-thanopoulos-76117965/</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="inlineStr">
+        <is>
+          <t>Thanopoulos, D., S.a.</t>
+        </is>
+      </c>
+      <c r="B377" s="2" t="inlineStr">
+        <is>
+          <t>Thanopoulos, D., S.a.</t>
+        </is>
+      </c>
+      <c r="C377" s="2" t="inlineStr">
+        <is>
+          <t>23604</t>
+        </is>
+      </c>
+      <c r="D377" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E377" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Kifisia</t>
+        </is>
+      </c>
+      <c r="F377" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G377" s="2" t="inlineStr">
+        <is>
+          <t>164 Charilaou Trikoupi</t>
+        </is>
+      </c>
+      <c r="H377" s="2" t="inlineStr">
+        <is>
+          <t>146 71</t>
+        </is>
+      </c>
+      <c r="I377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.thanopoulos.gr</t>
+        </is>
+      </c>
+      <c r="J377" s="2" t="inlineStr"/>
+      <c r="K377" s="2" t="inlineStr"/>
+      <c r="L377" s="2" t="inlineStr">
+        <is>
+          <t>396</t>
+        </is>
+      </c>
+      <c r="M377" s="2" t="inlineStr"/>
+      <c r="N377" s="2" t="inlineStr">
+        <is>
+          <t>info@thanopoulos.gr</t>
+        </is>
+      </c>
+      <c r="O377" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0625 4504</t>
+        </is>
+      </c>
+      <c r="P377" s="2" t="inlineStr">
+        <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="Q377" s="2" t="inlineStr">
+        <is>
+          <t>094053607</t>
+        </is>
+      </c>
+      <c r="R377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/d-thanopoulos-s-a-</t>
+        </is>
+      </c>
+      <c r="S377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/thanopoulos.supermarket/</t>
+        </is>
+      </c>
+      <c r="T377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/thanopoulos.gr</t>
+        </is>
+      </c>
+      <c r="U377" s="2" t="inlineStr"/>
+      <c r="V377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCD8JQM24JCbbBz3EVzcCWOQ</t>
+        </is>
+      </c>
+      <c r="W377" s="2" t="inlineStr">
+        <is>
+          <t>Telis Thanopoulos</t>
+        </is>
+      </c>
+      <c r="X377" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y377" s="2" t="inlineStr"/>
+      <c r="Z377" s="2" t="inlineStr"/>
+      <c r="AA377" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/telis-thanopoulos-2679711ab/</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="inlineStr">
+        <is>
+          <t>Cava '83</t>
+        </is>
+      </c>
+      <c r="B378" s="2" t="inlineStr">
+        <is>
+          <t>Cava '83</t>
+        </is>
+      </c>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>7437</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>Agrinio</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>Western Greece</t>
+        </is>
+      </c>
+      <c r="G378" s="2" t="inlineStr">
+        <is>
+          <t>25 Kakkavia</t>
+        </is>
+      </c>
+      <c r="H378" s="2" t="inlineStr">
+        <is>
+          <t>301 00</t>
+        </is>
+      </c>
+      <c r="I378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cava-83.gr</t>
+        </is>
+      </c>
+      <c r="J378" s="2" t="inlineStr"/>
+      <c r="K378" s="2" t="inlineStr"/>
+      <c r="L378" s="2" t="inlineStr"/>
+      <c r="M378" s="2" t="inlineStr"/>
+      <c r="N378" s="2" t="inlineStr">
+        <is>
+          <t>stravkon@otenet.gr</t>
+        </is>
+      </c>
+      <c r="O378" s="2" t="inlineStr">
+        <is>
+          <t>+30 2641 058019</t>
+        </is>
+      </c>
+      <c r="P378" s="2" t="inlineStr"/>
+      <c r="Q378" s="2" t="inlineStr"/>
+      <c r="R378" s="2" t="inlineStr"/>
+      <c r="S378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cava-83-316610725195422/</t>
+        </is>
+      </c>
+      <c r="T378" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cava.83/</t>
+        </is>
+      </c>
+      <c r="U378" s="2" t="inlineStr"/>
+      <c r="V378" s="2" t="inlineStr"/>
+      <c r="W378" s="2" t="inlineStr"/>
+      <c r="X378" s="2" t="inlineStr"/>
+      <c r="Y378" s="2" t="inlineStr"/>
+      <c r="Z378" s="2" t="inlineStr"/>
+      <c r="AA378" s="2" t="inlineStr"/>
+    </row>
+    <row r="379">
+      <c r="A379" s="2" t="inlineStr">
+        <is>
+          <t>Hatzigiakoumis, K., S.a.</t>
+        </is>
+      </c>
+      <c r="B379" s="2" t="inlineStr">
+        <is>
+          <t>Hatzigiakoumis, K., S.a.</t>
+        </is>
+      </c>
+      <c r="C379" s="2" t="inlineStr">
+        <is>
+          <t>61984</t>
+        </is>
+      </c>
+      <c r="D379" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E379" s="2" t="inlineStr">
+        <is>
+          <t>Tigaki</t>
+        </is>
+      </c>
+      <c r="F379" s="2" t="inlineStr">
+        <is>
+          <t>South Aegean</t>
+        </is>
+      </c>
+      <c r="G379" s="2" t="inlineStr">
+        <is>
+          <t>Tigaki Road</t>
+        </is>
+      </c>
+      <c r="H379" s="2" t="inlineStr">
+        <is>
+          <t>853 00</t>
+        </is>
+      </c>
+      <c r="I379" s="2" t="inlineStr">
+        <is>
+          <t>https://eviksa.com</t>
+        </is>
+      </c>
+      <c r="J379" s="2" t="inlineStr"/>
+      <c r="K379" s="2" t="inlineStr"/>
+      <c r="L379" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M379" s="2" t="inlineStr"/>
+      <c r="N379" s="2" t="inlineStr">
+        <is>
+          <t>info@eviksa.com</t>
+        </is>
+      </c>
+      <c r="O379" s="2" t="inlineStr">
+        <is>
+          <t>+30 2242 068303</t>
+        </is>
+      </c>
+      <c r="P379" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q379" s="2" t="inlineStr">
+        <is>
+          <t>094272644</t>
+        </is>
+      </c>
+      <c r="R379" s="2" t="inlineStr"/>
+      <c r="S379" s="2" t="inlineStr"/>
+      <c r="T379" s="2" t="inlineStr"/>
+      <c r="U379" s="2" t="inlineStr"/>
+      <c r="V379" s="2" t="inlineStr"/>
+      <c r="W379" s="2" t="inlineStr">
+        <is>
+          <t>Stamatis Billis</t>
+        </is>
+      </c>
+      <c r="X379" s="2" t="inlineStr">
+        <is>
+          <t>Wine Sales &amp; Import</t>
+        </is>
+      </c>
+      <c r="Y379" s="2" t="inlineStr"/>
+      <c r="Z379" s="2" t="inlineStr"/>
+      <c r="AA379" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stamatis-billis-97295bb9/</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="2" t="inlineStr">
+        <is>
+          <t>Maragkoudaki Eirini Wine Story</t>
+        </is>
+      </c>
+      <c r="B380" s="2" t="inlineStr">
+        <is>
+          <t>Maragkoudaki Eirini Wine Story</t>
+        </is>
+      </c>
+      <c r="C380" s="2" t="inlineStr">
+        <is>
+          <t>30635</t>
+        </is>
+      </c>
+      <c r="D380" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E380" s="2" t="inlineStr">
+        <is>
+          <t>Athens</t>
+        </is>
+      </c>
+      <c r="F380" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G380" s="2" t="inlineStr">
+        <is>
+          <t>21 Nikis</t>
+        </is>
+      </c>
+      <c r="H380" s="2" t="inlineStr">
+        <is>
+          <t>105 57</t>
+        </is>
+      </c>
+      <c r="I380" s="2" t="inlineStr">
+        <is>
+          <t>https://winestory.gr</t>
+        </is>
+      </c>
+      <c r="J380" s="2" t="inlineStr"/>
+      <c r="K380" s="2" t="inlineStr"/>
+      <c r="L380" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M380" s="2" t="inlineStr"/>
+      <c r="N380" s="2" t="inlineStr">
+        <is>
+          <t>info@winestory.gr</t>
+        </is>
+      </c>
+      <c r="O380" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0323 9997</t>
+        </is>
+      </c>
+      <c r="P380" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q380" s="2" t="inlineStr">
+        <is>
+          <t>042160697</t>
+        </is>
+      </c>
+      <c r="R380" s="2" t="inlineStr"/>
+      <c r="S380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wine-story-1493124957640514/</t>
+        </is>
+      </c>
+      <c r="T380" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winestory_gr/</t>
+        </is>
+      </c>
+      <c r="U380" s="2" t="inlineStr"/>
+      <c r="V380" s="2" t="inlineStr"/>
+      <c r="W380" s="2" t="inlineStr"/>
+      <c r="X380" s="2" t="inlineStr"/>
+      <c r="Y380" s="2" t="inlineStr"/>
+      <c r="Z380" s="2" t="inlineStr"/>
+      <c r="AA380" s="2" t="inlineStr"/>
+    </row>
+    <row r="381">
+      <c r="A381" s="2" t="inlineStr">
+        <is>
+          <t>Cava Abatzis S.a.</t>
+        </is>
+      </c>
+      <c r="B381" s="2" t="inlineStr">
+        <is>
+          <t>Cava Abatzis S.a.</t>
+        </is>
+      </c>
+      <c r="C381" s="2" t="inlineStr">
+        <is>
+          <t>7444</t>
+        </is>
+      </c>
+      <c r="D381" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E381" s="2" t="inlineStr">
+        <is>
+          <t>Evosmos Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F381" s="2" t="inlineStr">
+        <is>
+          <t>Central Macedonia</t>
+        </is>
+      </c>
+      <c r="G381" s="2" t="inlineStr">
+        <is>
+          <t>12 Aristotélous</t>
+        </is>
+      </c>
+      <c r="H381" s="2" t="inlineStr">
+        <is>
+          <t>562 24</t>
+        </is>
+      </c>
+      <c r="I381" s="2" t="inlineStr">
+        <is>
+          <t>https://cava-abatzis.com</t>
+        </is>
+      </c>
+      <c r="J381" s="2" t="inlineStr"/>
+      <c r="K381" s="2" t="inlineStr"/>
+      <c r="L381" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="M381" s="2" t="inlineStr"/>
+      <c r="N381" s="2" t="inlineStr">
+        <is>
+          <t>info@cava-abatzis.com</t>
+        </is>
+      </c>
+      <c r="O381" s="2" t="inlineStr">
+        <is>
+          <t>+30 231 038 7400</t>
+        </is>
+      </c>
+      <c r="P381" s="2" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="Q381" s="2" t="inlineStr">
+        <is>
+          <t>800862290</t>
+        </is>
+      </c>
+      <c r="R381" s="2" t="inlineStr"/>
+      <c r="S381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cavaabatzis</t>
+        </is>
+      </c>
+      <c r="T381" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cava_abatzis</t>
+        </is>
+      </c>
+      <c r="U381" s="2" t="inlineStr"/>
+      <c r="V381" s="2" t="inlineStr"/>
+      <c r="W381" s="2" t="inlineStr"/>
+      <c r="X381" s="2" t="inlineStr"/>
+      <c r="Y381" s="2" t="inlineStr"/>
+      <c r="Z381" s="2" t="inlineStr"/>
+      <c r="AA381" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Greece.xlsx
+++ b/BWI/bestwine_output/bestwine_Greece.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA381"/>
+  <dimension ref="A1:AA409"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -41293,6 +41293,2910 @@
       <c r="Z381" s="2" t="inlineStr"/>
       <c r="AA381" s="2" t="inlineStr"/>
     </row>
+    <row r="382">
+      <c r="A382" s="2" t="inlineStr">
+        <is>
+          <t>Paxos Wines</t>
+        </is>
+      </c>
+      <c r="B382" s="2" t="inlineStr">
+        <is>
+          <t>Paxos Wines</t>
+        </is>
+      </c>
+      <c r="C382" s="2" t="inlineStr">
+        <is>
+          <t>108636</t>
+        </is>
+      </c>
+      <c r="D382" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E382" s="2" t="inlineStr">
+        <is>
+          <t>Lakka</t>
+        </is>
+      </c>
+      <c r="F382" s="2" t="inlineStr">
+        <is>
+          <t>Kerkira</t>
+        </is>
+      </c>
+      <c r="G382" s="2" t="inlineStr">
+        <is>
+          <t>Unnamed Road</t>
+        </is>
+      </c>
+      <c r="H382" s="2" t="inlineStr">
+        <is>
+          <t>490 82</t>
+        </is>
+      </c>
+      <c r="I382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.paxoswines.com</t>
+        </is>
+      </c>
+      <c r="J382" s="2" t="inlineStr"/>
+      <c r="K382" s="2" t="inlineStr"/>
+      <c r="L382" s="2" t="inlineStr"/>
+      <c r="M382" s="2" t="inlineStr"/>
+      <c r="N382" s="2" t="inlineStr">
+        <is>
+          <t>info@paxoswines.com</t>
+        </is>
+      </c>
+      <c r="O382" s="2" t="inlineStr">
+        <is>
+          <t>+30 2662 031404</t>
+        </is>
+      </c>
+      <c r="P382" s="2" t="inlineStr"/>
+      <c r="Q382" s="2" t="inlineStr"/>
+      <c r="R382" s="2" t="inlineStr"/>
+      <c r="S382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cavadiamanti.paxoswines</t>
+        </is>
+      </c>
+      <c r="T382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cavadiamanti_paxoswines</t>
+        </is>
+      </c>
+      <c r="U382" s="2" t="inlineStr"/>
+      <c r="V382" s="2" t="inlineStr"/>
+      <c r="W382" s="2" t="inlineStr">
+        <is>
+          <t>Andreas Diamantis</t>
+        </is>
+      </c>
+      <c r="X382" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y382" s="2" t="inlineStr"/>
+      <c r="Z382" s="2" t="inlineStr"/>
+      <c r="AA382" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/andreas-diamantis-160413158/</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="2" t="inlineStr">
+        <is>
+          <t>Dimitriadis, Stilianos, P.c.</t>
+        </is>
+      </c>
+      <c r="B383" s="2" t="inlineStr">
+        <is>
+          <t>Dimitriadis, Stilianos, P.c.</t>
+        </is>
+      </c>
+      <c r="C383" s="2" t="inlineStr">
+        <is>
+          <t>7412</t>
+        </is>
+      </c>
+      <c r="D383" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E383" s="2" t="inlineStr">
+        <is>
+          <t>Thessaloniki Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F383" s="2" t="inlineStr">
+        <is>
+          <t>Central Macedonia</t>
+        </is>
+      </c>
+      <c r="G383" s="2" t="inlineStr">
+        <is>
+          <t>86 Georgiou Papandreou</t>
+        </is>
+      </c>
+      <c r="H383" s="2" t="inlineStr">
+        <is>
+          <t>546 55</t>
+        </is>
+      </c>
+      <c r="I383" s="2" t="inlineStr">
+        <is>
+          <t>https://mycava.gr</t>
+        </is>
+      </c>
+      <c r="J383" s="2" t="inlineStr"/>
+      <c r="K383" s="2" t="inlineStr"/>
+      <c r="L383" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M383" s="2" t="inlineStr"/>
+      <c r="N383" s="2" t="inlineStr">
+        <is>
+          <t>info@mycava.gr</t>
+        </is>
+      </c>
+      <c r="O383" s="2" t="inlineStr">
+        <is>
+          <t>+30 231 041 0605</t>
+        </is>
+      </c>
+      <c r="P383" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q383" s="2" t="inlineStr">
+        <is>
+          <t>800594395</t>
+        </is>
+      </c>
+      <c r="R383" s="2" t="inlineStr">
+        <is>
+          <t>https://gr.linkedin.com/company/mycava.gr</t>
+        </is>
+      </c>
+      <c r="S383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/mycava.gr</t>
+        </is>
+      </c>
+      <c r="T383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mycava_gr/</t>
+        </is>
+      </c>
+      <c r="U383" s="2" t="inlineStr"/>
+      <c r="V383" s="2" t="inlineStr"/>
+      <c r="W383" s="2" t="inlineStr">
+        <is>
+          <t>Stelios Dimitriadis</t>
+        </is>
+      </c>
+      <c r="X383" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y383" s="2" t="inlineStr"/>
+      <c r="Z383" s="2" t="inlineStr"/>
+      <c r="AA383" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stelios-dimitriadis-739210151/</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="2" t="inlineStr">
+        <is>
+          <t>Dimitriadis, Stilianos, P.c.</t>
+        </is>
+      </c>
+      <c r="B384" s="2" t="inlineStr">
+        <is>
+          <t>Dimitriadis, Stilianos, P.c.</t>
+        </is>
+      </c>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>7412</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>Thessaloniki Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="inlineStr">
+        <is>
+          <t>Central Macedonia</t>
+        </is>
+      </c>
+      <c r="G384" s="2" t="inlineStr">
+        <is>
+          <t>86 Georgiou Papandreou</t>
+        </is>
+      </c>
+      <c r="H384" s="2" t="inlineStr">
+        <is>
+          <t>546 55</t>
+        </is>
+      </c>
+      <c r="I384" s="2" t="inlineStr">
+        <is>
+          <t>https://mycava.gr</t>
+        </is>
+      </c>
+      <c r="J384" s="2" t="inlineStr"/>
+      <c r="K384" s="2" t="inlineStr"/>
+      <c r="L384" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M384" s="2" t="inlineStr"/>
+      <c r="N384" s="2" t="inlineStr">
+        <is>
+          <t>info@mycava.gr</t>
+        </is>
+      </c>
+      <c r="O384" s="2" t="inlineStr">
+        <is>
+          <t>+30 231 041 0605</t>
+        </is>
+      </c>
+      <c r="P384" s="2" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="Q384" s="2" t="inlineStr">
+        <is>
+          <t>800594395</t>
+        </is>
+      </c>
+      <c r="R384" s="2" t="inlineStr">
+        <is>
+          <t>https://gr.linkedin.com/company/mycava.gr</t>
+        </is>
+      </c>
+      <c r="S384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/mycava.gr</t>
+        </is>
+      </c>
+      <c r="T384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/mycava_gr/</t>
+        </is>
+      </c>
+      <c r="U384" s="2" t="inlineStr"/>
+      <c r="V384" s="2" t="inlineStr"/>
+      <c r="W384" s="2" t="inlineStr">
+        <is>
+          <t>Antonis Pattakos</t>
+        </is>
+      </c>
+      <c r="X384" s="2" t="inlineStr">
+        <is>
+          <t>Sales Executive</t>
+        </is>
+      </c>
+      <c r="Y384" s="2" t="inlineStr"/>
+      <c r="Z384" s="2" t="inlineStr"/>
+      <c r="AA384" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/antonis-pattakos-53322586/</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="2" t="inlineStr">
+        <is>
+          <t>Cava Anthidis P.c.</t>
+        </is>
+      </c>
+      <c r="B385" s="2" t="inlineStr">
+        <is>
+          <t>Cava Anthidis P.c.</t>
+        </is>
+      </c>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>7389</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Athens</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G385" s="2" t="inlineStr">
+        <is>
+          <t>45 Patriarchou Ioakim</t>
+        </is>
+      </c>
+      <c r="H385" s="2" t="inlineStr">
+        <is>
+          <t>106 76</t>
+        </is>
+      </c>
+      <c r="I385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.anthidis.gr</t>
+        </is>
+      </c>
+      <c r="J385" s="2" t="inlineStr"/>
+      <c r="K385" s="2" t="inlineStr"/>
+      <c r="L385" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M385" s="2" t="inlineStr"/>
+      <c r="N385" s="2" t="inlineStr">
+        <is>
+          <t>eshop@anthidis.gr</t>
+        </is>
+      </c>
+      <c r="O385" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0806 9220</t>
+        </is>
+      </c>
+      <c r="P385" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q385" s="2" t="inlineStr">
+        <is>
+          <t>801092400</t>
+        </is>
+      </c>
+      <c r="R385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cava-anthidis/</t>
+        </is>
+      </c>
+      <c r="S385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cava.anthidis</t>
+        </is>
+      </c>
+      <c r="T385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cava_anthidis</t>
+        </is>
+      </c>
+      <c r="U385" s="2" t="inlineStr"/>
+      <c r="V385" s="2" t="inlineStr"/>
+      <c r="W385" s="2" t="inlineStr">
+        <is>
+          <t>Anna Triantafyllis</t>
+        </is>
+      </c>
+      <c r="X385" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y385" s="2" t="inlineStr"/>
+      <c r="Z385" s="2" t="inlineStr"/>
+      <c r="AA385" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anna-triantafyllis-8a41431b3/</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" s="2" t="inlineStr">
+        <is>
+          <t>Cava Anthidis P.c.</t>
+        </is>
+      </c>
+      <c r="B386" s="2" t="inlineStr">
+        <is>
+          <t>Cava Anthidis P.c.</t>
+        </is>
+      </c>
+      <c r="C386" s="2" t="inlineStr">
+        <is>
+          <t>7389</t>
+        </is>
+      </c>
+      <c r="D386" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E386" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Athens</t>
+        </is>
+      </c>
+      <c r="F386" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G386" s="2" t="inlineStr">
+        <is>
+          <t>45 Patriarchou Ioakim</t>
+        </is>
+      </c>
+      <c r="H386" s="2" t="inlineStr">
+        <is>
+          <t>106 76</t>
+        </is>
+      </c>
+      <c r="I386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.anthidis.gr</t>
+        </is>
+      </c>
+      <c r="J386" s="2" t="inlineStr"/>
+      <c r="K386" s="2" t="inlineStr"/>
+      <c r="L386" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="M386" s="2" t="inlineStr"/>
+      <c r="N386" s="2" t="inlineStr">
+        <is>
+          <t>eshop@anthidis.gr</t>
+        </is>
+      </c>
+      <c r="O386" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0806 9220</t>
+        </is>
+      </c>
+      <c r="P386" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q386" s="2" t="inlineStr">
+        <is>
+          <t>801092400</t>
+        </is>
+      </c>
+      <c r="R386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cava-anthidis/</t>
+        </is>
+      </c>
+      <c r="S386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cava.anthidis</t>
+        </is>
+      </c>
+      <c r="T386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cava_anthidis</t>
+        </is>
+      </c>
+      <c r="U386" s="2" t="inlineStr"/>
+      <c r="V386" s="2" t="inlineStr"/>
+      <c r="W386" s="2" t="inlineStr">
+        <is>
+          <t>Ilias Anthidis</t>
+        </is>
+      </c>
+      <c r="X386" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y386" s="2" t="inlineStr"/>
+      <c r="Z386" s="2" t="inlineStr"/>
+      <c r="AA386" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ilias-anthidis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>Rokos, Athanassios &amp; George, E.e.</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>Rokos, Athanassios &amp; George, E.e.</t>
+        </is>
+      </c>
+      <c r="C387" s="2" t="inlineStr">
+        <is>
+          <t>27378</t>
+        </is>
+      </c>
+      <c r="D387" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E387" s="2" t="inlineStr">
+        <is>
+          <t>Municipal Unit of Larissa</t>
+        </is>
+      </c>
+      <c r="F387" s="2" t="inlineStr">
+        <is>
+          <t>Thessaly</t>
+        </is>
+      </c>
+      <c r="G387" s="2" t="inlineStr">
+        <is>
+          <t>35 Iroon Politechniou</t>
+        </is>
+      </c>
+      <c r="H387" s="2" t="inlineStr">
+        <is>
+          <t>412 22</t>
+        </is>
+      </c>
+      <c r="I387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cavarokos.gr</t>
+        </is>
+      </c>
+      <c r="J387" s="2" t="inlineStr"/>
+      <c r="K387" s="2" t="inlineStr"/>
+      <c r="L387" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M387" s="2" t="inlineStr"/>
+      <c r="N387" s="2" t="inlineStr">
+        <is>
+          <t>info@cavarokos.gr</t>
+        </is>
+      </c>
+      <c r="O387" s="2" t="inlineStr">
+        <is>
+          <t>+30 241 067 0210</t>
+        </is>
+      </c>
+      <c r="P387" s="2" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="Q387" s="2" t="inlineStr">
+        <is>
+          <t>999152087</t>
+        </is>
+      </c>
+      <c r="R387" s="2" t="inlineStr"/>
+      <c r="S387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cavarokos/</t>
+        </is>
+      </c>
+      <c r="T387" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cavarokos</t>
+        </is>
+      </c>
+      <c r="U387" s="2" t="inlineStr"/>
+      <c r="V387" s="2" t="inlineStr"/>
+      <c r="W387" s="2" t="inlineStr"/>
+      <c r="X387" s="2" t="inlineStr"/>
+      <c r="Y387" s="2" t="inlineStr"/>
+      <c r="Z387" s="2" t="inlineStr"/>
+      <c r="AA387" s="2" t="inlineStr"/>
+    </row>
+    <row r="388">
+      <c r="A388" s="2" t="inlineStr">
+        <is>
+          <t>Arion Athens Cava</t>
+        </is>
+      </c>
+      <c r="B388" s="2" t="inlineStr">
+        <is>
+          <t>Arion Athens Cava</t>
+        </is>
+      </c>
+      <c r="C388" s="2" t="inlineStr">
+        <is>
+          <t>7410</t>
+        </is>
+      </c>
+      <c r="D388" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E388" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Agios Dimitrios</t>
+        </is>
+      </c>
+      <c r="F388" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G388" s="2" t="inlineStr">
+        <is>
+          <t>80 Stratarchou Alexandrou Papagou</t>
+        </is>
+      </c>
+      <c r="H388" s="2" t="inlineStr">
+        <is>
+          <t>173 43</t>
+        </is>
+      </c>
+      <c r="I388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.cavaarion.gr</t>
+        </is>
+      </c>
+      <c r="J388" s="2" t="inlineStr"/>
+      <c r="K388" s="2" t="inlineStr"/>
+      <c r="L388" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M388" s="2" t="inlineStr"/>
+      <c r="N388" s="2" t="inlineStr">
+        <is>
+          <t>info@cavaarion.gr</t>
+        </is>
+      </c>
+      <c r="O388" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0973 9063</t>
+        </is>
+      </c>
+      <c r="P388" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q388" s="2" t="inlineStr">
+        <is>
+          <t>999421913</t>
+        </is>
+      </c>
+      <c r="R388" s="2" t="inlineStr"/>
+      <c r="S388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cavaarion</t>
+        </is>
+      </c>
+      <c r="T388" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cavaarion.gr</t>
+        </is>
+      </c>
+      <c r="U388" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/cavaarion_gr</t>
+        </is>
+      </c>
+      <c r="V388" s="2" t="inlineStr"/>
+      <c r="W388" s="2" t="inlineStr"/>
+      <c r="X388" s="2" t="inlineStr"/>
+      <c r="Y388" s="2" t="inlineStr"/>
+      <c r="Z388" s="2" t="inlineStr"/>
+      <c r="AA388" s="2" t="inlineStr"/>
+    </row>
+    <row r="389">
+      <c r="A389" s="2" t="inlineStr">
+        <is>
+          <t>Wine Cellar Ioannina</t>
+        </is>
+      </c>
+      <c r="B389" s="2" t="inlineStr">
+        <is>
+          <t>Wine Cellar Ioannina</t>
+        </is>
+      </c>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>24831</t>
+        </is>
+      </c>
+      <c r="D389" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="inlineStr">
+        <is>
+          <t>Preveza</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="inlineStr">
+        <is>
+          <t>Epirus</t>
+        </is>
+      </c>
+      <c r="G389" s="2" t="inlineStr">
+        <is>
+          <t>10 Anexartisias</t>
+        </is>
+      </c>
+      <c r="H389" s="2" t="inlineStr">
+        <is>
+          <t>481 00</t>
+        </is>
+      </c>
+      <c r="I389" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oinothiki.gr</t>
+        </is>
+      </c>
+      <c r="J389" s="2" t="inlineStr"/>
+      <c r="K389" s="2" t="inlineStr"/>
+      <c r="L389" s="2" t="inlineStr"/>
+      <c r="M389" s="2" t="inlineStr"/>
+      <c r="N389" s="2" t="inlineStr">
+        <is>
+          <t>oinothiki.cava@gmail.com</t>
+        </is>
+      </c>
+      <c r="O389" s="2" t="inlineStr">
+        <is>
+          <t>+30 2651 044334</t>
+        </is>
+      </c>
+      <c r="P389" s="2" t="inlineStr"/>
+      <c r="Q389" s="2" t="inlineStr"/>
+      <c r="R389" s="2" t="inlineStr"/>
+      <c r="S389" s="2" t="inlineStr"/>
+      <c r="T389" s="2" t="inlineStr"/>
+      <c r="U389" s="2" t="inlineStr"/>
+      <c r="V389" s="2" t="inlineStr"/>
+      <c r="W389" s="2" t="inlineStr"/>
+      <c r="X389" s="2" t="inlineStr"/>
+      <c r="Y389" s="2" t="inlineStr"/>
+      <c r="Z389" s="2" t="inlineStr"/>
+      <c r="AA389" s="2" t="inlineStr"/>
+    </row>
+    <row r="390">
+      <c r="A390" s="2" t="inlineStr">
+        <is>
+          <t>Oak Cava</t>
+        </is>
+      </c>
+      <c r="B390" s="2" t="inlineStr">
+        <is>
+          <t>Oak Cava</t>
+        </is>
+      </c>
+      <c r="C390" s="2" t="inlineStr">
+        <is>
+          <t>34993</t>
+        </is>
+      </c>
+      <c r="D390" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E390" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Chalandri</t>
+        </is>
+      </c>
+      <c r="F390" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G390" s="2" t="inlineStr">
+        <is>
+          <t>282 Leoforos Kifisias</t>
+        </is>
+      </c>
+      <c r="H390" s="2" t="inlineStr">
+        <is>
+          <t>152 32</t>
+        </is>
+      </c>
+      <c r="I390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oakcava.gr</t>
+        </is>
+      </c>
+      <c r="J390" s="2" t="inlineStr"/>
+      <c r="K390" s="2" t="inlineStr"/>
+      <c r="L390" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M390" s="2" t="inlineStr"/>
+      <c r="N390" s="2" t="inlineStr">
+        <is>
+          <t>contact@oakcava.gr</t>
+        </is>
+      </c>
+      <c r="O390" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0685 8078</t>
+        </is>
+      </c>
+      <c r="P390" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q390" s="2" t="inlineStr">
+        <is>
+          <t>800478519</t>
+        </is>
+      </c>
+      <c r="R390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/oak-cava/</t>
+        </is>
+      </c>
+      <c r="S390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/oakcava</t>
+        </is>
+      </c>
+      <c r="T390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oakcava</t>
+        </is>
+      </c>
+      <c r="U390" s="2" t="inlineStr"/>
+      <c r="V390" s="2" t="inlineStr"/>
+      <c r="W390" s="2" t="inlineStr">
+        <is>
+          <t>Giannis Vagenas</t>
+        </is>
+      </c>
+      <c r="X390" s="2" t="inlineStr">
+        <is>
+          <t>Director Of Operations &amp; Wine director</t>
+        </is>
+      </c>
+      <c r="Y390" s="2" t="inlineStr"/>
+      <c r="Z390" s="2" t="inlineStr"/>
+      <c r="AA390" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/giannis-vagenas-b2573320a/?originalSubdomain=gr</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" s="2" t="inlineStr">
+        <is>
+          <t>Oak Cava</t>
+        </is>
+      </c>
+      <c r="B391" s="2" t="inlineStr">
+        <is>
+          <t>Oak Cava</t>
+        </is>
+      </c>
+      <c r="C391" s="2" t="inlineStr">
+        <is>
+          <t>34993</t>
+        </is>
+      </c>
+      <c r="D391" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E391" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Chalandri</t>
+        </is>
+      </c>
+      <c r="F391" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G391" s="2" t="inlineStr">
+        <is>
+          <t>282 Leoforos Kifisias</t>
+        </is>
+      </c>
+      <c r="H391" s="2" t="inlineStr">
+        <is>
+          <t>152 32</t>
+        </is>
+      </c>
+      <c r="I391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oakcava.gr</t>
+        </is>
+      </c>
+      <c r="J391" s="2" t="inlineStr"/>
+      <c r="K391" s="2" t="inlineStr"/>
+      <c r="L391" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M391" s="2" t="inlineStr"/>
+      <c r="N391" s="2" t="inlineStr">
+        <is>
+          <t>contact@oakcava.gr</t>
+        </is>
+      </c>
+      <c r="O391" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0685 8078</t>
+        </is>
+      </c>
+      <c r="P391" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q391" s="2" t="inlineStr">
+        <is>
+          <t>800478519</t>
+        </is>
+      </c>
+      <c r="R391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/oak-cava/</t>
+        </is>
+      </c>
+      <c r="S391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/oakcava</t>
+        </is>
+      </c>
+      <c r="T391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oakcava</t>
+        </is>
+      </c>
+      <c r="U391" s="2" t="inlineStr"/>
+      <c r="V391" s="2" t="inlineStr"/>
+      <c r="W391" s="2" t="inlineStr">
+        <is>
+          <t>Panagiotis Paschalidis</t>
+        </is>
+      </c>
+      <c r="X391" s="2" t="inlineStr">
+        <is>
+          <t>General Manager &amp; Head of Procurement</t>
+        </is>
+      </c>
+      <c r="Y391" s="2" t="inlineStr"/>
+      <c r="Z391" s="2" t="inlineStr"/>
+      <c r="AA391" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/panagiotis-paschalidis-wset-dip-a8267a100/</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="2" t="inlineStr">
+        <is>
+          <t>Oak Cava</t>
+        </is>
+      </c>
+      <c r="B392" s="2" t="inlineStr">
+        <is>
+          <t>Oak Cava</t>
+        </is>
+      </c>
+      <c r="C392" s="2" t="inlineStr">
+        <is>
+          <t>34993</t>
+        </is>
+      </c>
+      <c r="D392" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E392" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Chalandri</t>
+        </is>
+      </c>
+      <c r="F392" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G392" s="2" t="inlineStr">
+        <is>
+          <t>282 Leoforos Kifisias</t>
+        </is>
+      </c>
+      <c r="H392" s="2" t="inlineStr">
+        <is>
+          <t>152 32</t>
+        </is>
+      </c>
+      <c r="I392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.oakcava.gr</t>
+        </is>
+      </c>
+      <c r="J392" s="2" t="inlineStr"/>
+      <c r="K392" s="2" t="inlineStr"/>
+      <c r="L392" s="2" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="M392" s="2" t="inlineStr"/>
+      <c r="N392" s="2" t="inlineStr">
+        <is>
+          <t>contact@oakcava.gr</t>
+        </is>
+      </c>
+      <c r="O392" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0685 8078</t>
+        </is>
+      </c>
+      <c r="P392" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q392" s="2" t="inlineStr">
+        <is>
+          <t>800478519</t>
+        </is>
+      </c>
+      <c r="R392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/oak-cava/</t>
+        </is>
+      </c>
+      <c r="S392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/oakcava</t>
+        </is>
+      </c>
+      <c r="T392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/oakcava</t>
+        </is>
+      </c>
+      <c r="U392" s="2" t="inlineStr"/>
+      <c r="V392" s="2" t="inlineStr"/>
+      <c r="W392" s="2" t="inlineStr">
+        <is>
+          <t>Paraskevi Kyrpikidi</t>
+        </is>
+      </c>
+      <c r="X392" s="2" t="inlineStr">
+        <is>
+          <t>Wine Sales Specialist</t>
+        </is>
+      </c>
+      <c r="Y392" s="2" t="inlineStr"/>
+      <c r="Z392" s="2" t="inlineStr"/>
+      <c r="AA392" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/paraskevikyrpikidi/</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" s="2" t="inlineStr">
+        <is>
+          <t>Jannec Sa</t>
+        </is>
+      </c>
+      <c r="B393" s="2" t="inlineStr">
+        <is>
+          <t>Jannec Sa</t>
+        </is>
+      </c>
+      <c r="C393" s="2" t="inlineStr">
+        <is>
+          <t>39125</t>
+        </is>
+      </c>
+      <c r="D393" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E393" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Aigaleo</t>
+        </is>
+      </c>
+      <c r="F393" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G393" s="2" t="inlineStr">
+        <is>
+          <t>Emmanuel Pappas 3</t>
+        </is>
+      </c>
+      <c r="H393" s="2" t="inlineStr">
+        <is>
+          <t>122 42</t>
+        </is>
+      </c>
+      <c r="I393" s="2" t="inlineStr">
+        <is>
+          <t>https://jannec.gr</t>
+        </is>
+      </c>
+      <c r="J393" s="2" t="inlineStr"/>
+      <c r="K393" s="2" t="inlineStr"/>
+      <c r="L393" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M393" s="2" t="inlineStr"/>
+      <c r="N393" s="2" t="inlineStr">
+        <is>
+          <t>contact@jannec.gr</t>
+        </is>
+      </c>
+      <c r="O393" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0495 4874</t>
+        </is>
+      </c>
+      <c r="P393" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q393" s="2" t="inlineStr">
+        <is>
+          <t>999514226</t>
+        </is>
+      </c>
+      <c r="R393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jannec-sa-gr/</t>
+        </is>
+      </c>
+      <c r="S393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61553865101850</t>
+        </is>
+      </c>
+      <c r="T393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jannecgr/</t>
+        </is>
+      </c>
+      <c r="U393" s="2" t="inlineStr"/>
+      <c r="V393" s="2" t="inlineStr"/>
+      <c r="W393" s="2" t="inlineStr">
+        <is>
+          <t>Mike Katsipis</t>
+        </is>
+      </c>
+      <c r="X393" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner</t>
+        </is>
+      </c>
+      <c r="Y393" s="2" t="inlineStr"/>
+      <c r="Z393" s="2" t="inlineStr"/>
+      <c r="AA393" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mike-katsipis-03653bb5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="2" t="inlineStr">
+        <is>
+          <t>Jannec Sa</t>
+        </is>
+      </c>
+      <c r="B394" s="2" t="inlineStr">
+        <is>
+          <t>Jannec Sa</t>
+        </is>
+      </c>
+      <c r="C394" s="2" t="inlineStr">
+        <is>
+          <t>39125</t>
+        </is>
+      </c>
+      <c r="D394" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E394" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Aigaleo</t>
+        </is>
+      </c>
+      <c r="F394" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G394" s="2" t="inlineStr">
+        <is>
+          <t>Emmanuel Pappas 3</t>
+        </is>
+      </c>
+      <c r="H394" s="2" t="inlineStr">
+        <is>
+          <t>122 42</t>
+        </is>
+      </c>
+      <c r="I394" s="2" t="inlineStr">
+        <is>
+          <t>https://jannec.gr</t>
+        </is>
+      </c>
+      <c r="J394" s="2" t="inlineStr"/>
+      <c r="K394" s="2" t="inlineStr"/>
+      <c r="L394" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M394" s="2" t="inlineStr"/>
+      <c r="N394" s="2" t="inlineStr">
+        <is>
+          <t>contact@jannec.gr</t>
+        </is>
+      </c>
+      <c r="O394" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0495 4874</t>
+        </is>
+      </c>
+      <c r="P394" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q394" s="2" t="inlineStr">
+        <is>
+          <t>999514226</t>
+        </is>
+      </c>
+      <c r="R394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jannec-sa-gr/</t>
+        </is>
+      </c>
+      <c r="S394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61553865101850</t>
+        </is>
+      </c>
+      <c r="T394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jannecgr/</t>
+        </is>
+      </c>
+      <c r="U394" s="2" t="inlineStr"/>
+      <c r="V394" s="2" t="inlineStr"/>
+      <c r="W394" s="2" t="inlineStr">
+        <is>
+          <t>Anastasia Kabouraki</t>
+        </is>
+      </c>
+      <c r="X394" s="2" t="inlineStr">
+        <is>
+          <t>Commercial Operations Specialist</t>
+        </is>
+      </c>
+      <c r="Y394" s="2" t="inlineStr"/>
+      <c r="Z394" s="2" t="inlineStr"/>
+      <c r="AA394" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anastasia-kabouraki-8632a069/</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" s="2" t="inlineStr">
+        <is>
+          <t>Jannec Sa</t>
+        </is>
+      </c>
+      <c r="B395" s="2" t="inlineStr">
+        <is>
+          <t>Jannec Sa</t>
+        </is>
+      </c>
+      <c r="C395" s="2" t="inlineStr">
+        <is>
+          <t>39125</t>
+        </is>
+      </c>
+      <c r="D395" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E395" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Aigaleo</t>
+        </is>
+      </c>
+      <c r="F395" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G395" s="2" t="inlineStr">
+        <is>
+          <t>Emmanuel Pappas 3</t>
+        </is>
+      </c>
+      <c r="H395" s="2" t="inlineStr">
+        <is>
+          <t>122 42</t>
+        </is>
+      </c>
+      <c r="I395" s="2" t="inlineStr">
+        <is>
+          <t>https://jannec.gr</t>
+        </is>
+      </c>
+      <c r="J395" s="2" t="inlineStr"/>
+      <c r="K395" s="2" t="inlineStr"/>
+      <c r="L395" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M395" s="2" t="inlineStr"/>
+      <c r="N395" s="2" t="inlineStr">
+        <is>
+          <t>contact@jannec.gr</t>
+        </is>
+      </c>
+      <c r="O395" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0495 4874</t>
+        </is>
+      </c>
+      <c r="P395" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q395" s="2" t="inlineStr">
+        <is>
+          <t>999514226</t>
+        </is>
+      </c>
+      <c r="R395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jannec-sa-gr/</t>
+        </is>
+      </c>
+      <c r="S395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61553865101850</t>
+        </is>
+      </c>
+      <c r="T395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jannecgr/</t>
+        </is>
+      </c>
+      <c r="U395" s="2" t="inlineStr"/>
+      <c r="V395" s="2" t="inlineStr"/>
+      <c r="W395" s="2" t="inlineStr">
+        <is>
+          <t>Elina Abatzoglou</t>
+        </is>
+      </c>
+      <c r="X395" s="2" t="inlineStr">
+        <is>
+          <t>Executive Assistant</t>
+        </is>
+      </c>
+      <c r="Y395" s="2" t="inlineStr"/>
+      <c r="Z395" s="2" t="inlineStr"/>
+      <c r="AA395" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/elina-abatzoglou-7b1a0693/</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="2" t="inlineStr">
+        <is>
+          <t>Jannec Sa</t>
+        </is>
+      </c>
+      <c r="B396" s="2" t="inlineStr">
+        <is>
+          <t>Jannec Sa</t>
+        </is>
+      </c>
+      <c r="C396" s="2" t="inlineStr">
+        <is>
+          <t>39125</t>
+        </is>
+      </c>
+      <c r="D396" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E396" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Aigaleo</t>
+        </is>
+      </c>
+      <c r="F396" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G396" s="2" t="inlineStr">
+        <is>
+          <t>Emmanuel Pappas 3</t>
+        </is>
+      </c>
+      <c r="H396" s="2" t="inlineStr">
+        <is>
+          <t>122 42</t>
+        </is>
+      </c>
+      <c r="I396" s="2" t="inlineStr">
+        <is>
+          <t>https://jannec.gr</t>
+        </is>
+      </c>
+      <c r="J396" s="2" t="inlineStr"/>
+      <c r="K396" s="2" t="inlineStr"/>
+      <c r="L396" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M396" s="2" t="inlineStr"/>
+      <c r="N396" s="2" t="inlineStr">
+        <is>
+          <t>contact@jannec.gr</t>
+        </is>
+      </c>
+      <c r="O396" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0495 4874</t>
+        </is>
+      </c>
+      <c r="P396" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q396" s="2" t="inlineStr">
+        <is>
+          <t>999514226</t>
+        </is>
+      </c>
+      <c r="R396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jannec-sa-gr/</t>
+        </is>
+      </c>
+      <c r="S396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61553865101850</t>
+        </is>
+      </c>
+      <c r="T396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jannecgr/</t>
+        </is>
+      </c>
+      <c r="U396" s="2" t="inlineStr"/>
+      <c r="V396" s="2" t="inlineStr"/>
+      <c r="W396" s="2" t="inlineStr">
+        <is>
+          <t>Panagiotis Boutzounis</t>
+        </is>
+      </c>
+      <c r="X396" s="2" t="inlineStr">
+        <is>
+          <t>Sales And Purchasing Import Manager</t>
+        </is>
+      </c>
+      <c r="Y396" s="2" t="inlineStr"/>
+      <c r="Z396" s="2" t="inlineStr"/>
+      <c r="AA396" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/panagiotis-boutzounis-3157a9159</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="2" t="inlineStr">
+        <is>
+          <t>Jannec Sa</t>
+        </is>
+      </c>
+      <c r="B397" s="2" t="inlineStr">
+        <is>
+          <t>Jannec Sa</t>
+        </is>
+      </c>
+      <c r="C397" s="2" t="inlineStr">
+        <is>
+          <t>39125</t>
+        </is>
+      </c>
+      <c r="D397" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E397" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Aigaleo</t>
+        </is>
+      </c>
+      <c r="F397" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G397" s="2" t="inlineStr">
+        <is>
+          <t>Emmanuel Pappas 3</t>
+        </is>
+      </c>
+      <c r="H397" s="2" t="inlineStr">
+        <is>
+          <t>122 42</t>
+        </is>
+      </c>
+      <c r="I397" s="2" t="inlineStr">
+        <is>
+          <t>https://jannec.gr</t>
+        </is>
+      </c>
+      <c r="J397" s="2" t="inlineStr"/>
+      <c r="K397" s="2" t="inlineStr"/>
+      <c r="L397" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M397" s="2" t="inlineStr"/>
+      <c r="N397" s="2" t="inlineStr">
+        <is>
+          <t>contact@jannec.gr</t>
+        </is>
+      </c>
+      <c r="O397" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0495 4874</t>
+        </is>
+      </c>
+      <c r="P397" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q397" s="2" t="inlineStr">
+        <is>
+          <t>999514226</t>
+        </is>
+      </c>
+      <c r="R397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jannec-sa-gr/</t>
+        </is>
+      </c>
+      <c r="S397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61553865101850</t>
+        </is>
+      </c>
+      <c r="T397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jannecgr/</t>
+        </is>
+      </c>
+      <c r="U397" s="2" t="inlineStr"/>
+      <c r="V397" s="2" t="inlineStr"/>
+      <c r="W397" s="2" t="inlineStr">
+        <is>
+          <t>Ilias Theologis</t>
+        </is>
+      </c>
+      <c r="X397" s="2" t="inlineStr">
+        <is>
+          <t>Sales Executive</t>
+        </is>
+      </c>
+      <c r="Y397" s="2" t="inlineStr"/>
+      <c r="Z397" s="2" t="inlineStr"/>
+      <c r="AA397" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ilias-theologis-9511831b9/</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>Jannec Sa</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>Jannec Sa</t>
+        </is>
+      </c>
+      <c r="C398" s="2" t="inlineStr">
+        <is>
+          <t>39125</t>
+        </is>
+      </c>
+      <c r="D398" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E398" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Aigaleo</t>
+        </is>
+      </c>
+      <c r="F398" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G398" s="2" t="inlineStr">
+        <is>
+          <t>Emmanuel Pappas 3</t>
+        </is>
+      </c>
+      <c r="H398" s="2" t="inlineStr">
+        <is>
+          <t>122 42</t>
+        </is>
+      </c>
+      <c r="I398" s="2" t="inlineStr">
+        <is>
+          <t>https://jannec.gr</t>
+        </is>
+      </c>
+      <c r="J398" s="2" t="inlineStr"/>
+      <c r="K398" s="2" t="inlineStr"/>
+      <c r="L398" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M398" s="2" t="inlineStr"/>
+      <c r="N398" s="2" t="inlineStr">
+        <is>
+          <t>contact@jannec.gr</t>
+        </is>
+      </c>
+      <c r="O398" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0495 4874</t>
+        </is>
+      </c>
+      <c r="P398" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q398" s="2" t="inlineStr">
+        <is>
+          <t>999514226</t>
+        </is>
+      </c>
+      <c r="R398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jannec-sa-gr/</t>
+        </is>
+      </c>
+      <c r="S398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61553865101850</t>
+        </is>
+      </c>
+      <c r="T398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jannecgr/</t>
+        </is>
+      </c>
+      <c r="U398" s="2" t="inlineStr"/>
+      <c r="V398" s="2" t="inlineStr"/>
+      <c r="W398" s="2" t="inlineStr">
+        <is>
+          <t>Eleftheria Vartholomaiou</t>
+        </is>
+      </c>
+      <c r="X398" s="2" t="inlineStr">
+        <is>
+          <t>Sales Representative</t>
+        </is>
+      </c>
+      <c r="Y398" s="2" t="inlineStr"/>
+      <c r="Z398" s="2" t="inlineStr"/>
+      <c r="AA398" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eleftheria-vartholomaiou-64a05914a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" s="2" t="inlineStr">
+        <is>
+          <t>Jannec Sa</t>
+        </is>
+      </c>
+      <c r="B399" s="2" t="inlineStr">
+        <is>
+          <t>Jannec Sa</t>
+        </is>
+      </c>
+      <c r="C399" s="2" t="inlineStr">
+        <is>
+          <t>39125</t>
+        </is>
+      </c>
+      <c r="D399" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E399" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Aigaleo</t>
+        </is>
+      </c>
+      <c r="F399" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G399" s="2" t="inlineStr">
+        <is>
+          <t>Emmanuel Pappas 3</t>
+        </is>
+      </c>
+      <c r="H399" s="2" t="inlineStr">
+        <is>
+          <t>122 42</t>
+        </is>
+      </c>
+      <c r="I399" s="2" t="inlineStr">
+        <is>
+          <t>https://jannec.gr</t>
+        </is>
+      </c>
+      <c r="J399" s="2" t="inlineStr"/>
+      <c r="K399" s="2" t="inlineStr"/>
+      <c r="L399" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M399" s="2" t="inlineStr"/>
+      <c r="N399" s="2" t="inlineStr">
+        <is>
+          <t>contact@jannec.gr</t>
+        </is>
+      </c>
+      <c r="O399" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0495 4874</t>
+        </is>
+      </c>
+      <c r="P399" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q399" s="2" t="inlineStr">
+        <is>
+          <t>999514226</t>
+        </is>
+      </c>
+      <c r="R399" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jannec-sa-gr/</t>
+        </is>
+      </c>
+      <c r="S399" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61553865101850</t>
+        </is>
+      </c>
+      <c r="T399" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jannecgr/</t>
+        </is>
+      </c>
+      <c r="U399" s="2" t="inlineStr"/>
+      <c r="V399" s="2" t="inlineStr"/>
+      <c r="W399" s="2" t="inlineStr">
+        <is>
+          <t>Pantelis Nezis</t>
+        </is>
+      </c>
+      <c r="X399" s="2" t="inlineStr">
+        <is>
+          <t>Sales Specialist</t>
+        </is>
+      </c>
+      <c r="Y399" s="2" t="inlineStr"/>
+      <c r="Z399" s="2" t="inlineStr"/>
+      <c r="AA399" s="2" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" s="2" t="inlineStr">
+        <is>
+          <t>Jannec Sa</t>
+        </is>
+      </c>
+      <c r="B400" s="2" t="inlineStr">
+        <is>
+          <t>Jannec Sa</t>
+        </is>
+      </c>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>39125</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Aigaleo</t>
+        </is>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G400" s="2" t="inlineStr">
+        <is>
+          <t>Emmanuel Pappas 3</t>
+        </is>
+      </c>
+      <c r="H400" s="2" t="inlineStr">
+        <is>
+          <t>122 42</t>
+        </is>
+      </c>
+      <c r="I400" s="2" t="inlineStr">
+        <is>
+          <t>https://jannec.gr</t>
+        </is>
+      </c>
+      <c r="J400" s="2" t="inlineStr"/>
+      <c r="K400" s="2" t="inlineStr"/>
+      <c r="L400" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M400" s="2" t="inlineStr"/>
+      <c r="N400" s="2" t="inlineStr">
+        <is>
+          <t>contact@jannec.gr</t>
+        </is>
+      </c>
+      <c r="O400" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0495 4874</t>
+        </is>
+      </c>
+      <c r="P400" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q400" s="2" t="inlineStr">
+        <is>
+          <t>999514226</t>
+        </is>
+      </c>
+      <c r="R400" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jannec-sa-gr/</t>
+        </is>
+      </c>
+      <c r="S400" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61553865101850</t>
+        </is>
+      </c>
+      <c r="T400" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jannecgr/</t>
+        </is>
+      </c>
+      <c r="U400" s="2" t="inlineStr"/>
+      <c r="V400" s="2" t="inlineStr"/>
+      <c r="W400" s="2" t="inlineStr">
+        <is>
+          <t>Leonidas Kotsalis</t>
+        </is>
+      </c>
+      <c r="X400" s="2" t="inlineStr">
+        <is>
+          <t>Sales Supervisor Traditional Trade</t>
+        </is>
+      </c>
+      <c r="Y400" s="2" t="inlineStr"/>
+      <c r="Z400" s="2" t="inlineStr"/>
+      <c r="AA400" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/leonidas-kotsalis/</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" s="2" t="inlineStr">
+        <is>
+          <t>Jannec Sa</t>
+        </is>
+      </c>
+      <c r="B401" s="2" t="inlineStr">
+        <is>
+          <t>Jannec Sa</t>
+        </is>
+      </c>
+      <c r="C401" s="2" t="inlineStr">
+        <is>
+          <t>39125</t>
+        </is>
+      </c>
+      <c r="D401" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E401" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Aigaleo</t>
+        </is>
+      </c>
+      <c r="F401" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G401" s="2" t="inlineStr">
+        <is>
+          <t>Emmanuel Pappas 3</t>
+        </is>
+      </c>
+      <c r="H401" s="2" t="inlineStr">
+        <is>
+          <t>122 42</t>
+        </is>
+      </c>
+      <c r="I401" s="2" t="inlineStr">
+        <is>
+          <t>https://jannec.gr</t>
+        </is>
+      </c>
+      <c r="J401" s="2" t="inlineStr"/>
+      <c r="K401" s="2" t="inlineStr"/>
+      <c r="L401" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M401" s="2" t="inlineStr"/>
+      <c r="N401" s="2" t="inlineStr">
+        <is>
+          <t>contact@jannec.gr</t>
+        </is>
+      </c>
+      <c r="O401" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0495 4874</t>
+        </is>
+      </c>
+      <c r="P401" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q401" s="2" t="inlineStr">
+        <is>
+          <t>999514226</t>
+        </is>
+      </c>
+      <c r="R401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jannec-sa-gr/</t>
+        </is>
+      </c>
+      <c r="S401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61553865101850</t>
+        </is>
+      </c>
+      <c r="T401" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jannecgr/</t>
+        </is>
+      </c>
+      <c r="U401" s="2" t="inlineStr"/>
+      <c r="V401" s="2" t="inlineStr"/>
+      <c r="W401" s="2" t="inlineStr">
+        <is>
+          <t>Aliki Pavlidou</t>
+        </is>
+      </c>
+      <c r="X401" s="2" t="inlineStr">
+        <is>
+          <t>Wholesale Manager</t>
+        </is>
+      </c>
+      <c r="Y401" s="2" t="inlineStr"/>
+      <c r="Z401" s="2" t="inlineStr"/>
+      <c r="AA401" s="2" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" s="2" t="inlineStr">
+        <is>
+          <t>Jannec Sa</t>
+        </is>
+      </c>
+      <c r="B402" s="2" t="inlineStr">
+        <is>
+          <t>Jannec Sa</t>
+        </is>
+      </c>
+      <c r="C402" s="2" t="inlineStr">
+        <is>
+          <t>39125</t>
+        </is>
+      </c>
+      <c r="D402" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E402" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Aigaleo</t>
+        </is>
+      </c>
+      <c r="F402" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G402" s="2" t="inlineStr">
+        <is>
+          <t>Emmanuel Pappas 3</t>
+        </is>
+      </c>
+      <c r="H402" s="2" t="inlineStr">
+        <is>
+          <t>122 42</t>
+        </is>
+      </c>
+      <c r="I402" s="2" t="inlineStr">
+        <is>
+          <t>https://jannec.gr</t>
+        </is>
+      </c>
+      <c r="J402" s="2" t="inlineStr"/>
+      <c r="K402" s="2" t="inlineStr"/>
+      <c r="L402" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M402" s="2" t="inlineStr"/>
+      <c r="N402" s="2" t="inlineStr">
+        <is>
+          <t>contact@jannec.gr</t>
+        </is>
+      </c>
+      <c r="O402" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0495 4874</t>
+        </is>
+      </c>
+      <c r="P402" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q402" s="2" t="inlineStr">
+        <is>
+          <t>999514226</t>
+        </is>
+      </c>
+      <c r="R402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/jannec-sa-gr/</t>
+        </is>
+      </c>
+      <c r="S402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61553865101850</t>
+        </is>
+      </c>
+      <c r="T402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/jannecgr/</t>
+        </is>
+      </c>
+      <c r="U402" s="2" t="inlineStr"/>
+      <c r="V402" s="2" t="inlineStr"/>
+      <c r="W402" s="2" t="inlineStr">
+        <is>
+          <t>Dimitra Poulopoulou</t>
+        </is>
+      </c>
+      <c r="X402" s="2" t="inlineStr">
+        <is>
+          <t>Import/ Export Department</t>
+        </is>
+      </c>
+      <c r="Y402" s="2" t="inlineStr"/>
+      <c r="Z402" s="2" t="inlineStr"/>
+      <c r="AA402" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dimitra-poulopoulou-964131298/</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" s="2" t="inlineStr">
+        <is>
+          <t>Cava Drosia Store Georgilakis O.e.</t>
+        </is>
+      </c>
+      <c r="B403" s="2" t="inlineStr">
+        <is>
+          <t>Cava Drosia Store Georgilakis O.e.</t>
+        </is>
+      </c>
+      <c r="C403" s="2" t="inlineStr">
+        <is>
+          <t>49957</t>
+        </is>
+      </c>
+      <c r="D403" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E403" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Dionysos</t>
+        </is>
+      </c>
+      <c r="F403" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G403" s="2" t="inlineStr">
+        <is>
+          <t>3 Leoforos Drosias Stamatas</t>
+        </is>
+      </c>
+      <c r="H403" s="2" t="inlineStr">
+        <is>
+          <t>145 75</t>
+        </is>
+      </c>
+      <c r="I403" s="2" t="inlineStr">
+        <is>
+          <t>https://cavadrosia.gr</t>
+        </is>
+      </c>
+      <c r="J403" s="2" t="inlineStr"/>
+      <c r="K403" s="2" t="inlineStr"/>
+      <c r="L403" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M403" s="2" t="inlineStr"/>
+      <c r="N403" s="2" t="inlineStr">
+        <is>
+          <t>sales@cavadrosia.gr</t>
+        </is>
+      </c>
+      <c r="O403" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0814 2947</t>
+        </is>
+      </c>
+      <c r="P403" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q403" s="2" t="inlineStr">
+        <is>
+          <t>801457189</t>
+        </is>
+      </c>
+      <c r="R403" s="2" t="inlineStr"/>
+      <c r="S403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cavadrosia/</t>
+        </is>
+      </c>
+      <c r="T403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cavadrosia/</t>
+        </is>
+      </c>
+      <c r="U403" s="2" t="inlineStr"/>
+      <c r="V403" s="2" t="inlineStr"/>
+      <c r="W403" s="2" t="inlineStr">
+        <is>
+          <t>Kostis Perakis</t>
+        </is>
+      </c>
+      <c r="X403" s="2" t="inlineStr">
+        <is>
+          <t>Purchasing Manager</t>
+        </is>
+      </c>
+      <c r="Y403" s="2" t="inlineStr"/>
+      <c r="Z403" s="2" t="inlineStr"/>
+      <c r="AA403" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/kostis-perakis-9b70542a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" s="2" t="inlineStr">
+        <is>
+          <t>Cava Drosia Store Georgilakis O.e.</t>
+        </is>
+      </c>
+      <c r="B404" s="2" t="inlineStr">
+        <is>
+          <t>Cava Drosia Store Georgilakis O.e.</t>
+        </is>
+      </c>
+      <c r="C404" s="2" t="inlineStr">
+        <is>
+          <t>49957</t>
+        </is>
+      </c>
+      <c r="D404" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E404" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Dionysos</t>
+        </is>
+      </c>
+      <c r="F404" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G404" s="2" t="inlineStr">
+        <is>
+          <t>3 Leoforos Drosias Stamatas</t>
+        </is>
+      </c>
+      <c r="H404" s="2" t="inlineStr">
+        <is>
+          <t>145 75</t>
+        </is>
+      </c>
+      <c r="I404" s="2" t="inlineStr">
+        <is>
+          <t>https://cavadrosia.gr</t>
+        </is>
+      </c>
+      <c r="J404" s="2" t="inlineStr"/>
+      <c r="K404" s="2" t="inlineStr"/>
+      <c r="L404" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M404" s="2" t="inlineStr"/>
+      <c r="N404" s="2" t="inlineStr">
+        <is>
+          <t>sales@cavadrosia.gr</t>
+        </is>
+      </c>
+      <c r="O404" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0814 2947</t>
+        </is>
+      </c>
+      <c r="P404" s="2" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="Q404" s="2" t="inlineStr">
+        <is>
+          <t>801457189</t>
+        </is>
+      </c>
+      <c r="R404" s="2" t="inlineStr"/>
+      <c r="S404" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cavadrosia/</t>
+        </is>
+      </c>
+      <c r="T404" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cavadrosia/</t>
+        </is>
+      </c>
+      <c r="U404" s="2" t="inlineStr"/>
+      <c r="V404" s="2" t="inlineStr"/>
+      <c r="W404" s="2" t="inlineStr">
+        <is>
+          <t>Konstantinos Kastrinos</t>
+        </is>
+      </c>
+      <c r="X404" s="2" t="inlineStr">
+        <is>
+          <t>Sales Department</t>
+        </is>
+      </c>
+      <c r="Y404" s="2" t="inlineStr"/>
+      <c r="Z404" s="2" t="inlineStr"/>
+      <c r="AA404" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/konstantinos-kastrinos-9360262b5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="2" t="inlineStr">
+        <is>
+          <t>Boutzounis Wine &amp; Spirits</t>
+        </is>
+      </c>
+      <c r="B405" s="2" t="inlineStr">
+        <is>
+          <t>Boutzounis Wine &amp; Spirits</t>
+        </is>
+      </c>
+      <c r="C405" s="2" t="inlineStr">
+        <is>
+          <t>35614</t>
+        </is>
+      </c>
+      <c r="D405" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E405" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Dionysos</t>
+        </is>
+      </c>
+      <c r="F405" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G405" s="2" t="inlineStr">
+        <is>
+          <t>53 Leoforos Trapezountos</t>
+        </is>
+      </c>
+      <c r="H405" s="2" t="inlineStr">
+        <is>
+          <t>145 65</t>
+        </is>
+      </c>
+      <c r="I405" s="2" t="inlineStr">
+        <is>
+          <t>https://boutzounis.gr</t>
+        </is>
+      </c>
+      <c r="J405" s="2" t="inlineStr"/>
+      <c r="K405" s="2" t="inlineStr"/>
+      <c r="L405" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M405" s="2" t="inlineStr"/>
+      <c r="N405" s="2" t="inlineStr">
+        <is>
+          <t>info@boutzounis.gr</t>
+        </is>
+      </c>
+      <c r="O405" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0490 3085</t>
+        </is>
+      </c>
+      <c r="P405" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q405" s="2" t="inlineStr">
+        <is>
+          <t>999515905</t>
+        </is>
+      </c>
+      <c r="R405" s="2" t="inlineStr"/>
+      <c r="S405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/boutzouniswines/</t>
+        </is>
+      </c>
+      <c r="T405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boutzounis_wines/</t>
+        </is>
+      </c>
+      <c r="U405" s="2" t="inlineStr"/>
+      <c r="V405" s="2" t="inlineStr"/>
+      <c r="W405" s="2" t="inlineStr">
+        <is>
+          <t>Aggelos Antoniou</t>
+        </is>
+      </c>
+      <c r="X405" s="2" t="inlineStr">
+        <is>
+          <t>Wine Consultant</t>
+        </is>
+      </c>
+      <c r="Y405" s="2" t="inlineStr"/>
+      <c r="Z405" s="2" t="inlineStr"/>
+      <c r="AA405" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/aggelos-antoniou-1908971a4/?originalSubdomain=gr</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" s="2" t="inlineStr">
+        <is>
+          <t>Boutzounis Wine &amp; Spirits</t>
+        </is>
+      </c>
+      <c r="B406" s="2" t="inlineStr">
+        <is>
+          <t>Boutzounis Wine &amp; Spirits</t>
+        </is>
+      </c>
+      <c r="C406" s="2" t="inlineStr">
+        <is>
+          <t>35614</t>
+        </is>
+      </c>
+      <c r="D406" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E406" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Dionysos</t>
+        </is>
+      </c>
+      <c r="F406" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G406" s="2" t="inlineStr">
+        <is>
+          <t>53 Leoforos Trapezountos</t>
+        </is>
+      </c>
+      <c r="H406" s="2" t="inlineStr">
+        <is>
+          <t>145 65</t>
+        </is>
+      </c>
+      <c r="I406" s="2" t="inlineStr">
+        <is>
+          <t>https://boutzounis.gr</t>
+        </is>
+      </c>
+      <c r="J406" s="2" t="inlineStr"/>
+      <c r="K406" s="2" t="inlineStr"/>
+      <c r="L406" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M406" s="2" t="inlineStr"/>
+      <c r="N406" s="2" t="inlineStr">
+        <is>
+          <t>info@boutzounis.gr</t>
+        </is>
+      </c>
+      <c r="O406" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0490 3085</t>
+        </is>
+      </c>
+      <c r="P406" s="2" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="Q406" s="2" t="inlineStr">
+        <is>
+          <t>999515905</t>
+        </is>
+      </c>
+      <c r="R406" s="2" t="inlineStr"/>
+      <c r="S406" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/boutzouniswines/</t>
+        </is>
+      </c>
+      <c r="T406" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/boutzounis_wines/</t>
+        </is>
+      </c>
+      <c r="U406" s="2" t="inlineStr"/>
+      <c r="V406" s="2" t="inlineStr"/>
+      <c r="W406" s="2" t="inlineStr">
+        <is>
+          <t>Maria Boutzouni</t>
+        </is>
+      </c>
+      <c r="X406" s="2" t="inlineStr">
+        <is>
+          <t>Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y406" s="2" t="inlineStr"/>
+      <c r="Z406" s="2" t="inlineStr"/>
+      <c r="AA406" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maria-boutzouni-6a095a5b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="2" t="inlineStr">
+        <is>
+          <t>Kirykos, G., &amp; Co. O.e.</t>
+        </is>
+      </c>
+      <c r="B407" s="2" t="inlineStr">
+        <is>
+          <t>Kirykos, G., &amp; Co. O.e.</t>
+        </is>
+      </c>
+      <c r="C407" s="2" t="inlineStr">
+        <is>
+          <t>24645</t>
+        </is>
+      </c>
+      <c r="D407" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E407" s="2" t="inlineStr">
+        <is>
+          <t>Athens</t>
+        </is>
+      </c>
+      <c r="F407" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G407" s="2" t="inlineStr">
+        <is>
+          <t>10 Stadiou</t>
+        </is>
+      </c>
+      <c r="H407" s="2" t="inlineStr">
+        <is>
+          <t>105 62</t>
+        </is>
+      </c>
+      <c r="I407" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gkirikos.gr</t>
+        </is>
+      </c>
+      <c r="J407" s="2" t="inlineStr"/>
+      <c r="K407" s="2" t="inlineStr"/>
+      <c r="L407" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M407" s="2" t="inlineStr"/>
+      <c r="N407" s="2" t="inlineStr">
+        <is>
+          <t>info@gkirikos.gr</t>
+        </is>
+      </c>
+      <c r="O407" s="2" t="inlineStr">
+        <is>
+          <t>+30 2221 030697</t>
+        </is>
+      </c>
+      <c r="P407" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="Q407" s="2" t="inlineStr">
+        <is>
+          <t>084152282</t>
+        </is>
+      </c>
+      <c r="R407" s="2" t="inlineStr"/>
+      <c r="S407" s="2" t="inlineStr"/>
+      <c r="T407" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gkirikos</t>
+        </is>
+      </c>
+      <c r="U407" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/gkirikos</t>
+        </is>
+      </c>
+      <c r="V407" s="2" t="inlineStr"/>
+      <c r="W407" s="2" t="inlineStr"/>
+      <c r="X407" s="2" t="inlineStr"/>
+      <c r="Y407" s="2" t="inlineStr"/>
+      <c r="Z407" s="2" t="inlineStr"/>
+      <c r="AA407" s="2" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" s="2" t="inlineStr">
+        <is>
+          <t>Anogiannakis Bros O.e. Kriti</t>
+        </is>
+      </c>
+      <c r="B408" s="2" t="inlineStr">
+        <is>
+          <t>Anogiannakis Bros O.e. Kriti</t>
+        </is>
+      </c>
+      <c r="C408" s="2" t="inlineStr">
+        <is>
+          <t>49446</t>
+        </is>
+      </c>
+      <c r="D408" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E408" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Marousi</t>
+        </is>
+      </c>
+      <c r="F408" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G408" s="2" t="inlineStr">
+        <is>
+          <t>29 Mitilinis</t>
+        </is>
+      </c>
+      <c r="H408" s="2" t="inlineStr">
+        <is>
+          <t>151 26</t>
+        </is>
+      </c>
+      <c r="I408" s="2" t="inlineStr">
+        <is>
+          <t>https://cavanogiannaki.gr</t>
+        </is>
+      </c>
+      <c r="J408" s="2" t="inlineStr"/>
+      <c r="K408" s="2" t="inlineStr"/>
+      <c r="L408" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M408" s="2" t="inlineStr"/>
+      <c r="N408" s="2" t="inlineStr">
+        <is>
+          <t>info@cava-anogiannaki.gr</t>
+        </is>
+      </c>
+      <c r="O408" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0804 7187</t>
+        </is>
+      </c>
+      <c r="P408" s="2" t="inlineStr">
+        <is>
+          <t>1988</t>
+        </is>
+      </c>
+      <c r="Q408" s="2" t="inlineStr">
+        <is>
+          <t>082894767</t>
+        </is>
+      </c>
+      <c r="R408" s="2" t="inlineStr"/>
+      <c r="S408" s="2" t="inlineStr"/>
+      <c r="T408" s="2" t="inlineStr"/>
+      <c r="U408" s="2" t="inlineStr"/>
+      <c r="V408" s="2" t="inlineStr"/>
+      <c r="W408" s="2" t="inlineStr">
+        <is>
+          <t>Stefanos Anogiannakis</t>
+        </is>
+      </c>
+      <c r="X408" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner</t>
+        </is>
+      </c>
+      <c r="Y408" s="2" t="inlineStr"/>
+      <c r="Z408" s="2" t="inlineStr"/>
+      <c r="AA408" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stefanos-anogiannakis-960264145/</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>Bakaliko Crete</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>Bakaliko Crete</t>
+        </is>
+      </c>
+      <c r="C409" s="2" t="inlineStr">
+        <is>
+          <t>27257</t>
+        </is>
+      </c>
+      <c r="D409" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E409" s="2" t="inlineStr">
+        <is>
+          <t>Spata-Loutsa Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F409" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G409" s="2" t="inlineStr">
+        <is>
+          <t>Attiki Odos</t>
+        </is>
+      </c>
+      <c r="H409" s="2" t="inlineStr">
+        <is>
+          <t>190 04</t>
+        </is>
+      </c>
+      <c r="I409" s="2" t="inlineStr">
+        <is>
+          <t>https://webshop.bakalikocrete.com, https://www.bakalikocrete.com</t>
+        </is>
+      </c>
+      <c r="J409" s="2" t="inlineStr"/>
+      <c r="K409" s="2" t="inlineStr"/>
+      <c r="L409" s="2" t="inlineStr"/>
+      <c r="M409" s="2" t="inlineStr"/>
+      <c r="N409" s="2" t="inlineStr">
+        <is>
+          <t>info@bakalikocrete.com</t>
+        </is>
+      </c>
+      <c r="O409" s="2" t="inlineStr">
+        <is>
+          <t>+30 281 075 1117</t>
+        </is>
+      </c>
+      <c r="P409" s="2" t="inlineStr"/>
+      <c r="Q409" s="2" t="inlineStr"/>
+      <c r="R409" s="2" t="inlineStr"/>
+      <c r="S409" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bakalikocrete/</t>
+        </is>
+      </c>
+      <c r="T409" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bakalikomilos/</t>
+        </is>
+      </c>
+      <c r="U409" s="2" t="inlineStr"/>
+      <c r="V409" s="2" t="inlineStr"/>
+      <c r="W409" s="2" t="inlineStr">
+        <is>
+          <t>Agnes Weninger</t>
+        </is>
+      </c>
+      <c r="X409" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner</t>
+        </is>
+      </c>
+      <c r="Y409" s="2" t="inlineStr"/>
+      <c r="Z409" s="2" t="inlineStr"/>
+      <c r="AA409" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/agnes-weninger-a5189422/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Greece.xlsx
+++ b/BWI/bestwine_output/bestwine_Greece.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA409"/>
+  <dimension ref="A1:AA419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -44197,6 +44197,984 @@
         </is>
       </c>
     </row>
+    <row r="410">
+      <c r="A410" s="2" t="inlineStr">
+        <is>
+          <t>Unibräu Hellas</t>
+        </is>
+      </c>
+      <c r="B410" s="2" t="inlineStr">
+        <is>
+          <t>Unibräu Hellas</t>
+        </is>
+      </c>
+      <c r="C410" s="2" t="inlineStr">
+        <is>
+          <t>25424</t>
+        </is>
+      </c>
+      <c r="D410" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E410" s="2" t="inlineStr">
+        <is>
+          <t>Spata-Loutsa Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F410" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G410" s="2" t="inlineStr">
+        <is>
+          <t>29 Agiou Dimitriou</t>
+        </is>
+      </c>
+      <c r="H410" s="2" t="inlineStr">
+        <is>
+          <t>190 04</t>
+        </is>
+      </c>
+      <c r="I410" s="2" t="inlineStr">
+        <is>
+          <t>https://www.unibrau.gr</t>
+        </is>
+      </c>
+      <c r="J410" s="2" t="inlineStr"/>
+      <c r="K410" s="2" t="inlineStr"/>
+      <c r="L410" s="2" t="inlineStr"/>
+      <c r="M410" s="2" t="inlineStr"/>
+      <c r="N410" s="2" t="inlineStr">
+        <is>
+          <t>info@unibrau.gr</t>
+        </is>
+      </c>
+      <c r="O410" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0665 4062</t>
+        </is>
+      </c>
+      <c r="P410" s="2" t="inlineStr"/>
+      <c r="Q410" s="2" t="inlineStr"/>
+      <c r="R410" s="2" t="inlineStr"/>
+      <c r="S410" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/unibrau.hellas/</t>
+        </is>
+      </c>
+      <c r="T410" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/unibrau.gr/</t>
+        </is>
+      </c>
+      <c r="U410" s="2" t="inlineStr"/>
+      <c r="V410" s="2" t="inlineStr"/>
+      <c r="W410" s="2" t="inlineStr"/>
+      <c r="X410" s="2" t="inlineStr"/>
+      <c r="Y410" s="2" t="inlineStr"/>
+      <c r="Z410" s="2" t="inlineStr"/>
+      <c r="AA410" s="2" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" s="2" t="inlineStr">
+        <is>
+          <t>Hebe Argentinian Wineology</t>
+        </is>
+      </c>
+      <c r="B411" s="2" t="inlineStr">
+        <is>
+          <t>Hebe Argentinian Wineology</t>
+        </is>
+      </c>
+      <c r="C411" s="2" t="inlineStr">
+        <is>
+          <t>27842</t>
+        </is>
+      </c>
+      <c r="D411" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E411" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Nea Smyrni</t>
+        </is>
+      </c>
+      <c r="F411" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G411" s="2" t="inlineStr">
+        <is>
+          <t>29 Adramittiou</t>
+        </is>
+      </c>
+      <c r="H411" s="2" t="inlineStr">
+        <is>
+          <t>171 21</t>
+        </is>
+      </c>
+      <c r="I411" s="2" t="inlineStr">
+        <is>
+          <t>http://hebewines.com</t>
+        </is>
+      </c>
+      <c r="J411" s="2" t="inlineStr"/>
+      <c r="K411" s="2" t="inlineStr"/>
+      <c r="L411" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M411" s="2" t="inlineStr"/>
+      <c r="N411" s="2" t="inlineStr">
+        <is>
+          <t>info@hebewines.com</t>
+        </is>
+      </c>
+      <c r="O411" s="2" t="inlineStr"/>
+      <c r="P411" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q411" s="2" t="inlineStr">
+        <is>
+          <t>998468164</t>
+        </is>
+      </c>
+      <c r="R411" s="2" t="inlineStr"/>
+      <c r="S411" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hebewines/</t>
+        </is>
+      </c>
+      <c r="T411" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hebe_wines/</t>
+        </is>
+      </c>
+      <c r="U411" s="2" t="inlineStr"/>
+      <c r="V411" s="2" t="inlineStr"/>
+      <c r="W411" s="2" t="inlineStr">
+        <is>
+          <t>Ivana Cecilia</t>
+        </is>
+      </c>
+      <c r="X411" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y411" s="2" t="inlineStr"/>
+      <c r="Z411" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA411" s="2" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" s="2" t="inlineStr">
+        <is>
+          <t>Hebe Argentinian Wineology</t>
+        </is>
+      </c>
+      <c r="B412" s="2" t="inlineStr">
+        <is>
+          <t>Hebe Argentinian Wineology</t>
+        </is>
+      </c>
+      <c r="C412" s="2" t="inlineStr">
+        <is>
+          <t>27842</t>
+        </is>
+      </c>
+      <c r="D412" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E412" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Nea Smyrni</t>
+        </is>
+      </c>
+      <c r="F412" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G412" s="2" t="inlineStr">
+        <is>
+          <t>29 Adramittiou</t>
+        </is>
+      </c>
+      <c r="H412" s="2" t="inlineStr">
+        <is>
+          <t>171 21</t>
+        </is>
+      </c>
+      <c r="I412" s="2" t="inlineStr">
+        <is>
+          <t>http://hebewines.com</t>
+        </is>
+      </c>
+      <c r="J412" s="2" t="inlineStr"/>
+      <c r="K412" s="2" t="inlineStr"/>
+      <c r="L412" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M412" s="2" t="inlineStr"/>
+      <c r="N412" s="2" t="inlineStr">
+        <is>
+          <t>info@hebewines.com</t>
+        </is>
+      </c>
+      <c r="O412" s="2" t="inlineStr"/>
+      <c r="P412" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q412" s="2" t="inlineStr">
+        <is>
+          <t>998468164</t>
+        </is>
+      </c>
+      <c r="R412" s="2" t="inlineStr"/>
+      <c r="S412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hebewines/</t>
+        </is>
+      </c>
+      <c r="T412" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hebe_wines/</t>
+        </is>
+      </c>
+      <c r="U412" s="2" t="inlineStr"/>
+      <c r="V412" s="2" t="inlineStr"/>
+      <c r="W412" s="2" t="inlineStr">
+        <is>
+          <t>Emmanuel Leonardos</t>
+        </is>
+      </c>
+      <c r="X412" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y412" s="2" t="inlineStr"/>
+      <c r="Z412" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA412" s="2" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" s="2" t="inlineStr">
+        <is>
+          <t>Marinos S.a.</t>
+        </is>
+      </c>
+      <c r="B413" s="2" t="inlineStr">
+        <is>
+          <t>Marinos S.a.</t>
+        </is>
+      </c>
+      <c r="C413" s="2" t="inlineStr">
+        <is>
+          <t>7397</t>
+        </is>
+      </c>
+      <c r="D413" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E413" s="2" t="inlineStr">
+        <is>
+          <t>Rhodes</t>
+        </is>
+      </c>
+      <c r="F413" s="2" t="inlineStr">
+        <is>
+          <t>South Aegean</t>
+        </is>
+      </c>
+      <c r="G413" s="2" t="inlineStr">
+        <is>
+          <t>Ermou 23</t>
+        </is>
+      </c>
+      <c r="H413" s="2" t="inlineStr">
+        <is>
+          <t>851 00</t>
+        </is>
+      </c>
+      <c r="I413" s="2" t="inlineStr">
+        <is>
+          <t>http://marinossa.gr</t>
+        </is>
+      </c>
+      <c r="J413" s="2" t="inlineStr"/>
+      <c r="K413" s="2" t="inlineStr"/>
+      <c r="L413" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M413" s="2" t="inlineStr"/>
+      <c r="N413" s="2" t="inlineStr">
+        <is>
+          <t>info@marinossa.gr</t>
+        </is>
+      </c>
+      <c r="O413" s="2" t="inlineStr">
+        <is>
+          <t>+30 2241 077141</t>
+        </is>
+      </c>
+      <c r="P413" s="2" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="Q413" s="2" t="inlineStr">
+        <is>
+          <t>094272005</t>
+        </is>
+      </c>
+      <c r="R413" s="2" t="inlineStr"/>
+      <c r="S413" s="2" t="inlineStr"/>
+      <c r="T413" s="2" t="inlineStr"/>
+      <c r="U413" s="2" t="inlineStr"/>
+      <c r="V413" s="2" t="inlineStr"/>
+      <c r="W413" s="2" t="inlineStr">
+        <is>
+          <t>Theofilos Marinos</t>
+        </is>
+      </c>
+      <c r="X413" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y413" s="2" t="inlineStr"/>
+      <c r="Z413" s="2" t="inlineStr"/>
+      <c r="AA413" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/theofilos-marinos-78296664/</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" s="2" t="inlineStr">
+        <is>
+          <t>Tsianakas Konstantinos Oinodia Sommelier</t>
+        </is>
+      </c>
+      <c r="B414" s="2" t="inlineStr">
+        <is>
+          <t>Tsianakas Konstantinos Oinodia Sommelier</t>
+        </is>
+      </c>
+      <c r="C414" s="2" t="inlineStr">
+        <is>
+          <t>24830</t>
+        </is>
+      </c>
+      <c r="D414" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E414" s="2" t="inlineStr">
+        <is>
+          <t>Municipal Unit of Papagou</t>
+        </is>
+      </c>
+      <c r="F414" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G414" s="2" t="inlineStr">
+        <is>
+          <t>55 Konstantinou Versi</t>
+        </is>
+      </c>
+      <c r="H414" s="2" t="inlineStr">
+        <is>
+          <t>156 69</t>
+        </is>
+      </c>
+      <c r="I414" s="2" t="inlineStr">
+        <is>
+          <t>http://www.oinodia.com</t>
+        </is>
+      </c>
+      <c r="J414" s="2" t="inlineStr"/>
+      <c r="K414" s="2" t="inlineStr"/>
+      <c r="L414" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M414" s="2" t="inlineStr"/>
+      <c r="N414" s="2" t="inlineStr">
+        <is>
+          <t>k.tsianakas@oinodia.com</t>
+        </is>
+      </c>
+      <c r="O414" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0653 5990</t>
+        </is>
+      </c>
+      <c r="P414" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q414" s="2" t="inlineStr">
+        <is>
+          <t>119203168</t>
+        </is>
+      </c>
+      <c r="R414" s="2" t="inlineStr"/>
+      <c r="S414" s="2" t="inlineStr"/>
+      <c r="T414" s="2" t="inlineStr"/>
+      <c r="U414" s="2" t="inlineStr"/>
+      <c r="V414" s="2" t="inlineStr"/>
+      <c r="W414" s="2" t="inlineStr">
+        <is>
+          <t>Konstantine Tsianakas</t>
+        </is>
+      </c>
+      <c r="X414" s="2" t="inlineStr">
+        <is>
+          <t>Sommelier</t>
+        </is>
+      </c>
+      <c r="Y414" s="2" t="inlineStr"/>
+      <c r="Z414" s="2" t="inlineStr"/>
+      <c r="AA414" s="2" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" s="2" t="inlineStr">
+        <is>
+          <t>Tsianakas Konstantinos Oinodia Sommelier</t>
+        </is>
+      </c>
+      <c r="B415" s="2" t="inlineStr">
+        <is>
+          <t>Tsianakas Konstantinos Oinodia Sommelier</t>
+        </is>
+      </c>
+      <c r="C415" s="2" t="inlineStr">
+        <is>
+          <t>24830</t>
+        </is>
+      </c>
+      <c r="D415" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E415" s="2" t="inlineStr">
+        <is>
+          <t>Municipal Unit of Papagou</t>
+        </is>
+      </c>
+      <c r="F415" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G415" s="2" t="inlineStr">
+        <is>
+          <t>55 Konstantinou Versi</t>
+        </is>
+      </c>
+      <c r="H415" s="2" t="inlineStr">
+        <is>
+          <t>156 69</t>
+        </is>
+      </c>
+      <c r="I415" s="2" t="inlineStr">
+        <is>
+          <t>http://www.oinodia.com</t>
+        </is>
+      </c>
+      <c r="J415" s="2" t="inlineStr"/>
+      <c r="K415" s="2" t="inlineStr"/>
+      <c r="L415" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M415" s="2" t="inlineStr"/>
+      <c r="N415" s="2" t="inlineStr">
+        <is>
+          <t>k.tsianakas@oinodia.com</t>
+        </is>
+      </c>
+      <c r="O415" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0653 5990</t>
+        </is>
+      </c>
+      <c r="P415" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q415" s="2" t="inlineStr">
+        <is>
+          <t>119203168</t>
+        </is>
+      </c>
+      <c r="R415" s="2" t="inlineStr"/>
+      <c r="S415" s="2" t="inlineStr"/>
+      <c r="T415" s="2" t="inlineStr"/>
+      <c r="U415" s="2" t="inlineStr"/>
+      <c r="V415" s="2" t="inlineStr"/>
+      <c r="W415" s="2" t="inlineStr">
+        <is>
+          <t>Spyridon Demertzis</t>
+        </is>
+      </c>
+      <c r="X415" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner</t>
+        </is>
+      </c>
+      <c r="Y415" s="2" t="inlineStr"/>
+      <c r="Z415" s="2" t="inlineStr"/>
+      <c r="AA415" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/spyridon-demertzis-b8295b5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" s="2" t="inlineStr">
+        <is>
+          <t>Mavrikos Imports S.a.</t>
+        </is>
+      </c>
+      <c r="B416" s="2" t="inlineStr">
+        <is>
+          <t>Mavrikos Imports S.a.</t>
+        </is>
+      </c>
+      <c r="C416" s="2" t="inlineStr">
+        <is>
+          <t>7398</t>
+        </is>
+      </c>
+      <c r="D416" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E416" s="2" t="inlineStr">
+        <is>
+          <t>Piraeus</t>
+        </is>
+      </c>
+      <c r="F416" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G416" s="2" t="inlineStr">
+        <is>
+          <t>7 Naxou</t>
+        </is>
+      </c>
+      <c r="H416" s="2" t="inlineStr">
+        <is>
+          <t>185 41</t>
+        </is>
+      </c>
+      <c r="I416" s="2" t="inlineStr">
+        <is>
+          <t>https://mavrikosimports.gr</t>
+        </is>
+      </c>
+      <c r="J416" s="2" t="inlineStr"/>
+      <c r="K416" s="2" t="inlineStr"/>
+      <c r="L416" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M416" s="2" t="inlineStr"/>
+      <c r="N416" s="2" t="inlineStr">
+        <is>
+          <t>orddep@mavrikosimports.gr</t>
+        </is>
+      </c>
+      <c r="O416" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0481 3064</t>
+        </is>
+      </c>
+      <c r="P416" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="Q416" s="2" t="inlineStr">
+        <is>
+          <t>094047465</t>
+        </is>
+      </c>
+      <c r="R416" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mavrikos-imports-s-a/</t>
+        </is>
+      </c>
+      <c r="S416" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/mavrikosimports</t>
+        </is>
+      </c>
+      <c r="T416" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/imports_mavrikos</t>
+        </is>
+      </c>
+      <c r="U416" s="2" t="inlineStr"/>
+      <c r="V416" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@mavrikosimports</t>
+        </is>
+      </c>
+      <c r="W416" s="2" t="inlineStr">
+        <is>
+          <t>MARIA MAVRIKOS</t>
+        </is>
+      </c>
+      <c r="X416" s="2" t="inlineStr">
+        <is>
+          <t>Export and import manager</t>
+        </is>
+      </c>
+      <c r="Y416" s="2" t="inlineStr"/>
+      <c r="Z416" s="2" t="inlineStr"/>
+      <c r="AA416" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maria-mavrikos-8943b3395/</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" s="2" t="inlineStr">
+        <is>
+          <t>Foodrinco S.a.</t>
+        </is>
+      </c>
+      <c r="B417" s="2" t="inlineStr">
+        <is>
+          <t>Foodrinco S.a.</t>
+        </is>
+      </c>
+      <c r="C417" s="2" t="inlineStr">
+        <is>
+          <t>22331</t>
+        </is>
+      </c>
+      <c r="D417" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E417" s="2" t="inlineStr">
+        <is>
+          <t>Kryoneri Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F417" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G417" s="2" t="inlineStr">
+        <is>
+          <t>132 Lefkis</t>
+        </is>
+      </c>
+      <c r="H417" s="2" t="inlineStr">
+        <is>
+          <t>145 68</t>
+        </is>
+      </c>
+      <c r="I417" s="2" t="inlineStr">
+        <is>
+          <t>https://foodrinco.gr</t>
+        </is>
+      </c>
+      <c r="J417" s="2" t="inlineStr"/>
+      <c r="K417" s="2" t="inlineStr"/>
+      <c r="L417" s="2" t="inlineStr"/>
+      <c r="M417" s="2" t="inlineStr"/>
+      <c r="N417" s="2" t="inlineStr">
+        <is>
+          <t>info@foodrinco.gr</t>
+        </is>
+      </c>
+      <c r="O417" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 6400 0200</t>
+        </is>
+      </c>
+      <c r="P417" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q417" s="2" t="inlineStr">
+        <is>
+          <t>094430257</t>
+        </is>
+      </c>
+      <c r="R417" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vytogiannis-group-of-companies/</t>
+        </is>
+      </c>
+      <c r="S417" s="2" t="inlineStr"/>
+      <c r="T417" s="2" t="inlineStr"/>
+      <c r="U417" s="2" t="inlineStr"/>
+      <c r="V417" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/foodrinco</t>
+        </is>
+      </c>
+      <c r="W417" s="2" t="inlineStr">
+        <is>
+          <t>George Vitogiannis</t>
+        </is>
+      </c>
+      <c r="X417" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y417" s="2" t="inlineStr"/>
+      <c r="Z417" s="2" t="inlineStr"/>
+      <c r="AA417" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/george-vitogiannis-a041753/</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="2" t="inlineStr">
+        <is>
+          <t>Foodrinco S.a.</t>
+        </is>
+      </c>
+      <c r="B418" s="2" t="inlineStr">
+        <is>
+          <t>Foodrinco S.a.</t>
+        </is>
+      </c>
+      <c r="C418" s="2" t="inlineStr">
+        <is>
+          <t>22331</t>
+        </is>
+      </c>
+      <c r="D418" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E418" s="2" t="inlineStr">
+        <is>
+          <t>Kryoneri Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F418" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G418" s="2" t="inlineStr">
+        <is>
+          <t>132 Lefkis</t>
+        </is>
+      </c>
+      <c r="H418" s="2" t="inlineStr">
+        <is>
+          <t>145 68</t>
+        </is>
+      </c>
+      <c r="I418" s="2" t="inlineStr">
+        <is>
+          <t>https://foodrinco.gr</t>
+        </is>
+      </c>
+      <c r="J418" s="2" t="inlineStr"/>
+      <c r="K418" s="2" t="inlineStr"/>
+      <c r="L418" s="2" t="inlineStr"/>
+      <c r="M418" s="2" t="inlineStr"/>
+      <c r="N418" s="2" t="inlineStr">
+        <is>
+          <t>info@foodrinco.gr</t>
+        </is>
+      </c>
+      <c r="O418" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 6400 0200</t>
+        </is>
+      </c>
+      <c r="P418" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q418" s="2" t="inlineStr">
+        <is>
+          <t>094430257</t>
+        </is>
+      </c>
+      <c r="R418" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vytogiannis-group-of-companies/</t>
+        </is>
+      </c>
+      <c r="S418" s="2" t="inlineStr"/>
+      <c r="T418" s="2" t="inlineStr"/>
+      <c r="U418" s="2" t="inlineStr"/>
+      <c r="V418" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/foodrinco</t>
+        </is>
+      </c>
+      <c r="W418" s="2" t="inlineStr">
+        <is>
+          <t>Stelios Tiktopoulos</t>
+        </is>
+      </c>
+      <c r="X418" s="2" t="inlineStr">
+        <is>
+          <t>Area Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y418" s="2" t="inlineStr"/>
+      <c r="Z418" s="2" t="inlineStr"/>
+      <c r="AA418" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stelios-tiktopoulos-6bb06934/</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="2" t="inlineStr">
+        <is>
+          <t>L. Patroni And Co. E.e.</t>
+        </is>
+      </c>
+      <c r="B419" s="2" t="inlineStr">
+        <is>
+          <t>L. Patroni And Co. E.e.</t>
+        </is>
+      </c>
+      <c r="C419" s="2" t="inlineStr">
+        <is>
+          <t>7418</t>
+        </is>
+      </c>
+      <c r="D419" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E419" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Marousi</t>
+        </is>
+      </c>
+      <c r="F419" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G419" s="2" t="inlineStr">
+        <is>
+          <t>37A Leoforos Kifisias</t>
+        </is>
+      </c>
+      <c r="H419" s="2" t="inlineStr">
+        <is>
+          <t>151 23</t>
+        </is>
+      </c>
+      <c r="I419" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lesconnaisseurs.gr</t>
+        </is>
+      </c>
+      <c r="J419" s="2" t="inlineStr"/>
+      <c r="K419" s="2" t="inlineStr"/>
+      <c r="L419" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M419" s="2" t="inlineStr"/>
+      <c r="N419" s="2" t="inlineStr">
+        <is>
+          <t>info@lesconnaisseurs.gr</t>
+        </is>
+      </c>
+      <c r="O419" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0723 9195</t>
+        </is>
+      </c>
+      <c r="P419" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="Q419" s="2" t="inlineStr">
+        <is>
+          <t>093693780</t>
+        </is>
+      </c>
+      <c r="R419" s="2" t="inlineStr"/>
+      <c r="S419" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lesconnaisseurs.gr/</t>
+        </is>
+      </c>
+      <c r="T419" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lesconnaisseurs/</t>
+        </is>
+      </c>
+      <c r="U419" s="2" t="inlineStr"/>
+      <c r="V419" s="2" t="inlineStr"/>
+      <c r="W419" s="2" t="inlineStr"/>
+      <c r="X419" s="2" t="inlineStr"/>
+      <c r="Y419" s="2" t="inlineStr"/>
+      <c r="Z419" s="2" t="inlineStr"/>
+      <c r="AA419" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Greece.xlsx
+++ b/BWI/bestwine_output/bestwine_Greece.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA419"/>
+  <dimension ref="A1:AA430"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -45175,6 +45175,1081 @@
       <c r="Z419" s="2" t="inlineStr"/>
       <c r="AA419" s="2" t="inlineStr"/>
     </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>Wine Art Sole Commercial S.a.</t>
+        </is>
+      </c>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t>Wine Art Sole Commercial S.a.</t>
+        </is>
+      </c>
+      <c r="C420" s="2" t="inlineStr">
+        <is>
+          <t>7419</t>
+        </is>
+      </c>
+      <c r="D420" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E420" s="2" t="inlineStr">
+        <is>
+          <t>Ergatikes Polykatoikies Kifisias</t>
+        </is>
+      </c>
+      <c r="F420" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G420" s="2" t="inlineStr">
+        <is>
+          <t>21 Menexedon</t>
+        </is>
+      </c>
+      <c r="H420" s="2" t="inlineStr">
+        <is>
+          <t>145 64</t>
+        </is>
+      </c>
+      <c r="I420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wineshop.gr</t>
+        </is>
+      </c>
+      <c r="J420" s="2" t="inlineStr"/>
+      <c r="K420" s="2" t="inlineStr"/>
+      <c r="L420" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M420" s="2" t="inlineStr"/>
+      <c r="N420" s="2" t="inlineStr">
+        <is>
+          <t>info@wineshop.gr</t>
+        </is>
+      </c>
+      <c r="O420" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0620 4176</t>
+        </is>
+      </c>
+      <c r="P420" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q420" s="2" t="inlineStr">
+        <is>
+          <t>997103442</t>
+        </is>
+      </c>
+      <c r="R420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wineshop-gr</t>
+        </is>
+      </c>
+      <c r="S420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wineshop.gr</t>
+        </is>
+      </c>
+      <c r="T420" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wineshop.gr/</t>
+        </is>
+      </c>
+      <c r="U420" s="2" t="inlineStr"/>
+      <c r="V420" s="2" t="inlineStr"/>
+      <c r="W420" s="2" t="inlineStr"/>
+      <c r="X420" s="2" t="inlineStr"/>
+      <c r="Y420" s="2" t="inlineStr"/>
+      <c r="Z420" s="2" t="inlineStr"/>
+      <c r="AA420" s="2" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" s="2" t="inlineStr">
+        <is>
+          <t>Unibräu Hellas</t>
+        </is>
+      </c>
+      <c r="B421" s="2" t="inlineStr">
+        <is>
+          <t>Unibräu Hellas</t>
+        </is>
+      </c>
+      <c r="C421" s="2" t="inlineStr">
+        <is>
+          <t>25424</t>
+        </is>
+      </c>
+      <c r="D421" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E421" s="2" t="inlineStr">
+        <is>
+          <t>Spata-Loutsa Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F421" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G421" s="2" t="inlineStr">
+        <is>
+          <t>29 Agiou Dimitriou</t>
+        </is>
+      </c>
+      <c r="H421" s="2" t="inlineStr">
+        <is>
+          <t>190 04</t>
+        </is>
+      </c>
+      <c r="I421" s="2" t="inlineStr">
+        <is>
+          <t>https://www.unibrau.gr</t>
+        </is>
+      </c>
+      <c r="J421" s="2" t="inlineStr"/>
+      <c r="K421" s="2" t="inlineStr"/>
+      <c r="L421" s="2" t="inlineStr"/>
+      <c r="M421" s="2" t="inlineStr"/>
+      <c r="N421" s="2" t="inlineStr">
+        <is>
+          <t>info@unibrau.gr</t>
+        </is>
+      </c>
+      <c r="O421" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0665 4062</t>
+        </is>
+      </c>
+      <c r="P421" s="2" t="inlineStr"/>
+      <c r="Q421" s="2" t="inlineStr"/>
+      <c r="R421" s="2" t="inlineStr"/>
+      <c r="S421" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/unibrau.hellas/</t>
+        </is>
+      </c>
+      <c r="T421" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/unibrau.gr/</t>
+        </is>
+      </c>
+      <c r="U421" s="2" t="inlineStr"/>
+      <c r="V421" s="2" t="inlineStr"/>
+      <c r="W421" s="2" t="inlineStr"/>
+      <c r="X421" s="2" t="inlineStr"/>
+      <c r="Y421" s="2" t="inlineStr"/>
+      <c r="Z421" s="2" t="inlineStr"/>
+      <c r="AA421" s="2" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" s="2" t="inlineStr">
+        <is>
+          <t>Hebe Argentinian Wineology</t>
+        </is>
+      </c>
+      <c r="B422" s="2" t="inlineStr">
+        <is>
+          <t>Hebe Argentinian Wineology</t>
+        </is>
+      </c>
+      <c r="C422" s="2" t="inlineStr">
+        <is>
+          <t>27842</t>
+        </is>
+      </c>
+      <c r="D422" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E422" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Nea Smyrni</t>
+        </is>
+      </c>
+      <c r="F422" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G422" s="2" t="inlineStr">
+        <is>
+          <t>29 Adramittiou</t>
+        </is>
+      </c>
+      <c r="H422" s="2" t="inlineStr">
+        <is>
+          <t>171 21</t>
+        </is>
+      </c>
+      <c r="I422" s="2" t="inlineStr">
+        <is>
+          <t>http://hebewines.com</t>
+        </is>
+      </c>
+      <c r="J422" s="2" t="inlineStr"/>
+      <c r="K422" s="2" t="inlineStr"/>
+      <c r="L422" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M422" s="2" t="inlineStr"/>
+      <c r="N422" s="2" t="inlineStr">
+        <is>
+          <t>info@hebewines.com</t>
+        </is>
+      </c>
+      <c r="O422" s="2" t="inlineStr"/>
+      <c r="P422" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q422" s="2" t="inlineStr">
+        <is>
+          <t>998468164</t>
+        </is>
+      </c>
+      <c r="R422" s="2" t="inlineStr"/>
+      <c r="S422" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hebewines/</t>
+        </is>
+      </c>
+      <c r="T422" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hebe_wines/</t>
+        </is>
+      </c>
+      <c r="U422" s="2" t="inlineStr"/>
+      <c r="V422" s="2" t="inlineStr"/>
+      <c r="W422" s="2" t="inlineStr">
+        <is>
+          <t>Ivana Cecilia</t>
+        </is>
+      </c>
+      <c r="X422" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y422" s="2" t="inlineStr"/>
+      <c r="Z422" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA422" s="2" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" s="2" t="inlineStr">
+        <is>
+          <t>Hebe Argentinian Wineology</t>
+        </is>
+      </c>
+      <c r="B423" s="2" t="inlineStr">
+        <is>
+          <t>Hebe Argentinian Wineology</t>
+        </is>
+      </c>
+      <c r="C423" s="2" t="inlineStr">
+        <is>
+          <t>27842</t>
+        </is>
+      </c>
+      <c r="D423" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E423" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Nea Smyrni</t>
+        </is>
+      </c>
+      <c r="F423" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G423" s="2" t="inlineStr">
+        <is>
+          <t>29 Adramittiou</t>
+        </is>
+      </c>
+      <c r="H423" s="2" t="inlineStr">
+        <is>
+          <t>171 21</t>
+        </is>
+      </c>
+      <c r="I423" s="2" t="inlineStr">
+        <is>
+          <t>http://hebewines.com</t>
+        </is>
+      </c>
+      <c r="J423" s="2" t="inlineStr"/>
+      <c r="K423" s="2" t="inlineStr"/>
+      <c r="L423" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M423" s="2" t="inlineStr"/>
+      <c r="N423" s="2" t="inlineStr">
+        <is>
+          <t>info@hebewines.com</t>
+        </is>
+      </c>
+      <c r="O423" s="2" t="inlineStr"/>
+      <c r="P423" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q423" s="2" t="inlineStr">
+        <is>
+          <t>998468164</t>
+        </is>
+      </c>
+      <c r="R423" s="2" t="inlineStr"/>
+      <c r="S423" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hebewines/</t>
+        </is>
+      </c>
+      <c r="T423" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hebe_wines/</t>
+        </is>
+      </c>
+      <c r="U423" s="2" t="inlineStr"/>
+      <c r="V423" s="2" t="inlineStr"/>
+      <c r="W423" s="2" t="inlineStr">
+        <is>
+          <t>Emmanuel Leonardos</t>
+        </is>
+      </c>
+      <c r="X423" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y423" s="2" t="inlineStr"/>
+      <c r="Z423" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA423" s="2" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" s="2" t="inlineStr">
+        <is>
+          <t>Marinos S.a.</t>
+        </is>
+      </c>
+      <c r="B424" s="2" t="inlineStr">
+        <is>
+          <t>Marinos S.a.</t>
+        </is>
+      </c>
+      <c r="C424" s="2" t="inlineStr">
+        <is>
+          <t>7397</t>
+        </is>
+      </c>
+      <c r="D424" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E424" s="2" t="inlineStr">
+        <is>
+          <t>Rhodes</t>
+        </is>
+      </c>
+      <c r="F424" s="2" t="inlineStr">
+        <is>
+          <t>South Aegean</t>
+        </is>
+      </c>
+      <c r="G424" s="2" t="inlineStr">
+        <is>
+          <t>Ermou 23</t>
+        </is>
+      </c>
+      <c r="H424" s="2" t="inlineStr">
+        <is>
+          <t>851 00</t>
+        </is>
+      </c>
+      <c r="I424" s="2" t="inlineStr">
+        <is>
+          <t>http://marinossa.gr</t>
+        </is>
+      </c>
+      <c r="J424" s="2" t="inlineStr"/>
+      <c r="K424" s="2" t="inlineStr"/>
+      <c r="L424" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M424" s="2" t="inlineStr"/>
+      <c r="N424" s="2" t="inlineStr">
+        <is>
+          <t>info@marinossa.gr</t>
+        </is>
+      </c>
+      <c r="O424" s="2" t="inlineStr">
+        <is>
+          <t>+30 2241 077141</t>
+        </is>
+      </c>
+      <c r="P424" s="2" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="Q424" s="2" t="inlineStr">
+        <is>
+          <t>094272005</t>
+        </is>
+      </c>
+      <c r="R424" s="2" t="inlineStr"/>
+      <c r="S424" s="2" t="inlineStr"/>
+      <c r="T424" s="2" t="inlineStr"/>
+      <c r="U424" s="2" t="inlineStr"/>
+      <c r="V424" s="2" t="inlineStr"/>
+      <c r="W424" s="2" t="inlineStr">
+        <is>
+          <t>Theofilos Marinos</t>
+        </is>
+      </c>
+      <c r="X424" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y424" s="2" t="inlineStr"/>
+      <c r="Z424" s="2" t="inlineStr"/>
+      <c r="AA424" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/theofilos-marinos-78296664/</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="2" t="inlineStr">
+        <is>
+          <t>Tsianakas Konstantinos Oinodia Sommelier</t>
+        </is>
+      </c>
+      <c r="B425" s="2" t="inlineStr">
+        <is>
+          <t>Tsianakas Konstantinos Oinodia Sommelier</t>
+        </is>
+      </c>
+      <c r="C425" s="2" t="inlineStr">
+        <is>
+          <t>24830</t>
+        </is>
+      </c>
+      <c r="D425" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E425" s="2" t="inlineStr">
+        <is>
+          <t>Municipal Unit of Papagou</t>
+        </is>
+      </c>
+      <c r="F425" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G425" s="2" t="inlineStr">
+        <is>
+          <t>55 Konstantinou Versi</t>
+        </is>
+      </c>
+      <c r="H425" s="2" t="inlineStr">
+        <is>
+          <t>156 69</t>
+        </is>
+      </c>
+      <c r="I425" s="2" t="inlineStr">
+        <is>
+          <t>http://www.oinodia.com</t>
+        </is>
+      </c>
+      <c r="J425" s="2" t="inlineStr"/>
+      <c r="K425" s="2" t="inlineStr"/>
+      <c r="L425" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M425" s="2" t="inlineStr"/>
+      <c r="N425" s="2" t="inlineStr">
+        <is>
+          <t>k.tsianakas@oinodia.com</t>
+        </is>
+      </c>
+      <c r="O425" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0653 5990</t>
+        </is>
+      </c>
+      <c r="P425" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q425" s="2" t="inlineStr">
+        <is>
+          <t>119203168</t>
+        </is>
+      </c>
+      <c r="R425" s="2" t="inlineStr"/>
+      <c r="S425" s="2" t="inlineStr"/>
+      <c r="T425" s="2" t="inlineStr"/>
+      <c r="U425" s="2" t="inlineStr"/>
+      <c r="V425" s="2" t="inlineStr"/>
+      <c r="W425" s="2" t="inlineStr">
+        <is>
+          <t>Konstantine Tsianakas</t>
+        </is>
+      </c>
+      <c r="X425" s="2" t="inlineStr">
+        <is>
+          <t>Sommelier</t>
+        </is>
+      </c>
+      <c r="Y425" s="2" t="inlineStr"/>
+      <c r="Z425" s="2" t="inlineStr"/>
+      <c r="AA425" s="2" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" s="2" t="inlineStr">
+        <is>
+          <t>Tsianakas Konstantinos Oinodia Sommelier</t>
+        </is>
+      </c>
+      <c r="B426" s="2" t="inlineStr">
+        <is>
+          <t>Tsianakas Konstantinos Oinodia Sommelier</t>
+        </is>
+      </c>
+      <c r="C426" s="2" t="inlineStr">
+        <is>
+          <t>24830</t>
+        </is>
+      </c>
+      <c r="D426" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E426" s="2" t="inlineStr">
+        <is>
+          <t>Municipal Unit of Papagou</t>
+        </is>
+      </c>
+      <c r="F426" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G426" s="2" t="inlineStr">
+        <is>
+          <t>55 Konstantinou Versi</t>
+        </is>
+      </c>
+      <c r="H426" s="2" t="inlineStr">
+        <is>
+          <t>156 69</t>
+        </is>
+      </c>
+      <c r="I426" s="2" t="inlineStr">
+        <is>
+          <t>http://www.oinodia.com</t>
+        </is>
+      </c>
+      <c r="J426" s="2" t="inlineStr"/>
+      <c r="K426" s="2" t="inlineStr"/>
+      <c r="L426" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M426" s="2" t="inlineStr"/>
+      <c r="N426" s="2" t="inlineStr">
+        <is>
+          <t>k.tsianakas@oinodia.com</t>
+        </is>
+      </c>
+      <c r="O426" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0653 5990</t>
+        </is>
+      </c>
+      <c r="P426" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q426" s="2" t="inlineStr">
+        <is>
+          <t>119203168</t>
+        </is>
+      </c>
+      <c r="R426" s="2" t="inlineStr"/>
+      <c r="S426" s="2" t="inlineStr"/>
+      <c r="T426" s="2" t="inlineStr"/>
+      <c r="U426" s="2" t="inlineStr"/>
+      <c r="V426" s="2" t="inlineStr"/>
+      <c r="W426" s="2" t="inlineStr">
+        <is>
+          <t>Spyridon Demertzis</t>
+        </is>
+      </c>
+      <c r="X426" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner</t>
+        </is>
+      </c>
+      <c r="Y426" s="2" t="inlineStr"/>
+      <c r="Z426" s="2" t="inlineStr"/>
+      <c r="AA426" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/spyridon-demertzis-b8295b5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" s="2" t="inlineStr">
+        <is>
+          <t>Mavrikos Imports S.a.</t>
+        </is>
+      </c>
+      <c r="B427" s="2" t="inlineStr">
+        <is>
+          <t>Mavrikos Imports S.a.</t>
+        </is>
+      </c>
+      <c r="C427" s="2" t="inlineStr">
+        <is>
+          <t>7398</t>
+        </is>
+      </c>
+      <c r="D427" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E427" s="2" t="inlineStr">
+        <is>
+          <t>Piraeus</t>
+        </is>
+      </c>
+      <c r="F427" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G427" s="2" t="inlineStr">
+        <is>
+          <t>7 Naxou</t>
+        </is>
+      </c>
+      <c r="H427" s="2" t="inlineStr">
+        <is>
+          <t>185 41</t>
+        </is>
+      </c>
+      <c r="I427" s="2" t="inlineStr">
+        <is>
+          <t>https://mavrikosimports.gr</t>
+        </is>
+      </c>
+      <c r="J427" s="2" t="inlineStr"/>
+      <c r="K427" s="2" t="inlineStr"/>
+      <c r="L427" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M427" s="2" t="inlineStr"/>
+      <c r="N427" s="2" t="inlineStr">
+        <is>
+          <t>orddep@mavrikosimports.gr</t>
+        </is>
+      </c>
+      <c r="O427" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0481 3064</t>
+        </is>
+      </c>
+      <c r="P427" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="Q427" s="2" t="inlineStr">
+        <is>
+          <t>094047465</t>
+        </is>
+      </c>
+      <c r="R427" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mavrikos-imports-s-a/</t>
+        </is>
+      </c>
+      <c r="S427" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/mavrikosimports</t>
+        </is>
+      </c>
+      <c r="T427" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/imports_mavrikos</t>
+        </is>
+      </c>
+      <c r="U427" s="2" t="inlineStr"/>
+      <c r="V427" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@mavrikosimports</t>
+        </is>
+      </c>
+      <c r="W427" s="2" t="inlineStr">
+        <is>
+          <t>MARIA MAVRIKOS</t>
+        </is>
+      </c>
+      <c r="X427" s="2" t="inlineStr">
+        <is>
+          <t>Export and import manager</t>
+        </is>
+      </c>
+      <c r="Y427" s="2" t="inlineStr"/>
+      <c r="Z427" s="2" t="inlineStr"/>
+      <c r="AA427" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maria-mavrikos-8943b3395/</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" s="2" t="inlineStr">
+        <is>
+          <t>Foodrinco S.a.</t>
+        </is>
+      </c>
+      <c r="B428" s="2" t="inlineStr">
+        <is>
+          <t>Foodrinco S.a.</t>
+        </is>
+      </c>
+      <c r="C428" s="2" t="inlineStr">
+        <is>
+          <t>22331</t>
+        </is>
+      </c>
+      <c r="D428" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E428" s="2" t="inlineStr">
+        <is>
+          <t>Kryoneri Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F428" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G428" s="2" t="inlineStr">
+        <is>
+          <t>132 Lefkis</t>
+        </is>
+      </c>
+      <c r="H428" s="2" t="inlineStr">
+        <is>
+          <t>145 68</t>
+        </is>
+      </c>
+      <c r="I428" s="2" t="inlineStr">
+        <is>
+          <t>https://foodrinco.gr</t>
+        </is>
+      </c>
+      <c r="J428" s="2" t="inlineStr"/>
+      <c r="K428" s="2" t="inlineStr"/>
+      <c r="L428" s="2" t="inlineStr"/>
+      <c r="M428" s="2" t="inlineStr"/>
+      <c r="N428" s="2" t="inlineStr">
+        <is>
+          <t>info@foodrinco.gr</t>
+        </is>
+      </c>
+      <c r="O428" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 6400 0200</t>
+        </is>
+      </c>
+      <c r="P428" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q428" s="2" t="inlineStr">
+        <is>
+          <t>094430257</t>
+        </is>
+      </c>
+      <c r="R428" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vytogiannis-group-of-companies/</t>
+        </is>
+      </c>
+      <c r="S428" s="2" t="inlineStr"/>
+      <c r="T428" s="2" t="inlineStr"/>
+      <c r="U428" s="2" t="inlineStr"/>
+      <c r="V428" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/foodrinco</t>
+        </is>
+      </c>
+      <c r="W428" s="2" t="inlineStr">
+        <is>
+          <t>George Vitogiannis</t>
+        </is>
+      </c>
+      <c r="X428" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y428" s="2" t="inlineStr"/>
+      <c r="Z428" s="2" t="inlineStr"/>
+      <c r="AA428" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/george-vitogiannis-a041753/</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" s="2" t="inlineStr">
+        <is>
+          <t>Foodrinco S.a.</t>
+        </is>
+      </c>
+      <c r="B429" s="2" t="inlineStr">
+        <is>
+          <t>Foodrinco S.a.</t>
+        </is>
+      </c>
+      <c r="C429" s="2" t="inlineStr">
+        <is>
+          <t>22331</t>
+        </is>
+      </c>
+      <c r="D429" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E429" s="2" t="inlineStr">
+        <is>
+          <t>Kryoneri Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F429" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G429" s="2" t="inlineStr">
+        <is>
+          <t>132 Lefkis</t>
+        </is>
+      </c>
+      <c r="H429" s="2" t="inlineStr">
+        <is>
+          <t>145 68</t>
+        </is>
+      </c>
+      <c r="I429" s="2" t="inlineStr">
+        <is>
+          <t>https://foodrinco.gr</t>
+        </is>
+      </c>
+      <c r="J429" s="2" t="inlineStr"/>
+      <c r="K429" s="2" t="inlineStr"/>
+      <c r="L429" s="2" t="inlineStr"/>
+      <c r="M429" s="2" t="inlineStr"/>
+      <c r="N429" s="2" t="inlineStr">
+        <is>
+          <t>info@foodrinco.gr</t>
+        </is>
+      </c>
+      <c r="O429" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 6400 0200</t>
+        </is>
+      </c>
+      <c r="P429" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q429" s="2" t="inlineStr">
+        <is>
+          <t>094430257</t>
+        </is>
+      </c>
+      <c r="R429" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vytogiannis-group-of-companies/</t>
+        </is>
+      </c>
+      <c r="S429" s="2" t="inlineStr"/>
+      <c r="T429" s="2" t="inlineStr"/>
+      <c r="U429" s="2" t="inlineStr"/>
+      <c r="V429" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/foodrinco</t>
+        </is>
+      </c>
+      <c r="W429" s="2" t="inlineStr">
+        <is>
+          <t>Stelios Tiktopoulos</t>
+        </is>
+      </c>
+      <c r="X429" s="2" t="inlineStr">
+        <is>
+          <t>Area Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y429" s="2" t="inlineStr"/>
+      <c r="Z429" s="2" t="inlineStr"/>
+      <c r="AA429" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stelios-tiktopoulos-6bb06934/</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" s="2" t="inlineStr">
+        <is>
+          <t>L. Patroni And Co. E.e.</t>
+        </is>
+      </c>
+      <c r="B430" s="2" t="inlineStr">
+        <is>
+          <t>L. Patroni And Co. E.e.</t>
+        </is>
+      </c>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>7418</t>
+        </is>
+      </c>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Marousi</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G430" s="2" t="inlineStr">
+        <is>
+          <t>37A Leoforos Kifisias</t>
+        </is>
+      </c>
+      <c r="H430" s="2" t="inlineStr">
+        <is>
+          <t>151 23</t>
+        </is>
+      </c>
+      <c r="I430" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lesconnaisseurs.gr</t>
+        </is>
+      </c>
+      <c r="J430" s="2" t="inlineStr"/>
+      <c r="K430" s="2" t="inlineStr"/>
+      <c r="L430" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M430" s="2" t="inlineStr"/>
+      <c r="N430" s="2" t="inlineStr">
+        <is>
+          <t>info@lesconnaisseurs.gr</t>
+        </is>
+      </c>
+      <c r="O430" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0723 9195</t>
+        </is>
+      </c>
+      <c r="P430" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="Q430" s="2" t="inlineStr">
+        <is>
+          <t>093693780</t>
+        </is>
+      </c>
+      <c r="R430" s="2" t="inlineStr"/>
+      <c r="S430" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lesconnaisseurs.gr/</t>
+        </is>
+      </c>
+      <c r="T430" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lesconnaisseurs/</t>
+        </is>
+      </c>
+      <c r="U430" s="2" t="inlineStr"/>
+      <c r="V430" s="2" t="inlineStr"/>
+      <c r="W430" s="2" t="inlineStr"/>
+      <c r="X430" s="2" t="inlineStr"/>
+      <c r="Y430" s="2" t="inlineStr"/>
+      <c r="Z430" s="2" t="inlineStr"/>
+      <c r="AA430" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Greece.xlsx
+++ b/BWI/bestwine_output/bestwine_Greece.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA430"/>
+  <dimension ref="A1:AA442"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -46250,6 +46250,1186 @@
       <c r="Z430" s="2" t="inlineStr"/>
       <c r="AA430" s="2" t="inlineStr"/>
     </row>
+    <row r="431">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>Foodsngoods O.e.</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>Foodsngoods O.e.</t>
+        </is>
+      </c>
+      <c r="C431" s="2" t="inlineStr">
+        <is>
+          <t>7413</t>
+        </is>
+      </c>
+      <c r="D431" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E431" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Chania</t>
+        </is>
+      </c>
+      <c r="F431" s="2" t="inlineStr">
+        <is>
+          <t>Region of Crete</t>
+        </is>
+      </c>
+      <c r="G431" s="2" t="inlineStr">
+        <is>
+          <t>6 Antoniou Michelidaki</t>
+        </is>
+      </c>
+      <c r="H431" s="2" t="inlineStr">
+        <is>
+          <t>731 32</t>
+        </is>
+      </c>
+      <c r="I431" s="2" t="inlineStr">
+        <is>
+          <t>https://www.foodsngoods.com</t>
+        </is>
+      </c>
+      <c r="J431" s="2" t="inlineStr"/>
+      <c r="K431" s="2" t="inlineStr"/>
+      <c r="L431" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M431" s="2" t="inlineStr"/>
+      <c r="N431" s="2" t="inlineStr">
+        <is>
+          <t>info@foodsngoods.com</t>
+        </is>
+      </c>
+      <c r="O431" s="2" t="inlineStr">
+        <is>
+          <t>+30 2821 501949</t>
+        </is>
+      </c>
+      <c r="P431" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q431" s="2" t="inlineStr">
+        <is>
+          <t>800331952</t>
+        </is>
+      </c>
+      <c r="R431" s="2" t="inlineStr"/>
+      <c r="S431" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/foodsngoods/</t>
+        </is>
+      </c>
+      <c r="T431" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/foods_n_goods_com</t>
+        </is>
+      </c>
+      <c r="U431" s="2" t="inlineStr"/>
+      <c r="V431" s="2" t="inlineStr"/>
+      <c r="W431" s="2" t="inlineStr">
+        <is>
+          <t>Gurprit Doad</t>
+        </is>
+      </c>
+      <c r="X431" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y431" s="2" t="inlineStr"/>
+      <c r="Z431" s="2" t="inlineStr"/>
+      <c r="AA431" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gurprit-doad-068212203/?originalSubdomain=ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="2" t="inlineStr">
+        <is>
+          <t>Wine Art Sole Commercial S.a.</t>
+        </is>
+      </c>
+      <c r="B432" s="2" t="inlineStr">
+        <is>
+          <t>Wine Art Sole Commercial S.a.</t>
+        </is>
+      </c>
+      <c r="C432" s="2" t="inlineStr">
+        <is>
+          <t>7419</t>
+        </is>
+      </c>
+      <c r="D432" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E432" s="2" t="inlineStr">
+        <is>
+          <t>Ergatikes Polykatoikies Kifisias</t>
+        </is>
+      </c>
+      <c r="F432" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G432" s="2" t="inlineStr">
+        <is>
+          <t>21 Menexedon</t>
+        </is>
+      </c>
+      <c r="H432" s="2" t="inlineStr">
+        <is>
+          <t>145 64</t>
+        </is>
+      </c>
+      <c r="I432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wineshop.gr</t>
+        </is>
+      </c>
+      <c r="J432" s="2" t="inlineStr"/>
+      <c r="K432" s="2" t="inlineStr"/>
+      <c r="L432" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M432" s="2" t="inlineStr"/>
+      <c r="N432" s="2" t="inlineStr">
+        <is>
+          <t>info@wineshop.gr</t>
+        </is>
+      </c>
+      <c r="O432" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0620 4176</t>
+        </is>
+      </c>
+      <c r="P432" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q432" s="2" t="inlineStr">
+        <is>
+          <t>997103442</t>
+        </is>
+      </c>
+      <c r="R432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wineshop-gr</t>
+        </is>
+      </c>
+      <c r="S432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wineshop.gr</t>
+        </is>
+      </c>
+      <c r="T432" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wineshop.gr/</t>
+        </is>
+      </c>
+      <c r="U432" s="2" t="inlineStr"/>
+      <c r="V432" s="2" t="inlineStr"/>
+      <c r="W432" s="2" t="inlineStr"/>
+      <c r="X432" s="2" t="inlineStr"/>
+      <c r="Y432" s="2" t="inlineStr"/>
+      <c r="Z432" s="2" t="inlineStr"/>
+      <c r="AA432" s="2" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="2" t="inlineStr">
+        <is>
+          <t>Unibräu Hellas</t>
+        </is>
+      </c>
+      <c r="B433" s="2" t="inlineStr">
+        <is>
+          <t>Unibräu Hellas</t>
+        </is>
+      </c>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>25424</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>Spata-Loutsa Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F433" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G433" s="2" t="inlineStr">
+        <is>
+          <t>29 Agiou Dimitriou</t>
+        </is>
+      </c>
+      <c r="H433" s="2" t="inlineStr">
+        <is>
+          <t>190 04</t>
+        </is>
+      </c>
+      <c r="I433" s="2" t="inlineStr">
+        <is>
+          <t>https://www.unibrau.gr</t>
+        </is>
+      </c>
+      <c r="J433" s="2" t="inlineStr"/>
+      <c r="K433" s="2" t="inlineStr"/>
+      <c r="L433" s="2" t="inlineStr"/>
+      <c r="M433" s="2" t="inlineStr"/>
+      <c r="N433" s="2" t="inlineStr">
+        <is>
+          <t>info@unibrau.gr</t>
+        </is>
+      </c>
+      <c r="O433" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0665 4062</t>
+        </is>
+      </c>
+      <c r="P433" s="2" t="inlineStr"/>
+      <c r="Q433" s="2" t="inlineStr"/>
+      <c r="R433" s="2" t="inlineStr"/>
+      <c r="S433" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/unibrau.hellas/</t>
+        </is>
+      </c>
+      <c r="T433" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/unibrau.gr/</t>
+        </is>
+      </c>
+      <c r="U433" s="2" t="inlineStr"/>
+      <c r="V433" s="2" t="inlineStr"/>
+      <c r="W433" s="2" t="inlineStr"/>
+      <c r="X433" s="2" t="inlineStr"/>
+      <c r="Y433" s="2" t="inlineStr"/>
+      <c r="Z433" s="2" t="inlineStr"/>
+      <c r="AA433" s="2" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="2" t="inlineStr">
+        <is>
+          <t>Hebe Argentinian Wineology</t>
+        </is>
+      </c>
+      <c r="B434" s="2" t="inlineStr">
+        <is>
+          <t>Hebe Argentinian Wineology</t>
+        </is>
+      </c>
+      <c r="C434" s="2" t="inlineStr">
+        <is>
+          <t>27842</t>
+        </is>
+      </c>
+      <c r="D434" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E434" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Nea Smyrni</t>
+        </is>
+      </c>
+      <c r="F434" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G434" s="2" t="inlineStr">
+        <is>
+          <t>29 Adramittiou</t>
+        </is>
+      </c>
+      <c r="H434" s="2" t="inlineStr">
+        <is>
+          <t>171 21</t>
+        </is>
+      </c>
+      <c r="I434" s="2" t="inlineStr">
+        <is>
+          <t>http://hebewines.com</t>
+        </is>
+      </c>
+      <c r="J434" s="2" t="inlineStr"/>
+      <c r="K434" s="2" t="inlineStr"/>
+      <c r="L434" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M434" s="2" t="inlineStr"/>
+      <c r="N434" s="2" t="inlineStr">
+        <is>
+          <t>info@hebewines.com</t>
+        </is>
+      </c>
+      <c r="O434" s="2" t="inlineStr"/>
+      <c r="P434" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q434" s="2" t="inlineStr">
+        <is>
+          <t>998468164</t>
+        </is>
+      </c>
+      <c r="R434" s="2" t="inlineStr"/>
+      <c r="S434" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hebewines/</t>
+        </is>
+      </c>
+      <c r="T434" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hebe_wines/</t>
+        </is>
+      </c>
+      <c r="U434" s="2" t="inlineStr"/>
+      <c r="V434" s="2" t="inlineStr"/>
+      <c r="W434" s="2" t="inlineStr">
+        <is>
+          <t>Ivana Cecilia</t>
+        </is>
+      </c>
+      <c r="X434" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y434" s="2" t="inlineStr"/>
+      <c r="Z434" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA434" s="2" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="2" t="inlineStr">
+        <is>
+          <t>Hebe Argentinian Wineology</t>
+        </is>
+      </c>
+      <c r="B435" s="2" t="inlineStr">
+        <is>
+          <t>Hebe Argentinian Wineology</t>
+        </is>
+      </c>
+      <c r="C435" s="2" t="inlineStr">
+        <is>
+          <t>27842</t>
+        </is>
+      </c>
+      <c r="D435" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E435" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Nea Smyrni</t>
+        </is>
+      </c>
+      <c r="F435" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G435" s="2" t="inlineStr">
+        <is>
+          <t>29 Adramittiou</t>
+        </is>
+      </c>
+      <c r="H435" s="2" t="inlineStr">
+        <is>
+          <t>171 21</t>
+        </is>
+      </c>
+      <c r="I435" s="2" t="inlineStr">
+        <is>
+          <t>http://hebewines.com</t>
+        </is>
+      </c>
+      <c r="J435" s="2" t="inlineStr"/>
+      <c r="K435" s="2" t="inlineStr"/>
+      <c r="L435" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M435" s="2" t="inlineStr"/>
+      <c r="N435" s="2" t="inlineStr">
+        <is>
+          <t>info@hebewines.com</t>
+        </is>
+      </c>
+      <c r="O435" s="2" t="inlineStr"/>
+      <c r="P435" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q435" s="2" t="inlineStr">
+        <is>
+          <t>998468164</t>
+        </is>
+      </c>
+      <c r="R435" s="2" t="inlineStr"/>
+      <c r="S435" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hebewines/</t>
+        </is>
+      </c>
+      <c r="T435" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hebe_wines/</t>
+        </is>
+      </c>
+      <c r="U435" s="2" t="inlineStr"/>
+      <c r="V435" s="2" t="inlineStr"/>
+      <c r="W435" s="2" t="inlineStr">
+        <is>
+          <t>Emmanuel Leonardos</t>
+        </is>
+      </c>
+      <c r="X435" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y435" s="2" t="inlineStr"/>
+      <c r="Z435" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA435" s="2" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="2" t="inlineStr">
+        <is>
+          <t>Marinos S.a.</t>
+        </is>
+      </c>
+      <c r="B436" s="2" t="inlineStr">
+        <is>
+          <t>Marinos S.a.</t>
+        </is>
+      </c>
+      <c r="C436" s="2" t="inlineStr">
+        <is>
+          <t>7397</t>
+        </is>
+      </c>
+      <c r="D436" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E436" s="2" t="inlineStr">
+        <is>
+          <t>Rhodes</t>
+        </is>
+      </c>
+      <c r="F436" s="2" t="inlineStr">
+        <is>
+          <t>South Aegean</t>
+        </is>
+      </c>
+      <c r="G436" s="2" t="inlineStr">
+        <is>
+          <t>Ermou 23</t>
+        </is>
+      </c>
+      <c r="H436" s="2" t="inlineStr">
+        <is>
+          <t>851 00</t>
+        </is>
+      </c>
+      <c r="I436" s="2" t="inlineStr">
+        <is>
+          <t>http://marinossa.gr</t>
+        </is>
+      </c>
+      <c r="J436" s="2" t="inlineStr"/>
+      <c r="K436" s="2" t="inlineStr"/>
+      <c r="L436" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M436" s="2" t="inlineStr"/>
+      <c r="N436" s="2" t="inlineStr">
+        <is>
+          <t>info@marinossa.gr</t>
+        </is>
+      </c>
+      <c r="O436" s="2" t="inlineStr">
+        <is>
+          <t>+30 2241 077141</t>
+        </is>
+      </c>
+      <c r="P436" s="2" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="Q436" s="2" t="inlineStr">
+        <is>
+          <t>094272005</t>
+        </is>
+      </c>
+      <c r="R436" s="2" t="inlineStr"/>
+      <c r="S436" s="2" t="inlineStr"/>
+      <c r="T436" s="2" t="inlineStr"/>
+      <c r="U436" s="2" t="inlineStr"/>
+      <c r="V436" s="2" t="inlineStr"/>
+      <c r="W436" s="2" t="inlineStr">
+        <is>
+          <t>Theofilos Marinos</t>
+        </is>
+      </c>
+      <c r="X436" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y436" s="2" t="inlineStr"/>
+      <c r="Z436" s="2" t="inlineStr"/>
+      <c r="AA436" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/theofilos-marinos-78296664/</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="2" t="inlineStr">
+        <is>
+          <t>Tsianakas Konstantinos Oinodia Sommelier</t>
+        </is>
+      </c>
+      <c r="B437" s="2" t="inlineStr">
+        <is>
+          <t>Tsianakas Konstantinos Oinodia Sommelier</t>
+        </is>
+      </c>
+      <c r="C437" s="2" t="inlineStr">
+        <is>
+          <t>24830</t>
+        </is>
+      </c>
+      <c r="D437" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E437" s="2" t="inlineStr">
+        <is>
+          <t>Municipal Unit of Papagou</t>
+        </is>
+      </c>
+      <c r="F437" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G437" s="2" t="inlineStr">
+        <is>
+          <t>55 Konstantinou Versi</t>
+        </is>
+      </c>
+      <c r="H437" s="2" t="inlineStr">
+        <is>
+          <t>156 69</t>
+        </is>
+      </c>
+      <c r="I437" s="2" t="inlineStr">
+        <is>
+          <t>http://www.oinodia.com</t>
+        </is>
+      </c>
+      <c r="J437" s="2" t="inlineStr"/>
+      <c r="K437" s="2" t="inlineStr"/>
+      <c r="L437" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M437" s="2" t="inlineStr"/>
+      <c r="N437" s="2" t="inlineStr">
+        <is>
+          <t>k.tsianakas@oinodia.com</t>
+        </is>
+      </c>
+      <c r="O437" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0653 5990</t>
+        </is>
+      </c>
+      <c r="P437" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q437" s="2" t="inlineStr">
+        <is>
+          <t>119203168</t>
+        </is>
+      </c>
+      <c r="R437" s="2" t="inlineStr"/>
+      <c r="S437" s="2" t="inlineStr"/>
+      <c r="T437" s="2" t="inlineStr"/>
+      <c r="U437" s="2" t="inlineStr"/>
+      <c r="V437" s="2" t="inlineStr"/>
+      <c r="W437" s="2" t="inlineStr">
+        <is>
+          <t>Konstantine Tsianakas</t>
+        </is>
+      </c>
+      <c r="X437" s="2" t="inlineStr">
+        <is>
+          <t>Sommelier</t>
+        </is>
+      </c>
+      <c r="Y437" s="2" t="inlineStr"/>
+      <c r="Z437" s="2" t="inlineStr"/>
+      <c r="AA437" s="2" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="2" t="inlineStr">
+        <is>
+          <t>Tsianakas Konstantinos Oinodia Sommelier</t>
+        </is>
+      </c>
+      <c r="B438" s="2" t="inlineStr">
+        <is>
+          <t>Tsianakas Konstantinos Oinodia Sommelier</t>
+        </is>
+      </c>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>24830</t>
+        </is>
+      </c>
+      <c r="D438" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="inlineStr">
+        <is>
+          <t>Municipal Unit of Papagou</t>
+        </is>
+      </c>
+      <c r="F438" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G438" s="2" t="inlineStr">
+        <is>
+          <t>55 Konstantinou Versi</t>
+        </is>
+      </c>
+      <c r="H438" s="2" t="inlineStr">
+        <is>
+          <t>156 69</t>
+        </is>
+      </c>
+      <c r="I438" s="2" t="inlineStr">
+        <is>
+          <t>http://www.oinodia.com</t>
+        </is>
+      </c>
+      <c r="J438" s="2" t="inlineStr"/>
+      <c r="K438" s="2" t="inlineStr"/>
+      <c r="L438" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M438" s="2" t="inlineStr"/>
+      <c r="N438" s="2" t="inlineStr">
+        <is>
+          <t>k.tsianakas@oinodia.com</t>
+        </is>
+      </c>
+      <c r="O438" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0653 5990</t>
+        </is>
+      </c>
+      <c r="P438" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q438" s="2" t="inlineStr">
+        <is>
+          <t>119203168</t>
+        </is>
+      </c>
+      <c r="R438" s="2" t="inlineStr"/>
+      <c r="S438" s="2" t="inlineStr"/>
+      <c r="T438" s="2" t="inlineStr"/>
+      <c r="U438" s="2" t="inlineStr"/>
+      <c r="V438" s="2" t="inlineStr"/>
+      <c r="W438" s="2" t="inlineStr">
+        <is>
+          <t>Spyridon Demertzis</t>
+        </is>
+      </c>
+      <c r="X438" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner</t>
+        </is>
+      </c>
+      <c r="Y438" s="2" t="inlineStr"/>
+      <c r="Z438" s="2" t="inlineStr"/>
+      <c r="AA438" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/spyridon-demertzis-b8295b5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="2" t="inlineStr">
+        <is>
+          <t>Mavrikos Imports S.a.</t>
+        </is>
+      </c>
+      <c r="B439" s="2" t="inlineStr">
+        <is>
+          <t>Mavrikos Imports S.a.</t>
+        </is>
+      </c>
+      <c r="C439" s="2" t="inlineStr">
+        <is>
+          <t>7398</t>
+        </is>
+      </c>
+      <c r="D439" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E439" s="2" t="inlineStr">
+        <is>
+          <t>Piraeus</t>
+        </is>
+      </c>
+      <c r="F439" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G439" s="2" t="inlineStr">
+        <is>
+          <t>7 Naxou</t>
+        </is>
+      </c>
+      <c r="H439" s="2" t="inlineStr">
+        <is>
+          <t>185 41</t>
+        </is>
+      </c>
+      <c r="I439" s="2" t="inlineStr">
+        <is>
+          <t>https://mavrikosimports.gr</t>
+        </is>
+      </c>
+      <c r="J439" s="2" t="inlineStr"/>
+      <c r="K439" s="2" t="inlineStr"/>
+      <c r="L439" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M439" s="2" t="inlineStr"/>
+      <c r="N439" s="2" t="inlineStr">
+        <is>
+          <t>orddep@mavrikosimports.gr</t>
+        </is>
+      </c>
+      <c r="O439" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0481 3064</t>
+        </is>
+      </c>
+      <c r="P439" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="Q439" s="2" t="inlineStr">
+        <is>
+          <t>094047465</t>
+        </is>
+      </c>
+      <c r="R439" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mavrikos-imports-s-a/</t>
+        </is>
+      </c>
+      <c r="S439" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/mavrikosimports</t>
+        </is>
+      </c>
+      <c r="T439" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/imports_mavrikos</t>
+        </is>
+      </c>
+      <c r="U439" s="2" t="inlineStr"/>
+      <c r="V439" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@mavrikosimports</t>
+        </is>
+      </c>
+      <c r="W439" s="2" t="inlineStr">
+        <is>
+          <t>MARIA MAVRIKOS</t>
+        </is>
+      </c>
+      <c r="X439" s="2" t="inlineStr">
+        <is>
+          <t>Export and import manager</t>
+        </is>
+      </c>
+      <c r="Y439" s="2" t="inlineStr"/>
+      <c r="Z439" s="2" t="inlineStr"/>
+      <c r="AA439" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maria-mavrikos-8943b3395/</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" s="2" t="inlineStr">
+        <is>
+          <t>Foodrinco S.a.</t>
+        </is>
+      </c>
+      <c r="B440" s="2" t="inlineStr">
+        <is>
+          <t>Foodrinco S.a.</t>
+        </is>
+      </c>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>22331</t>
+        </is>
+      </c>
+      <c r="D440" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>Kryoneri Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F440" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G440" s="2" t="inlineStr">
+        <is>
+          <t>132 Lefkis</t>
+        </is>
+      </c>
+      <c r="H440" s="2" t="inlineStr">
+        <is>
+          <t>145 68</t>
+        </is>
+      </c>
+      <c r="I440" s="2" t="inlineStr">
+        <is>
+          <t>https://foodrinco.gr</t>
+        </is>
+      </c>
+      <c r="J440" s="2" t="inlineStr"/>
+      <c r="K440" s="2" t="inlineStr"/>
+      <c r="L440" s="2" t="inlineStr"/>
+      <c r="M440" s="2" t="inlineStr"/>
+      <c r="N440" s="2" t="inlineStr">
+        <is>
+          <t>info@foodrinco.gr</t>
+        </is>
+      </c>
+      <c r="O440" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 6400 0200</t>
+        </is>
+      </c>
+      <c r="P440" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q440" s="2" t="inlineStr">
+        <is>
+          <t>094430257</t>
+        </is>
+      </c>
+      <c r="R440" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vytogiannis-group-of-companies/</t>
+        </is>
+      </c>
+      <c r="S440" s="2" t="inlineStr"/>
+      <c r="T440" s="2" t="inlineStr"/>
+      <c r="U440" s="2" t="inlineStr"/>
+      <c r="V440" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/foodrinco</t>
+        </is>
+      </c>
+      <c r="W440" s="2" t="inlineStr">
+        <is>
+          <t>George Vitogiannis</t>
+        </is>
+      </c>
+      <c r="X440" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y440" s="2" t="inlineStr"/>
+      <c r="Z440" s="2" t="inlineStr"/>
+      <c r="AA440" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/george-vitogiannis-a041753/</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" s="2" t="inlineStr">
+        <is>
+          <t>Foodrinco S.a.</t>
+        </is>
+      </c>
+      <c r="B441" s="2" t="inlineStr">
+        <is>
+          <t>Foodrinco S.a.</t>
+        </is>
+      </c>
+      <c r="C441" s="2" t="inlineStr">
+        <is>
+          <t>22331</t>
+        </is>
+      </c>
+      <c r="D441" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E441" s="2" t="inlineStr">
+        <is>
+          <t>Kryoneri Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F441" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G441" s="2" t="inlineStr">
+        <is>
+          <t>132 Lefkis</t>
+        </is>
+      </c>
+      <c r="H441" s="2" t="inlineStr">
+        <is>
+          <t>145 68</t>
+        </is>
+      </c>
+      <c r="I441" s="2" t="inlineStr">
+        <is>
+          <t>https://foodrinco.gr</t>
+        </is>
+      </c>
+      <c r="J441" s="2" t="inlineStr"/>
+      <c r="K441" s="2" t="inlineStr"/>
+      <c r="L441" s="2" t="inlineStr"/>
+      <c r="M441" s="2" t="inlineStr"/>
+      <c r="N441" s="2" t="inlineStr">
+        <is>
+          <t>info@foodrinco.gr</t>
+        </is>
+      </c>
+      <c r="O441" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 6400 0200</t>
+        </is>
+      </c>
+      <c r="P441" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q441" s="2" t="inlineStr">
+        <is>
+          <t>094430257</t>
+        </is>
+      </c>
+      <c r="R441" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vytogiannis-group-of-companies/</t>
+        </is>
+      </c>
+      <c r="S441" s="2" t="inlineStr"/>
+      <c r="T441" s="2" t="inlineStr"/>
+      <c r="U441" s="2" t="inlineStr"/>
+      <c r="V441" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/foodrinco</t>
+        </is>
+      </c>
+      <c r="W441" s="2" t="inlineStr">
+        <is>
+          <t>Stelios Tiktopoulos</t>
+        </is>
+      </c>
+      <c r="X441" s="2" t="inlineStr">
+        <is>
+          <t>Area Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y441" s="2" t="inlineStr"/>
+      <c r="Z441" s="2" t="inlineStr"/>
+      <c r="AA441" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stelios-tiktopoulos-6bb06934/</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>L. Patroni And Co. E.e.</t>
+        </is>
+      </c>
+      <c r="B442" s="2" t="inlineStr">
+        <is>
+          <t>L. Patroni And Co. E.e.</t>
+        </is>
+      </c>
+      <c r="C442" s="2" t="inlineStr">
+        <is>
+          <t>7418</t>
+        </is>
+      </c>
+      <c r="D442" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E442" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Marousi</t>
+        </is>
+      </c>
+      <c r="F442" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G442" s="2" t="inlineStr">
+        <is>
+          <t>37A Leoforos Kifisias</t>
+        </is>
+      </c>
+      <c r="H442" s="2" t="inlineStr">
+        <is>
+          <t>151 23</t>
+        </is>
+      </c>
+      <c r="I442" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lesconnaisseurs.gr</t>
+        </is>
+      </c>
+      <c r="J442" s="2" t="inlineStr"/>
+      <c r="K442" s="2" t="inlineStr"/>
+      <c r="L442" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M442" s="2" t="inlineStr"/>
+      <c r="N442" s="2" t="inlineStr">
+        <is>
+          <t>info@lesconnaisseurs.gr</t>
+        </is>
+      </c>
+      <c r="O442" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0723 9195</t>
+        </is>
+      </c>
+      <c r="P442" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="Q442" s="2" t="inlineStr">
+        <is>
+          <t>093693780</t>
+        </is>
+      </c>
+      <c r="R442" s="2" t="inlineStr"/>
+      <c r="S442" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lesconnaisseurs.gr/</t>
+        </is>
+      </c>
+      <c r="T442" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lesconnaisseurs/</t>
+        </is>
+      </c>
+      <c r="U442" s="2" t="inlineStr"/>
+      <c r="V442" s="2" t="inlineStr"/>
+      <c r="W442" s="2" t="inlineStr"/>
+      <c r="X442" s="2" t="inlineStr"/>
+      <c r="Y442" s="2" t="inlineStr"/>
+      <c r="Z442" s="2" t="inlineStr"/>
+      <c r="AA442" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Greece.xlsx
+++ b/BWI/bestwine_output/bestwine_Greece.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA442"/>
+  <dimension ref="A1:AA454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -47430,6 +47430,1186 @@
       <c r="Z442" s="2" t="inlineStr"/>
       <c r="AA442" s="2" t="inlineStr"/>
     </row>
+    <row r="443">
+      <c r="A443" s="2" t="inlineStr">
+        <is>
+          <t>Foodsngoods O.e.</t>
+        </is>
+      </c>
+      <c r="B443" s="2" t="inlineStr">
+        <is>
+          <t>Foodsngoods O.e.</t>
+        </is>
+      </c>
+      <c r="C443" s="2" t="inlineStr">
+        <is>
+          <t>7413</t>
+        </is>
+      </c>
+      <c r="D443" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E443" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Chania</t>
+        </is>
+      </c>
+      <c r="F443" s="2" t="inlineStr">
+        <is>
+          <t>Region of Crete</t>
+        </is>
+      </c>
+      <c r="G443" s="2" t="inlineStr">
+        <is>
+          <t>6 Antoniou Michelidaki</t>
+        </is>
+      </c>
+      <c r="H443" s="2" t="inlineStr">
+        <is>
+          <t>731 32</t>
+        </is>
+      </c>
+      <c r="I443" s="2" t="inlineStr">
+        <is>
+          <t>https://www.foodsngoods.com</t>
+        </is>
+      </c>
+      <c r="J443" s="2" t="inlineStr"/>
+      <c r="K443" s="2" t="inlineStr"/>
+      <c r="L443" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M443" s="2" t="inlineStr"/>
+      <c r="N443" s="2" t="inlineStr">
+        <is>
+          <t>info@foodsngoods.com</t>
+        </is>
+      </c>
+      <c r="O443" s="2" t="inlineStr">
+        <is>
+          <t>+30 2821 501949</t>
+        </is>
+      </c>
+      <c r="P443" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q443" s="2" t="inlineStr">
+        <is>
+          <t>800331952</t>
+        </is>
+      </c>
+      <c r="R443" s="2" t="inlineStr"/>
+      <c r="S443" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/foodsngoods/</t>
+        </is>
+      </c>
+      <c r="T443" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/foods_n_goods_com</t>
+        </is>
+      </c>
+      <c r="U443" s="2" t="inlineStr"/>
+      <c r="V443" s="2" t="inlineStr"/>
+      <c r="W443" s="2" t="inlineStr">
+        <is>
+          <t>Gurprit Doad</t>
+        </is>
+      </c>
+      <c r="X443" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y443" s="2" t="inlineStr"/>
+      <c r="Z443" s="2" t="inlineStr"/>
+      <c r="AA443" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gurprit-doad-068212203/?originalSubdomain=ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="2" t="inlineStr">
+        <is>
+          <t>Wine Art Sole Commercial S.a.</t>
+        </is>
+      </c>
+      <c r="B444" s="2" t="inlineStr">
+        <is>
+          <t>Wine Art Sole Commercial S.a.</t>
+        </is>
+      </c>
+      <c r="C444" s="2" t="inlineStr">
+        <is>
+          <t>7419</t>
+        </is>
+      </c>
+      <c r="D444" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E444" s="2" t="inlineStr">
+        <is>
+          <t>Ergatikes Polykatoikies Kifisias</t>
+        </is>
+      </c>
+      <c r="F444" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G444" s="2" t="inlineStr">
+        <is>
+          <t>21 Menexedon</t>
+        </is>
+      </c>
+      <c r="H444" s="2" t="inlineStr">
+        <is>
+          <t>145 64</t>
+        </is>
+      </c>
+      <c r="I444" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wineshop.gr</t>
+        </is>
+      </c>
+      <c r="J444" s="2" t="inlineStr"/>
+      <c r="K444" s="2" t="inlineStr"/>
+      <c r="L444" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M444" s="2" t="inlineStr"/>
+      <c r="N444" s="2" t="inlineStr">
+        <is>
+          <t>info@wineshop.gr</t>
+        </is>
+      </c>
+      <c r="O444" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0620 4176</t>
+        </is>
+      </c>
+      <c r="P444" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q444" s="2" t="inlineStr">
+        <is>
+          <t>997103442</t>
+        </is>
+      </c>
+      <c r="R444" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wineshop-gr</t>
+        </is>
+      </c>
+      <c r="S444" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wineshop.gr</t>
+        </is>
+      </c>
+      <c r="T444" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wineshop.gr/</t>
+        </is>
+      </c>
+      <c r="U444" s="2" t="inlineStr"/>
+      <c r="V444" s="2" t="inlineStr"/>
+      <c r="W444" s="2" t="inlineStr"/>
+      <c r="X444" s="2" t="inlineStr"/>
+      <c r="Y444" s="2" t="inlineStr"/>
+      <c r="Z444" s="2" t="inlineStr"/>
+      <c r="AA444" s="2" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="2" t="inlineStr">
+        <is>
+          <t>Unibräu Hellas</t>
+        </is>
+      </c>
+      <c r="B445" s="2" t="inlineStr">
+        <is>
+          <t>Unibräu Hellas</t>
+        </is>
+      </c>
+      <c r="C445" s="2" t="inlineStr">
+        <is>
+          <t>25424</t>
+        </is>
+      </c>
+      <c r="D445" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E445" s="2" t="inlineStr">
+        <is>
+          <t>Spata-Loutsa Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F445" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G445" s="2" t="inlineStr">
+        <is>
+          <t>29 Agiou Dimitriou</t>
+        </is>
+      </c>
+      <c r="H445" s="2" t="inlineStr">
+        <is>
+          <t>190 04</t>
+        </is>
+      </c>
+      <c r="I445" s="2" t="inlineStr">
+        <is>
+          <t>https://www.unibrau.gr</t>
+        </is>
+      </c>
+      <c r="J445" s="2" t="inlineStr"/>
+      <c r="K445" s="2" t="inlineStr"/>
+      <c r="L445" s="2" t="inlineStr"/>
+      <c r="M445" s="2" t="inlineStr"/>
+      <c r="N445" s="2" t="inlineStr">
+        <is>
+          <t>info@unibrau.gr</t>
+        </is>
+      </c>
+      <c r="O445" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0665 4062</t>
+        </is>
+      </c>
+      <c r="P445" s="2" t="inlineStr"/>
+      <c r="Q445" s="2" t="inlineStr"/>
+      <c r="R445" s="2" t="inlineStr"/>
+      <c r="S445" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/unibrau.hellas/</t>
+        </is>
+      </c>
+      <c r="T445" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/unibrau.gr/</t>
+        </is>
+      </c>
+      <c r="U445" s="2" t="inlineStr"/>
+      <c r="V445" s="2" t="inlineStr"/>
+      <c r="W445" s="2" t="inlineStr"/>
+      <c r="X445" s="2" t="inlineStr"/>
+      <c r="Y445" s="2" t="inlineStr"/>
+      <c r="Z445" s="2" t="inlineStr"/>
+      <c r="AA445" s="2" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="2" t="inlineStr">
+        <is>
+          <t>Hebe Argentinian Wineology</t>
+        </is>
+      </c>
+      <c r="B446" s="2" t="inlineStr">
+        <is>
+          <t>Hebe Argentinian Wineology</t>
+        </is>
+      </c>
+      <c r="C446" s="2" t="inlineStr">
+        <is>
+          <t>27842</t>
+        </is>
+      </c>
+      <c r="D446" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E446" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Nea Smyrni</t>
+        </is>
+      </c>
+      <c r="F446" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G446" s="2" t="inlineStr">
+        <is>
+          <t>29 Adramittiou</t>
+        </is>
+      </c>
+      <c r="H446" s="2" t="inlineStr">
+        <is>
+          <t>171 21</t>
+        </is>
+      </c>
+      <c r="I446" s="2" t="inlineStr">
+        <is>
+          <t>http://hebewines.com</t>
+        </is>
+      </c>
+      <c r="J446" s="2" t="inlineStr"/>
+      <c r="K446" s="2" t="inlineStr"/>
+      <c r="L446" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M446" s="2" t="inlineStr"/>
+      <c r="N446" s="2" t="inlineStr">
+        <is>
+          <t>info@hebewines.com</t>
+        </is>
+      </c>
+      <c r="O446" s="2" t="inlineStr"/>
+      <c r="P446" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q446" s="2" t="inlineStr">
+        <is>
+          <t>998468164</t>
+        </is>
+      </c>
+      <c r="R446" s="2" t="inlineStr"/>
+      <c r="S446" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hebewines/</t>
+        </is>
+      </c>
+      <c r="T446" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hebe_wines/</t>
+        </is>
+      </c>
+      <c r="U446" s="2" t="inlineStr"/>
+      <c r="V446" s="2" t="inlineStr"/>
+      <c r="W446" s="2" t="inlineStr">
+        <is>
+          <t>Ivana Cecilia</t>
+        </is>
+      </c>
+      <c r="X446" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y446" s="2" t="inlineStr"/>
+      <c r="Z446" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA446" s="2" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="2" t="inlineStr">
+        <is>
+          <t>Hebe Argentinian Wineology</t>
+        </is>
+      </c>
+      <c r="B447" s="2" t="inlineStr">
+        <is>
+          <t>Hebe Argentinian Wineology</t>
+        </is>
+      </c>
+      <c r="C447" s="2" t="inlineStr">
+        <is>
+          <t>27842</t>
+        </is>
+      </c>
+      <c r="D447" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E447" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Nea Smyrni</t>
+        </is>
+      </c>
+      <c r="F447" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G447" s="2" t="inlineStr">
+        <is>
+          <t>29 Adramittiou</t>
+        </is>
+      </c>
+      <c r="H447" s="2" t="inlineStr">
+        <is>
+          <t>171 21</t>
+        </is>
+      </c>
+      <c r="I447" s="2" t="inlineStr">
+        <is>
+          <t>http://hebewines.com</t>
+        </is>
+      </c>
+      <c r="J447" s="2" t="inlineStr"/>
+      <c r="K447" s="2" t="inlineStr"/>
+      <c r="L447" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M447" s="2" t="inlineStr"/>
+      <c r="N447" s="2" t="inlineStr">
+        <is>
+          <t>info@hebewines.com</t>
+        </is>
+      </c>
+      <c r="O447" s="2" t="inlineStr"/>
+      <c r="P447" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q447" s="2" t="inlineStr">
+        <is>
+          <t>998468164</t>
+        </is>
+      </c>
+      <c r="R447" s="2" t="inlineStr"/>
+      <c r="S447" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hebewines/</t>
+        </is>
+      </c>
+      <c r="T447" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hebe_wines/</t>
+        </is>
+      </c>
+      <c r="U447" s="2" t="inlineStr"/>
+      <c r="V447" s="2" t="inlineStr"/>
+      <c r="W447" s="2" t="inlineStr">
+        <is>
+          <t>Emmanuel Leonardos</t>
+        </is>
+      </c>
+      <c r="X447" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y447" s="2" t="inlineStr"/>
+      <c r="Z447" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA447" s="2" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="2" t="inlineStr">
+        <is>
+          <t>Marinos S.a.</t>
+        </is>
+      </c>
+      <c r="B448" s="2" t="inlineStr">
+        <is>
+          <t>Marinos S.a.</t>
+        </is>
+      </c>
+      <c r="C448" s="2" t="inlineStr">
+        <is>
+          <t>7397</t>
+        </is>
+      </c>
+      <c r="D448" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E448" s="2" t="inlineStr">
+        <is>
+          <t>Rhodes</t>
+        </is>
+      </c>
+      <c r="F448" s="2" t="inlineStr">
+        <is>
+          <t>South Aegean</t>
+        </is>
+      </c>
+      <c r="G448" s="2" t="inlineStr">
+        <is>
+          <t>Ermou 23</t>
+        </is>
+      </c>
+      <c r="H448" s="2" t="inlineStr">
+        <is>
+          <t>851 00</t>
+        </is>
+      </c>
+      <c r="I448" s="2" t="inlineStr">
+        <is>
+          <t>http://marinossa.gr</t>
+        </is>
+      </c>
+      <c r="J448" s="2" t="inlineStr"/>
+      <c r="K448" s="2" t="inlineStr"/>
+      <c r="L448" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M448" s="2" t="inlineStr"/>
+      <c r="N448" s="2" t="inlineStr">
+        <is>
+          <t>info@marinossa.gr</t>
+        </is>
+      </c>
+      <c r="O448" s="2" t="inlineStr">
+        <is>
+          <t>+30 2241 077141</t>
+        </is>
+      </c>
+      <c r="P448" s="2" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="Q448" s="2" t="inlineStr">
+        <is>
+          <t>094272005</t>
+        </is>
+      </c>
+      <c r="R448" s="2" t="inlineStr"/>
+      <c r="S448" s="2" t="inlineStr"/>
+      <c r="T448" s="2" t="inlineStr"/>
+      <c r="U448" s="2" t="inlineStr"/>
+      <c r="V448" s="2" t="inlineStr"/>
+      <c r="W448" s="2" t="inlineStr">
+        <is>
+          <t>Theofilos Marinos</t>
+        </is>
+      </c>
+      <c r="X448" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y448" s="2" t="inlineStr"/>
+      <c r="Z448" s="2" t="inlineStr"/>
+      <c r="AA448" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/theofilos-marinos-78296664/</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="2" t="inlineStr">
+        <is>
+          <t>Tsianakas Konstantinos Oinodia Sommelier</t>
+        </is>
+      </c>
+      <c r="B449" s="2" t="inlineStr">
+        <is>
+          <t>Tsianakas Konstantinos Oinodia Sommelier</t>
+        </is>
+      </c>
+      <c r="C449" s="2" t="inlineStr">
+        <is>
+          <t>24830</t>
+        </is>
+      </c>
+      <c r="D449" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E449" s="2" t="inlineStr">
+        <is>
+          <t>Municipal Unit of Papagou</t>
+        </is>
+      </c>
+      <c r="F449" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G449" s="2" t="inlineStr">
+        <is>
+          <t>55 Konstantinou Versi</t>
+        </is>
+      </c>
+      <c r="H449" s="2" t="inlineStr">
+        <is>
+          <t>156 69</t>
+        </is>
+      </c>
+      <c r="I449" s="2" t="inlineStr">
+        <is>
+          <t>http://www.oinodia.com</t>
+        </is>
+      </c>
+      <c r="J449" s="2" t="inlineStr"/>
+      <c r="K449" s="2" t="inlineStr"/>
+      <c r="L449" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M449" s="2" t="inlineStr"/>
+      <c r="N449" s="2" t="inlineStr">
+        <is>
+          <t>k.tsianakas@oinodia.com</t>
+        </is>
+      </c>
+      <c r="O449" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0653 5990</t>
+        </is>
+      </c>
+      <c r="P449" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q449" s="2" t="inlineStr">
+        <is>
+          <t>119203168</t>
+        </is>
+      </c>
+      <c r="R449" s="2" t="inlineStr"/>
+      <c r="S449" s="2" t="inlineStr"/>
+      <c r="T449" s="2" t="inlineStr"/>
+      <c r="U449" s="2" t="inlineStr"/>
+      <c r="V449" s="2" t="inlineStr"/>
+      <c r="W449" s="2" t="inlineStr">
+        <is>
+          <t>Konstantine Tsianakas</t>
+        </is>
+      </c>
+      <c r="X449" s="2" t="inlineStr">
+        <is>
+          <t>Sommelier</t>
+        </is>
+      </c>
+      <c r="Y449" s="2" t="inlineStr"/>
+      <c r="Z449" s="2" t="inlineStr"/>
+      <c r="AA449" s="2" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="2" t="inlineStr">
+        <is>
+          <t>Tsianakas Konstantinos Oinodia Sommelier</t>
+        </is>
+      </c>
+      <c r="B450" s="2" t="inlineStr">
+        <is>
+          <t>Tsianakas Konstantinos Oinodia Sommelier</t>
+        </is>
+      </c>
+      <c r="C450" s="2" t="inlineStr">
+        <is>
+          <t>24830</t>
+        </is>
+      </c>
+      <c r="D450" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E450" s="2" t="inlineStr">
+        <is>
+          <t>Municipal Unit of Papagou</t>
+        </is>
+      </c>
+      <c r="F450" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G450" s="2" t="inlineStr">
+        <is>
+          <t>55 Konstantinou Versi</t>
+        </is>
+      </c>
+      <c r="H450" s="2" t="inlineStr">
+        <is>
+          <t>156 69</t>
+        </is>
+      </c>
+      <c r="I450" s="2" t="inlineStr">
+        <is>
+          <t>http://www.oinodia.com</t>
+        </is>
+      </c>
+      <c r="J450" s="2" t="inlineStr"/>
+      <c r="K450" s="2" t="inlineStr"/>
+      <c r="L450" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M450" s="2" t="inlineStr"/>
+      <c r="N450" s="2" t="inlineStr">
+        <is>
+          <t>k.tsianakas@oinodia.com</t>
+        </is>
+      </c>
+      <c r="O450" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0653 5990</t>
+        </is>
+      </c>
+      <c r="P450" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q450" s="2" t="inlineStr">
+        <is>
+          <t>119203168</t>
+        </is>
+      </c>
+      <c r="R450" s="2" t="inlineStr"/>
+      <c r="S450" s="2" t="inlineStr"/>
+      <c r="T450" s="2" t="inlineStr"/>
+      <c r="U450" s="2" t="inlineStr"/>
+      <c r="V450" s="2" t="inlineStr"/>
+      <c r="W450" s="2" t="inlineStr">
+        <is>
+          <t>Spyridon Demertzis</t>
+        </is>
+      </c>
+      <c r="X450" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner</t>
+        </is>
+      </c>
+      <c r="Y450" s="2" t="inlineStr"/>
+      <c r="Z450" s="2" t="inlineStr"/>
+      <c r="AA450" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/spyridon-demertzis-b8295b5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" s="2" t="inlineStr">
+        <is>
+          <t>Mavrikos Imports S.a.</t>
+        </is>
+      </c>
+      <c r="B451" s="2" t="inlineStr">
+        <is>
+          <t>Mavrikos Imports S.a.</t>
+        </is>
+      </c>
+      <c r="C451" s="2" t="inlineStr">
+        <is>
+          <t>7398</t>
+        </is>
+      </c>
+      <c r="D451" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E451" s="2" t="inlineStr">
+        <is>
+          <t>Piraeus</t>
+        </is>
+      </c>
+      <c r="F451" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G451" s="2" t="inlineStr">
+        <is>
+          <t>7 Naxou</t>
+        </is>
+      </c>
+      <c r="H451" s="2" t="inlineStr">
+        <is>
+          <t>185 41</t>
+        </is>
+      </c>
+      <c r="I451" s="2" t="inlineStr">
+        <is>
+          <t>https://mavrikosimports.gr</t>
+        </is>
+      </c>
+      <c r="J451" s="2" t="inlineStr"/>
+      <c r="K451" s="2" t="inlineStr"/>
+      <c r="L451" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M451" s="2" t="inlineStr"/>
+      <c r="N451" s="2" t="inlineStr">
+        <is>
+          <t>orddep@mavrikosimports.gr</t>
+        </is>
+      </c>
+      <c r="O451" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0481 3064</t>
+        </is>
+      </c>
+      <c r="P451" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="Q451" s="2" t="inlineStr">
+        <is>
+          <t>094047465</t>
+        </is>
+      </c>
+      <c r="R451" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mavrikos-imports-s-a/</t>
+        </is>
+      </c>
+      <c r="S451" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/mavrikosimports</t>
+        </is>
+      </c>
+      <c r="T451" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/imports_mavrikos</t>
+        </is>
+      </c>
+      <c r="U451" s="2" t="inlineStr"/>
+      <c r="V451" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@mavrikosimports</t>
+        </is>
+      </c>
+      <c r="W451" s="2" t="inlineStr">
+        <is>
+          <t>MARIA MAVRIKOS</t>
+        </is>
+      </c>
+      <c r="X451" s="2" t="inlineStr">
+        <is>
+          <t>Export and import manager</t>
+        </is>
+      </c>
+      <c r="Y451" s="2" t="inlineStr"/>
+      <c r="Z451" s="2" t="inlineStr"/>
+      <c r="AA451" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maria-mavrikos-8943b3395/</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" s="2" t="inlineStr">
+        <is>
+          <t>Foodrinco S.a.</t>
+        </is>
+      </c>
+      <c r="B452" s="2" t="inlineStr">
+        <is>
+          <t>Foodrinco S.a.</t>
+        </is>
+      </c>
+      <c r="C452" s="2" t="inlineStr">
+        <is>
+          <t>22331</t>
+        </is>
+      </c>
+      <c r="D452" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E452" s="2" t="inlineStr">
+        <is>
+          <t>Kryoneri Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F452" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G452" s="2" t="inlineStr">
+        <is>
+          <t>132 Lefkis</t>
+        </is>
+      </c>
+      <c r="H452" s="2" t="inlineStr">
+        <is>
+          <t>145 68</t>
+        </is>
+      </c>
+      <c r="I452" s="2" t="inlineStr">
+        <is>
+          <t>https://foodrinco.gr</t>
+        </is>
+      </c>
+      <c r="J452" s="2" t="inlineStr"/>
+      <c r="K452" s="2" t="inlineStr"/>
+      <c r="L452" s="2" t="inlineStr"/>
+      <c r="M452" s="2" t="inlineStr"/>
+      <c r="N452" s="2" t="inlineStr">
+        <is>
+          <t>info@foodrinco.gr</t>
+        </is>
+      </c>
+      <c r="O452" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 6400 0200</t>
+        </is>
+      </c>
+      <c r="P452" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q452" s="2" t="inlineStr">
+        <is>
+          <t>094430257</t>
+        </is>
+      </c>
+      <c r="R452" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vytogiannis-group-of-companies/</t>
+        </is>
+      </c>
+      <c r="S452" s="2" t="inlineStr"/>
+      <c r="T452" s="2" t="inlineStr"/>
+      <c r="U452" s="2" t="inlineStr"/>
+      <c r="V452" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/foodrinco</t>
+        </is>
+      </c>
+      <c r="W452" s="2" t="inlineStr">
+        <is>
+          <t>George Vitogiannis</t>
+        </is>
+      </c>
+      <c r="X452" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y452" s="2" t="inlineStr"/>
+      <c r="Z452" s="2" t="inlineStr"/>
+      <c r="AA452" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/george-vitogiannis-a041753/</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>Foodrinco S.a.</t>
+        </is>
+      </c>
+      <c r="B453" s="2" t="inlineStr">
+        <is>
+          <t>Foodrinco S.a.</t>
+        </is>
+      </c>
+      <c r="C453" s="2" t="inlineStr">
+        <is>
+          <t>22331</t>
+        </is>
+      </c>
+      <c r="D453" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E453" s="2" t="inlineStr">
+        <is>
+          <t>Kryoneri Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F453" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G453" s="2" t="inlineStr">
+        <is>
+          <t>132 Lefkis</t>
+        </is>
+      </c>
+      <c r="H453" s="2" t="inlineStr">
+        <is>
+          <t>145 68</t>
+        </is>
+      </c>
+      <c r="I453" s="2" t="inlineStr">
+        <is>
+          <t>https://foodrinco.gr</t>
+        </is>
+      </c>
+      <c r="J453" s="2" t="inlineStr"/>
+      <c r="K453" s="2" t="inlineStr"/>
+      <c r="L453" s="2" t="inlineStr"/>
+      <c r="M453" s="2" t="inlineStr"/>
+      <c r="N453" s="2" t="inlineStr">
+        <is>
+          <t>info@foodrinco.gr</t>
+        </is>
+      </c>
+      <c r="O453" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 6400 0200</t>
+        </is>
+      </c>
+      <c r="P453" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q453" s="2" t="inlineStr">
+        <is>
+          <t>094430257</t>
+        </is>
+      </c>
+      <c r="R453" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vytogiannis-group-of-companies/</t>
+        </is>
+      </c>
+      <c r="S453" s="2" t="inlineStr"/>
+      <c r="T453" s="2" t="inlineStr"/>
+      <c r="U453" s="2" t="inlineStr"/>
+      <c r="V453" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/foodrinco</t>
+        </is>
+      </c>
+      <c r="W453" s="2" t="inlineStr">
+        <is>
+          <t>Stelios Tiktopoulos</t>
+        </is>
+      </c>
+      <c r="X453" s="2" t="inlineStr">
+        <is>
+          <t>Area Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y453" s="2" t="inlineStr"/>
+      <c r="Z453" s="2" t="inlineStr"/>
+      <c r="AA453" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stelios-tiktopoulos-6bb06934/</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" s="2" t="inlineStr">
+        <is>
+          <t>L. Patroni And Co. E.e.</t>
+        </is>
+      </c>
+      <c r="B454" s="2" t="inlineStr">
+        <is>
+          <t>L. Patroni And Co. E.e.</t>
+        </is>
+      </c>
+      <c r="C454" s="2" t="inlineStr">
+        <is>
+          <t>7418</t>
+        </is>
+      </c>
+      <c r="D454" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E454" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Marousi</t>
+        </is>
+      </c>
+      <c r="F454" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G454" s="2" t="inlineStr">
+        <is>
+          <t>37A Leoforos Kifisias</t>
+        </is>
+      </c>
+      <c r="H454" s="2" t="inlineStr">
+        <is>
+          <t>151 23</t>
+        </is>
+      </c>
+      <c r="I454" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lesconnaisseurs.gr</t>
+        </is>
+      </c>
+      <c r="J454" s="2" t="inlineStr"/>
+      <c r="K454" s="2" t="inlineStr"/>
+      <c r="L454" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M454" s="2" t="inlineStr"/>
+      <c r="N454" s="2" t="inlineStr">
+        <is>
+          <t>info@lesconnaisseurs.gr</t>
+        </is>
+      </c>
+      <c r="O454" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0723 9195</t>
+        </is>
+      </c>
+      <c r="P454" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="Q454" s="2" t="inlineStr">
+        <is>
+          <t>093693780</t>
+        </is>
+      </c>
+      <c r="R454" s="2" t="inlineStr"/>
+      <c r="S454" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lesconnaisseurs.gr/</t>
+        </is>
+      </c>
+      <c r="T454" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lesconnaisseurs/</t>
+        </is>
+      </c>
+      <c r="U454" s="2" t="inlineStr"/>
+      <c r="V454" s="2" t="inlineStr"/>
+      <c r="W454" s="2" t="inlineStr"/>
+      <c r="X454" s="2" t="inlineStr"/>
+      <c r="Y454" s="2" t="inlineStr"/>
+      <c r="Z454" s="2" t="inlineStr"/>
+      <c r="AA454" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Greece.xlsx
+++ b/BWI/bestwine_output/bestwine_Greece.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA454"/>
+  <dimension ref="A1:AA466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -48610,6 +48610,1186 @@
       <c r="Z454" s="2" t="inlineStr"/>
       <c r="AA454" s="2" t="inlineStr"/>
     </row>
+    <row r="455">
+      <c r="A455" s="2" t="inlineStr">
+        <is>
+          <t>Foodsngoods O.e.</t>
+        </is>
+      </c>
+      <c r="B455" s="2" t="inlineStr">
+        <is>
+          <t>Foodsngoods O.e.</t>
+        </is>
+      </c>
+      <c r="C455" s="2" t="inlineStr">
+        <is>
+          <t>7413</t>
+        </is>
+      </c>
+      <c r="D455" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E455" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Chania</t>
+        </is>
+      </c>
+      <c r="F455" s="2" t="inlineStr">
+        <is>
+          <t>Region of Crete</t>
+        </is>
+      </c>
+      <c r="G455" s="2" t="inlineStr">
+        <is>
+          <t>6 Antoniou Michelidaki</t>
+        </is>
+      </c>
+      <c r="H455" s="2" t="inlineStr">
+        <is>
+          <t>731 32</t>
+        </is>
+      </c>
+      <c r="I455" s="2" t="inlineStr">
+        <is>
+          <t>https://www.foodsngoods.com</t>
+        </is>
+      </c>
+      <c r="J455" s="2" t="inlineStr"/>
+      <c r="K455" s="2" t="inlineStr"/>
+      <c r="L455" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M455" s="2" t="inlineStr"/>
+      <c r="N455" s="2" t="inlineStr">
+        <is>
+          <t>info@foodsngoods.com</t>
+        </is>
+      </c>
+      <c r="O455" s="2" t="inlineStr">
+        <is>
+          <t>+30 2821 501949</t>
+        </is>
+      </c>
+      <c r="P455" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q455" s="2" t="inlineStr">
+        <is>
+          <t>800331952</t>
+        </is>
+      </c>
+      <c r="R455" s="2" t="inlineStr"/>
+      <c r="S455" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/foodsngoods/</t>
+        </is>
+      </c>
+      <c r="T455" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/foods_n_goods_com</t>
+        </is>
+      </c>
+      <c r="U455" s="2" t="inlineStr"/>
+      <c r="V455" s="2" t="inlineStr"/>
+      <c r="W455" s="2" t="inlineStr">
+        <is>
+          <t>Gurprit Doad</t>
+        </is>
+      </c>
+      <c r="X455" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y455" s="2" t="inlineStr"/>
+      <c r="Z455" s="2" t="inlineStr"/>
+      <c r="AA455" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/gurprit-doad-068212203/?originalSubdomain=ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" s="2" t="inlineStr">
+        <is>
+          <t>Wine Art Sole Commercial S.a.</t>
+        </is>
+      </c>
+      <c r="B456" s="2" t="inlineStr">
+        <is>
+          <t>Wine Art Sole Commercial S.a.</t>
+        </is>
+      </c>
+      <c r="C456" s="2" t="inlineStr">
+        <is>
+          <t>7419</t>
+        </is>
+      </c>
+      <c r="D456" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E456" s="2" t="inlineStr">
+        <is>
+          <t>Ergatikes Polykatoikies Kifisias</t>
+        </is>
+      </c>
+      <c r="F456" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G456" s="2" t="inlineStr">
+        <is>
+          <t>21 Menexedon</t>
+        </is>
+      </c>
+      <c r="H456" s="2" t="inlineStr">
+        <is>
+          <t>145 64</t>
+        </is>
+      </c>
+      <c r="I456" s="2" t="inlineStr">
+        <is>
+          <t>https://www.wineshop.gr</t>
+        </is>
+      </c>
+      <c r="J456" s="2" t="inlineStr"/>
+      <c r="K456" s="2" t="inlineStr"/>
+      <c r="L456" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M456" s="2" t="inlineStr"/>
+      <c r="N456" s="2" t="inlineStr">
+        <is>
+          <t>info@wineshop.gr</t>
+        </is>
+      </c>
+      <c r="O456" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0620 4176</t>
+        </is>
+      </c>
+      <c r="P456" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q456" s="2" t="inlineStr">
+        <is>
+          <t>997103442</t>
+        </is>
+      </c>
+      <c r="R456" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/wineshop-gr</t>
+        </is>
+      </c>
+      <c r="S456" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/wineshop.gr</t>
+        </is>
+      </c>
+      <c r="T456" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wineshop.gr/</t>
+        </is>
+      </c>
+      <c r="U456" s="2" t="inlineStr"/>
+      <c r="V456" s="2" t="inlineStr"/>
+      <c r="W456" s="2" t="inlineStr"/>
+      <c r="X456" s="2" t="inlineStr"/>
+      <c r="Y456" s="2" t="inlineStr"/>
+      <c r="Z456" s="2" t="inlineStr"/>
+      <c r="AA456" s="2" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="2" t="inlineStr">
+        <is>
+          <t>Unibräu Hellas</t>
+        </is>
+      </c>
+      <c r="B457" s="2" t="inlineStr">
+        <is>
+          <t>Unibräu Hellas</t>
+        </is>
+      </c>
+      <c r="C457" s="2" t="inlineStr">
+        <is>
+          <t>25424</t>
+        </is>
+      </c>
+      <c r="D457" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E457" s="2" t="inlineStr">
+        <is>
+          <t>Spata-Loutsa Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F457" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G457" s="2" t="inlineStr">
+        <is>
+          <t>29 Agiou Dimitriou</t>
+        </is>
+      </c>
+      <c r="H457" s="2" t="inlineStr">
+        <is>
+          <t>190 04</t>
+        </is>
+      </c>
+      <c r="I457" s="2" t="inlineStr">
+        <is>
+          <t>https://www.unibrau.gr</t>
+        </is>
+      </c>
+      <c r="J457" s="2" t="inlineStr"/>
+      <c r="K457" s="2" t="inlineStr"/>
+      <c r="L457" s="2" t="inlineStr"/>
+      <c r="M457" s="2" t="inlineStr"/>
+      <c r="N457" s="2" t="inlineStr">
+        <is>
+          <t>info@unibrau.gr</t>
+        </is>
+      </c>
+      <c r="O457" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0665 4062</t>
+        </is>
+      </c>
+      <c r="P457" s="2" t="inlineStr"/>
+      <c r="Q457" s="2" t="inlineStr"/>
+      <c r="R457" s="2" t="inlineStr"/>
+      <c r="S457" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/unibrau.hellas/</t>
+        </is>
+      </c>
+      <c r="T457" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/unibrau.gr/</t>
+        </is>
+      </c>
+      <c r="U457" s="2" t="inlineStr"/>
+      <c r="V457" s="2" t="inlineStr"/>
+      <c r="W457" s="2" t="inlineStr"/>
+      <c r="X457" s="2" t="inlineStr"/>
+      <c r="Y457" s="2" t="inlineStr"/>
+      <c r="Z457" s="2" t="inlineStr"/>
+      <c r="AA457" s="2" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="2" t="inlineStr">
+        <is>
+          <t>Hebe Argentinian Wineology</t>
+        </is>
+      </c>
+      <c r="B458" s="2" t="inlineStr">
+        <is>
+          <t>Hebe Argentinian Wineology</t>
+        </is>
+      </c>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>27842</t>
+        </is>
+      </c>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Nea Smyrni</t>
+        </is>
+      </c>
+      <c r="F458" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G458" s="2" t="inlineStr">
+        <is>
+          <t>29 Adramittiou</t>
+        </is>
+      </c>
+      <c r="H458" s="2" t="inlineStr">
+        <is>
+          <t>171 21</t>
+        </is>
+      </c>
+      <c r="I458" s="2" t="inlineStr">
+        <is>
+          <t>http://hebewines.com</t>
+        </is>
+      </c>
+      <c r="J458" s="2" t="inlineStr"/>
+      <c r="K458" s="2" t="inlineStr"/>
+      <c r="L458" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M458" s="2" t="inlineStr"/>
+      <c r="N458" s="2" t="inlineStr">
+        <is>
+          <t>info@hebewines.com</t>
+        </is>
+      </c>
+      <c r="O458" s="2" t="inlineStr"/>
+      <c r="P458" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q458" s="2" t="inlineStr">
+        <is>
+          <t>998468164</t>
+        </is>
+      </c>
+      <c r="R458" s="2" t="inlineStr"/>
+      <c r="S458" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hebewines/</t>
+        </is>
+      </c>
+      <c r="T458" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hebe_wines/</t>
+        </is>
+      </c>
+      <c r="U458" s="2" t="inlineStr"/>
+      <c r="V458" s="2" t="inlineStr"/>
+      <c r="W458" s="2" t="inlineStr">
+        <is>
+          <t>Ivana Cecilia</t>
+        </is>
+      </c>
+      <c r="X458" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y458" s="2" t="inlineStr"/>
+      <c r="Z458" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA458" s="2" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="2" t="inlineStr">
+        <is>
+          <t>Hebe Argentinian Wineology</t>
+        </is>
+      </c>
+      <c r="B459" s="2" t="inlineStr">
+        <is>
+          <t>Hebe Argentinian Wineology</t>
+        </is>
+      </c>
+      <c r="C459" s="2" t="inlineStr">
+        <is>
+          <t>27842</t>
+        </is>
+      </c>
+      <c r="D459" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E459" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Nea Smyrni</t>
+        </is>
+      </c>
+      <c r="F459" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G459" s="2" t="inlineStr">
+        <is>
+          <t>29 Adramittiou</t>
+        </is>
+      </c>
+      <c r="H459" s="2" t="inlineStr">
+        <is>
+          <t>171 21</t>
+        </is>
+      </c>
+      <c r="I459" s="2" t="inlineStr">
+        <is>
+          <t>http://hebewines.com</t>
+        </is>
+      </c>
+      <c r="J459" s="2" t="inlineStr"/>
+      <c r="K459" s="2" t="inlineStr"/>
+      <c r="L459" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M459" s="2" t="inlineStr"/>
+      <c r="N459" s="2" t="inlineStr">
+        <is>
+          <t>info@hebewines.com</t>
+        </is>
+      </c>
+      <c r="O459" s="2" t="inlineStr"/>
+      <c r="P459" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q459" s="2" t="inlineStr">
+        <is>
+          <t>998468164</t>
+        </is>
+      </c>
+      <c r="R459" s="2" t="inlineStr"/>
+      <c r="S459" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hebewines/</t>
+        </is>
+      </c>
+      <c r="T459" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hebe_wines/</t>
+        </is>
+      </c>
+      <c r="U459" s="2" t="inlineStr"/>
+      <c r="V459" s="2" t="inlineStr"/>
+      <c r="W459" s="2" t="inlineStr">
+        <is>
+          <t>Emmanuel Leonardos</t>
+        </is>
+      </c>
+      <c r="X459" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y459" s="2" t="inlineStr"/>
+      <c r="Z459" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA459" s="2" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="2" t="inlineStr">
+        <is>
+          <t>Marinos S.a.</t>
+        </is>
+      </c>
+      <c r="B460" s="2" t="inlineStr">
+        <is>
+          <t>Marinos S.a.</t>
+        </is>
+      </c>
+      <c r="C460" s="2" t="inlineStr">
+        <is>
+          <t>7397</t>
+        </is>
+      </c>
+      <c r="D460" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E460" s="2" t="inlineStr">
+        <is>
+          <t>Rhodes</t>
+        </is>
+      </c>
+      <c r="F460" s="2" t="inlineStr">
+        <is>
+          <t>South Aegean</t>
+        </is>
+      </c>
+      <c r="G460" s="2" t="inlineStr">
+        <is>
+          <t>Ermou 23</t>
+        </is>
+      </c>
+      <c r="H460" s="2" t="inlineStr">
+        <is>
+          <t>851 00</t>
+        </is>
+      </c>
+      <c r="I460" s="2" t="inlineStr">
+        <is>
+          <t>http://marinossa.gr</t>
+        </is>
+      </c>
+      <c r="J460" s="2" t="inlineStr"/>
+      <c r="K460" s="2" t="inlineStr"/>
+      <c r="L460" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M460" s="2" t="inlineStr"/>
+      <c r="N460" s="2" t="inlineStr">
+        <is>
+          <t>info@marinossa.gr</t>
+        </is>
+      </c>
+      <c r="O460" s="2" t="inlineStr">
+        <is>
+          <t>+30 2241 077141</t>
+        </is>
+      </c>
+      <c r="P460" s="2" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="Q460" s="2" t="inlineStr">
+        <is>
+          <t>094272005</t>
+        </is>
+      </c>
+      <c r="R460" s="2" t="inlineStr"/>
+      <c r="S460" s="2" t="inlineStr"/>
+      <c r="T460" s="2" t="inlineStr"/>
+      <c r="U460" s="2" t="inlineStr"/>
+      <c r="V460" s="2" t="inlineStr"/>
+      <c r="W460" s="2" t="inlineStr">
+        <is>
+          <t>Theofilos Marinos</t>
+        </is>
+      </c>
+      <c r="X460" s="2" t="inlineStr">
+        <is>
+          <t>President</t>
+        </is>
+      </c>
+      <c r="Y460" s="2" t="inlineStr"/>
+      <c r="Z460" s="2" t="inlineStr"/>
+      <c r="AA460" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/theofilos-marinos-78296664/</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="2" t="inlineStr">
+        <is>
+          <t>Tsianakas Konstantinos Oinodia Sommelier</t>
+        </is>
+      </c>
+      <c r="B461" s="2" t="inlineStr">
+        <is>
+          <t>Tsianakas Konstantinos Oinodia Sommelier</t>
+        </is>
+      </c>
+      <c r="C461" s="2" t="inlineStr">
+        <is>
+          <t>24830</t>
+        </is>
+      </c>
+      <c r="D461" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E461" s="2" t="inlineStr">
+        <is>
+          <t>Municipal Unit of Papagou</t>
+        </is>
+      </c>
+      <c r="F461" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G461" s="2" t="inlineStr">
+        <is>
+          <t>55 Konstantinou Versi</t>
+        </is>
+      </c>
+      <c r="H461" s="2" t="inlineStr">
+        <is>
+          <t>156 69</t>
+        </is>
+      </c>
+      <c r="I461" s="2" t="inlineStr">
+        <is>
+          <t>http://www.oinodia.com</t>
+        </is>
+      </c>
+      <c r="J461" s="2" t="inlineStr"/>
+      <c r="K461" s="2" t="inlineStr"/>
+      <c r="L461" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M461" s="2" t="inlineStr"/>
+      <c r="N461" s="2" t="inlineStr">
+        <is>
+          <t>k.tsianakas@oinodia.com</t>
+        </is>
+      </c>
+      <c r="O461" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0653 5990</t>
+        </is>
+      </c>
+      <c r="P461" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q461" s="2" t="inlineStr">
+        <is>
+          <t>119203168</t>
+        </is>
+      </c>
+      <c r="R461" s="2" t="inlineStr"/>
+      <c r="S461" s="2" t="inlineStr"/>
+      <c r="T461" s="2" t="inlineStr"/>
+      <c r="U461" s="2" t="inlineStr"/>
+      <c r="V461" s="2" t="inlineStr"/>
+      <c r="W461" s="2" t="inlineStr">
+        <is>
+          <t>Konstantine Tsianakas</t>
+        </is>
+      </c>
+      <c r="X461" s="2" t="inlineStr">
+        <is>
+          <t>Sommelier</t>
+        </is>
+      </c>
+      <c r="Y461" s="2" t="inlineStr"/>
+      <c r="Z461" s="2" t="inlineStr"/>
+      <c r="AA461" s="2" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="2" t="inlineStr">
+        <is>
+          <t>Tsianakas Konstantinos Oinodia Sommelier</t>
+        </is>
+      </c>
+      <c r="B462" s="2" t="inlineStr">
+        <is>
+          <t>Tsianakas Konstantinos Oinodia Sommelier</t>
+        </is>
+      </c>
+      <c r="C462" s="2" t="inlineStr">
+        <is>
+          <t>24830</t>
+        </is>
+      </c>
+      <c r="D462" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E462" s="2" t="inlineStr">
+        <is>
+          <t>Municipal Unit of Papagou</t>
+        </is>
+      </c>
+      <c r="F462" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G462" s="2" t="inlineStr">
+        <is>
+          <t>55 Konstantinou Versi</t>
+        </is>
+      </c>
+      <c r="H462" s="2" t="inlineStr">
+        <is>
+          <t>156 69</t>
+        </is>
+      </c>
+      <c r="I462" s="2" t="inlineStr">
+        <is>
+          <t>http://www.oinodia.com</t>
+        </is>
+      </c>
+      <c r="J462" s="2" t="inlineStr"/>
+      <c r="K462" s="2" t="inlineStr"/>
+      <c r="L462" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M462" s="2" t="inlineStr"/>
+      <c r="N462" s="2" t="inlineStr">
+        <is>
+          <t>k.tsianakas@oinodia.com</t>
+        </is>
+      </c>
+      <c r="O462" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0653 5990</t>
+        </is>
+      </c>
+      <c r="P462" s="2" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="Q462" s="2" t="inlineStr">
+        <is>
+          <t>119203168</t>
+        </is>
+      </c>
+      <c r="R462" s="2" t="inlineStr"/>
+      <c r="S462" s="2" t="inlineStr"/>
+      <c r="T462" s="2" t="inlineStr"/>
+      <c r="U462" s="2" t="inlineStr"/>
+      <c r="V462" s="2" t="inlineStr"/>
+      <c r="W462" s="2" t="inlineStr">
+        <is>
+          <t>Spyridon Demertzis</t>
+        </is>
+      </c>
+      <c r="X462" s="2" t="inlineStr">
+        <is>
+          <t>Co-owner</t>
+        </is>
+      </c>
+      <c r="Y462" s="2" t="inlineStr"/>
+      <c r="Z462" s="2" t="inlineStr"/>
+      <c r="AA462" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/spyridon-demertzis-b8295b5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="2" t="inlineStr">
+        <is>
+          <t>Mavrikos Imports S.a.</t>
+        </is>
+      </c>
+      <c r="B463" s="2" t="inlineStr">
+        <is>
+          <t>Mavrikos Imports S.a.</t>
+        </is>
+      </c>
+      <c r="C463" s="2" t="inlineStr">
+        <is>
+          <t>7398</t>
+        </is>
+      </c>
+      <c r="D463" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E463" s="2" t="inlineStr">
+        <is>
+          <t>Piraeus</t>
+        </is>
+      </c>
+      <c r="F463" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G463" s="2" t="inlineStr">
+        <is>
+          <t>7 Naxou</t>
+        </is>
+      </c>
+      <c r="H463" s="2" t="inlineStr">
+        <is>
+          <t>185 41</t>
+        </is>
+      </c>
+      <c r="I463" s="2" t="inlineStr">
+        <is>
+          <t>https://mavrikosimports.gr</t>
+        </is>
+      </c>
+      <c r="J463" s="2" t="inlineStr"/>
+      <c r="K463" s="2" t="inlineStr"/>
+      <c r="L463" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M463" s="2" t="inlineStr"/>
+      <c r="N463" s="2" t="inlineStr">
+        <is>
+          <t>orddep@mavrikosimports.gr</t>
+        </is>
+      </c>
+      <c r="O463" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0481 3064</t>
+        </is>
+      </c>
+      <c r="P463" s="2" t="inlineStr">
+        <is>
+          <t>1975</t>
+        </is>
+      </c>
+      <c r="Q463" s="2" t="inlineStr">
+        <is>
+          <t>094047465</t>
+        </is>
+      </c>
+      <c r="R463" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/mavrikos-imports-s-a/</t>
+        </is>
+      </c>
+      <c r="S463" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/mavrikosimports</t>
+        </is>
+      </c>
+      <c r="T463" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/imports_mavrikos</t>
+        </is>
+      </c>
+      <c r="U463" s="2" t="inlineStr"/>
+      <c r="V463" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@mavrikosimports</t>
+        </is>
+      </c>
+      <c r="W463" s="2" t="inlineStr">
+        <is>
+          <t>MARIA MAVRIKOS</t>
+        </is>
+      </c>
+      <c r="X463" s="2" t="inlineStr">
+        <is>
+          <t>Export and import manager</t>
+        </is>
+      </c>
+      <c r="Y463" s="2" t="inlineStr"/>
+      <c r="Z463" s="2" t="inlineStr"/>
+      <c r="AA463" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/maria-mavrikos-8943b3395/</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>Foodrinco S.a.</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t>Foodrinco S.a.</t>
+        </is>
+      </c>
+      <c r="C464" s="2" t="inlineStr">
+        <is>
+          <t>22331</t>
+        </is>
+      </c>
+      <c r="D464" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E464" s="2" t="inlineStr">
+        <is>
+          <t>Kryoneri Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F464" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G464" s="2" t="inlineStr">
+        <is>
+          <t>132 Lefkis</t>
+        </is>
+      </c>
+      <c r="H464" s="2" t="inlineStr">
+        <is>
+          <t>145 68</t>
+        </is>
+      </c>
+      <c r="I464" s="2" t="inlineStr">
+        <is>
+          <t>https://foodrinco.gr</t>
+        </is>
+      </c>
+      <c r="J464" s="2" t="inlineStr"/>
+      <c r="K464" s="2" t="inlineStr"/>
+      <c r="L464" s="2" t="inlineStr"/>
+      <c r="M464" s="2" t="inlineStr"/>
+      <c r="N464" s="2" t="inlineStr">
+        <is>
+          <t>info@foodrinco.gr</t>
+        </is>
+      </c>
+      <c r="O464" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 6400 0200</t>
+        </is>
+      </c>
+      <c r="P464" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q464" s="2" t="inlineStr">
+        <is>
+          <t>094430257</t>
+        </is>
+      </c>
+      <c r="R464" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vytogiannis-group-of-companies/</t>
+        </is>
+      </c>
+      <c r="S464" s="2" t="inlineStr"/>
+      <c r="T464" s="2" t="inlineStr"/>
+      <c r="U464" s="2" t="inlineStr"/>
+      <c r="V464" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/foodrinco</t>
+        </is>
+      </c>
+      <c r="W464" s="2" t="inlineStr">
+        <is>
+          <t>George Vitogiannis</t>
+        </is>
+      </c>
+      <c r="X464" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y464" s="2" t="inlineStr"/>
+      <c r="Z464" s="2" t="inlineStr"/>
+      <c r="AA464" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/george-vitogiannis-a041753/</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" s="2" t="inlineStr">
+        <is>
+          <t>Foodrinco S.a.</t>
+        </is>
+      </c>
+      <c r="B465" s="2" t="inlineStr">
+        <is>
+          <t>Foodrinco S.a.</t>
+        </is>
+      </c>
+      <c r="C465" s="2" t="inlineStr">
+        <is>
+          <t>22331</t>
+        </is>
+      </c>
+      <c r="D465" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E465" s="2" t="inlineStr">
+        <is>
+          <t>Kryoneri Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F465" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G465" s="2" t="inlineStr">
+        <is>
+          <t>132 Lefkis</t>
+        </is>
+      </c>
+      <c r="H465" s="2" t="inlineStr">
+        <is>
+          <t>145 68</t>
+        </is>
+      </c>
+      <c r="I465" s="2" t="inlineStr">
+        <is>
+          <t>https://foodrinco.gr</t>
+        </is>
+      </c>
+      <c r="J465" s="2" t="inlineStr"/>
+      <c r="K465" s="2" t="inlineStr"/>
+      <c r="L465" s="2" t="inlineStr"/>
+      <c r="M465" s="2" t="inlineStr"/>
+      <c r="N465" s="2" t="inlineStr">
+        <is>
+          <t>info@foodrinco.gr</t>
+        </is>
+      </c>
+      <c r="O465" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 6400 0200</t>
+        </is>
+      </c>
+      <c r="P465" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q465" s="2" t="inlineStr">
+        <is>
+          <t>094430257</t>
+        </is>
+      </c>
+      <c r="R465" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vytogiannis-group-of-companies/</t>
+        </is>
+      </c>
+      <c r="S465" s="2" t="inlineStr"/>
+      <c r="T465" s="2" t="inlineStr"/>
+      <c r="U465" s="2" t="inlineStr"/>
+      <c r="V465" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/user/foodrinco</t>
+        </is>
+      </c>
+      <c r="W465" s="2" t="inlineStr">
+        <is>
+          <t>Stelios Tiktopoulos</t>
+        </is>
+      </c>
+      <c r="X465" s="2" t="inlineStr">
+        <is>
+          <t>Area Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y465" s="2" t="inlineStr"/>
+      <c r="Z465" s="2" t="inlineStr"/>
+      <c r="AA465" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/stelios-tiktopoulos-6bb06934/</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" s="2" t="inlineStr">
+        <is>
+          <t>L. Patroni And Co. E.e.</t>
+        </is>
+      </c>
+      <c r="B466" s="2" t="inlineStr">
+        <is>
+          <t>L. Patroni And Co. E.e.</t>
+        </is>
+      </c>
+      <c r="C466" s="2" t="inlineStr">
+        <is>
+          <t>7418</t>
+        </is>
+      </c>
+      <c r="D466" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E466" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Marousi</t>
+        </is>
+      </c>
+      <c r="F466" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G466" s="2" t="inlineStr">
+        <is>
+          <t>37A Leoforos Kifisias</t>
+        </is>
+      </c>
+      <c r="H466" s="2" t="inlineStr">
+        <is>
+          <t>151 23</t>
+        </is>
+      </c>
+      <c r="I466" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lesconnaisseurs.gr</t>
+        </is>
+      </c>
+      <c r="J466" s="2" t="inlineStr"/>
+      <c r="K466" s="2" t="inlineStr"/>
+      <c r="L466" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M466" s="2" t="inlineStr"/>
+      <c r="N466" s="2" t="inlineStr">
+        <is>
+          <t>info@lesconnaisseurs.gr</t>
+        </is>
+      </c>
+      <c r="O466" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0723 9195</t>
+        </is>
+      </c>
+      <c r="P466" s="2" t="inlineStr">
+        <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="Q466" s="2" t="inlineStr">
+        <is>
+          <t>093693780</t>
+        </is>
+      </c>
+      <c r="R466" s="2" t="inlineStr"/>
+      <c r="S466" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/lesconnaisseurs.gr/</t>
+        </is>
+      </c>
+      <c r="T466" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lesconnaisseurs/</t>
+        </is>
+      </c>
+      <c r="U466" s="2" t="inlineStr"/>
+      <c r="V466" s="2" t="inlineStr"/>
+      <c r="W466" s="2" t="inlineStr"/>
+      <c r="X466" s="2" t="inlineStr"/>
+      <c r="Y466" s="2" t="inlineStr"/>
+      <c r="Z466" s="2" t="inlineStr"/>
+      <c r="AA466" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
